--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ShopItemData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
@@ -18,26 +18,88 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>作者</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>作者:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+道具=0,动物=1,家具=2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>作者:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+ 金币=0,钻石=1,货币=2</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>string</t>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>bool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>shopItemDatas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>shopName</t>
@@ -50,7 +112,7 @@
   </si>
   <si>
     <t>item</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>priceValue</t>
@@ -60,26 +122,54 @@
   </si>
   <si>
     <t>种子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>果蔬</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>植物店</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>EditorShopItemData</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>设施</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>payType</t>
+  </si>
+  <si>
+    <t>shopItemType</t>
+  </si>
+  <si>
+    <t>buyLimitOne</t>
+  </si>
+  <si>
+    <t>buyAction</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,11 +178,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -112,10 +225,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -123,9 +239,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -402,18 +525,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
     <col min="3" max="3" width="24" style="1" customWidth="1"/>
-    <col min="4" max="5" width="13.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.25" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="4" max="7" width="13.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -421,7 +544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,10 +561,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -455,13 +590,25 @@
         <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -474,14 +621,26 @@
       <c r="D4" s="2">
         <v>1001</v>
       </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -494,14 +653,26 @@
       <c r="D5" s="2">
         <v>1002</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>100</v>
+      </c>
+      <c r="H5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -514,14 +685,26 @@
       <c r="D6" s="2">
         <v>1003</v>
       </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -534,14 +717,26 @@
       <c r="D7" s="2">
         <v>1004</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>100</v>
+      </c>
+      <c r="H7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -554,14 +749,26 @@
       <c r="D8" s="2">
         <v>1005</v>
       </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -574,16 +781,541 @@
       <c r="D9" s="2">
         <v>1006</v>
       </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="b">
-        <v>1</v>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>100</v>
+      </c>
+      <c r="H9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2101</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2102</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2103</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>100</v>
+      </c>
+      <c r="H13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2104</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>100</v>
+      </c>
+      <c r="H14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2105</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>100</v>
+      </c>
+      <c r="H15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2106</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="3">
+        <v>2107</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2108</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2109</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2110</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>100</v>
+      </c>
+      <c r="H20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2111</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>100</v>
+      </c>
+      <c r="H21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2112</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>100</v>
+      </c>
+      <c r="H22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2113</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>100</v>
+      </c>
+      <c r="H23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="4">
+        <v>2200</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>100</v>
+      </c>
+      <c r="H24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="4">
+        <v>2201</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>100</v>
+      </c>
+      <c r="H25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="25">
   <si>
     <t>string</t>
   </si>
@@ -162,6 +162,14 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>动物</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -526,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -1312,6 +1320,38 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3000</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>100</v>
+      </c>
+      <c r="H26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="34">
   <si>
     <t>string</t>
   </si>
@@ -171,6 +171,33 @@
   <si>
     <t>动物</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>public int id;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public string pastureName; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public int linkItem;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public int creatMoney;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public List&lt;int2&gt; creatItems = new List&lt;int2&gt;();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public int level;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public int packageCount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public int waterCount;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    public int animalCount;</t>
   </si>
 </sst>
 </file>
@@ -534,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -1333,8 +1360,8 @@
       <c r="D26" s="1">
         <v>3000</v>
       </c>
-      <c r="E26" s="1">
-        <v>1</v>
+      <c r="E26" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -1350,6 +1377,46 @@
       </c>
       <c r="J26" s="1">
         <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E29" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E30" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E31" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E32" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E33" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E34" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="25">
   <si>
     <t>string</t>
   </si>
@@ -171,33 +171,6 @@
   <si>
     <t>动物</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>public int id;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public string pastureName; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public int linkItem;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public int creatMoney;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public List&lt;int2&gt; creatItems = new List&lt;int2&gt;();</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public int level;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public int packageCount;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public int waterCount;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    public int animalCount;</t>
   </si>
 </sst>
 </file>
@@ -561,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -1360,8 +1333,8 @@
       <c r="D26" s="1">
         <v>3000</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>25</v>
+      <c r="E26" s="1">
+        <v>1</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -1377,46 +1350,6 @@
       </c>
       <c r="J26" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E27" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E28" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E29" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E30" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E31" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="E32" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E33" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E34" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="25">
   <si>
     <t>string</t>
   </si>
@@ -534,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -1258,16 +1258,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="4">
-        <v>2200</v>
+        <v>2114</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -1299,7 +1299,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="4">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -1322,33 +1322,65 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="4">
+        <v>2201</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>100</v>
+      </c>
+      <c r="H26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B27" s="1">
         <v>1004</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D27" s="1">
         <v>3000</v>
       </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1">
-        <v>100</v>
-      </c>
-      <c r="H26" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" s="1">
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>100</v>
+      </c>
+      <c r="H27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="25">
   <si>
     <t>string</t>
   </si>
@@ -534,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -1203,7 +1203,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="3">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -1234,8 +1234,8 @@
       <c r="C23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="3">
-        <v>2113</v>
+      <c r="D23" s="4">
+        <v>2114</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
@@ -1258,16 +1258,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B24" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="4">
-        <v>2114</v>
+        <v>2200</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -1299,7 +1299,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="4">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -1322,21 +1322,21 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="4">
-        <v>2201</v>
+        <v>23</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3000</v>
       </c>
       <c r="E26" s="1">
-        <v>2</v>
-      </c>
-      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1">
@@ -1349,38 +1349,6 @@
         <v>1</v>
       </c>
       <c r="J26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="1">
-        <v>1004</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="1">
-        <v>3000</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1">
-        <v>100</v>
-      </c>
-      <c r="H27" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I27" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -811,6 +811,12 @@
       <c r="H4" s="1">
         <v>1</v>
       </c>
+      <c r="I4" s="1">
+        <v>948</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K4" s="1" t="s">
         <v>32</v>
       </c>
@@ -846,6 +852,12 @@
       <c r="H5" s="1">
         <v>1</v>
       </c>
+      <c r="I5" s="1">
+        <v>948</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K5" s="1" t="s">
         <v>32</v>
       </c>
@@ -881,6 +893,12 @@
       <c r="H6" s="1">
         <v>1</v>
       </c>
+      <c r="I6" s="1">
+        <v>948</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K6" s="1" t="s">
         <v>32</v>
       </c>
@@ -916,6 +934,12 @@
       <c r="H7" s="1">
         <v>2</v>
       </c>
+      <c r="I7" s="1">
+        <v>948</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K7" s="1" t="s">
         <v>32</v>
       </c>
@@ -951,6 +975,12 @@
       <c r="H8" s="1">
         <v>2</v>
       </c>
+      <c r="I8" s="1">
+        <v>948</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K8" s="1" t="s">
         <v>32</v>
       </c>
@@ -986,6 +1016,12 @@
       <c r="H9" s="1">
         <v>2</v>
       </c>
+      <c r="I9" s="1">
+        <v>948</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K9" s="1" t="s">
         <v>32</v>
       </c>
@@ -1021,6 +1057,12 @@
       <c r="H10" s="1">
         <v>3</v>
       </c>
+      <c r="I10" s="1">
+        <v>948</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K10" s="1" t="s">
         <v>32</v>
       </c>
@@ -1056,6 +1098,12 @@
       <c r="H11" s="1">
         <v>3</v>
       </c>
+      <c r="I11" s="1">
+        <v>948</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K11" s="1" t="s">
         <v>32</v>
       </c>
@@ -1091,6 +1139,12 @@
       <c r="H12" s="1">
         <v>3</v>
       </c>
+      <c r="I12" s="1">
+        <v>948</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K12" s="1" t="s">
         <v>32</v>
       </c>
@@ -1126,6 +1180,12 @@
       <c r="H13" s="1">
         <v>4</v>
       </c>
+      <c r="I13" s="1">
+        <v>948</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K13" s="1" t="s">
         <v>32</v>
       </c>
@@ -1161,6 +1221,12 @@
       <c r="H14" s="1">
         <v>4</v>
       </c>
+      <c r="I14" s="1">
+        <v>948</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K14" s="1" t="s">
         <v>32</v>
       </c>
@@ -1196,6 +1262,12 @@
       <c r="H15" s="1">
         <v>4</v>
       </c>
+      <c r="I15" s="1">
+        <v>948</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K15" s="1" t="s">
         <v>32</v>
       </c>
@@ -1231,6 +1303,12 @@
       <c r="H16" s="1">
         <v>5</v>
       </c>
+      <c r="I16" s="1">
+        <v>948</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K16" s="1" t="s">
         <v>32</v>
       </c>
@@ -1266,6 +1344,12 @@
       <c r="H17" s="1">
         <v>5</v>
       </c>
+      <c r="I17" s="1">
+        <v>948</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K17" s="1" t="s">
         <v>32</v>
       </c>
@@ -1301,6 +1385,12 @@
       <c r="H18" s="1">
         <v>5</v>
       </c>
+      <c r="I18" s="1">
+        <v>948</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K18" s="1" t="s">
         <v>32</v>
       </c>
@@ -1336,6 +1426,12 @@
       <c r="H19" s="1">
         <v>6</v>
       </c>
+      <c r="I19" s="1">
+        <v>948</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K19" s="1" t="s">
         <v>32</v>
       </c>
@@ -1371,6 +1467,12 @@
       <c r="H20" s="1">
         <v>6</v>
       </c>
+      <c r="I20" s="1">
+        <v>948</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K20" s="1" t="s">
         <v>32</v>
       </c>
@@ -1406,6 +1508,12 @@
       <c r="H21" s="1">
         <v>6</v>
       </c>
+      <c r="I21" s="1">
+        <v>948</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K21" s="1" t="s">
         <v>32</v>
       </c>
@@ -1441,6 +1549,12 @@
       <c r="H22" s="1">
         <v>7</v>
       </c>
+      <c r="I22" s="1">
+        <v>948</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K22" s="1" t="s">
         <v>32</v>
       </c>
@@ -1476,6 +1590,12 @@
       <c r="H23" s="1">
         <v>7</v>
       </c>
+      <c r="I23" s="1">
+        <v>948</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K23" s="1" t="s">
         <v>32</v>
       </c>
@@ -1511,6 +1631,12 @@
       <c r="H24" s="1">
         <v>7</v>
       </c>
+      <c r="I24" s="1">
+        <v>948</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K24" s="1" t="s">
         <v>32</v>
       </c>
@@ -1546,6 +1672,12 @@
       <c r="H25" s="1">
         <v>8</v>
       </c>
+      <c r="I25" s="1">
+        <v>948</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K25" s="1" t="s">
         <v>32</v>
       </c>
@@ -1581,6 +1713,12 @@
       <c r="H26" s="1">
         <v>8</v>
       </c>
+      <c r="I26" s="1">
+        <v>948</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K26" s="1" t="s">
         <v>32</v>
       </c>
@@ -1616,6 +1754,12 @@
       <c r="H27" s="1">
         <v>8</v>
       </c>
+      <c r="I27" s="1">
+        <v>948</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K27" s="1" t="s">
         <v>32</v>
       </c>
@@ -1651,6 +1795,12 @@
       <c r="H28" s="1">
         <v>9</v>
       </c>
+      <c r="I28" s="1">
+        <v>948</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K28" s="1" t="s">
         <v>32</v>
       </c>
@@ -1686,6 +1836,12 @@
       <c r="H29" s="1">
         <v>9</v>
       </c>
+      <c r="I29" s="1">
+        <v>948</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K29" s="1" t="s">
         <v>32</v>
       </c>
@@ -1721,6 +1877,12 @@
       <c r="H30" s="1">
         <v>9</v>
       </c>
+      <c r="I30" s="1">
+        <v>948</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K30" s="1" t="s">
         <v>32</v>
       </c>
@@ -1756,6 +1918,12 @@
       <c r="H31" s="1">
         <v>9</v>
       </c>
+      <c r="I31" s="1">
+        <v>948</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K31" s="1" t="s">
         <v>32</v>
       </c>
@@ -1791,6 +1959,12 @@
       <c r="H32" s="1">
         <v>1</v>
       </c>
+      <c r="I32" s="1">
+        <v>948</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K32" s="1" t="s">
         <v>32</v>
       </c>
@@ -1826,6 +2000,12 @@
       <c r="H33" s="1">
         <v>1</v>
       </c>
+      <c r="I33" s="1">
+        <v>948</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K33" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,6 +2041,12 @@
       <c r="H34" s="1">
         <v>1</v>
       </c>
+      <c r="I34" s="1">
+        <v>948</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K34" s="1" t="s">
         <v>32</v>
       </c>
@@ -1896,6 +2082,12 @@
       <c r="H35" s="1">
         <v>2</v>
       </c>
+      <c r="I35" s="1">
+        <v>948</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K35" s="1" t="s">
         <v>32</v>
       </c>
@@ -1931,6 +2123,12 @@
       <c r="H36" s="1">
         <v>2</v>
       </c>
+      <c r="I36" s="1">
+        <v>948</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K36" s="1" t="s">
         <v>32</v>
       </c>
@@ -1966,6 +2164,12 @@
       <c r="H37" s="1">
         <v>2</v>
       </c>
+      <c r="I37" s="1">
+        <v>948</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K37" s="1" t="s">
         <v>32</v>
       </c>
@@ -2001,6 +2205,12 @@
       <c r="H38" s="1">
         <v>3</v>
       </c>
+      <c r="I38" s="1">
+        <v>948</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K38" s="1" t="s">
         <v>32</v>
       </c>
@@ -2036,6 +2246,12 @@
       <c r="H39" s="1">
         <v>3</v>
       </c>
+      <c r="I39" s="1">
+        <v>948</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2071,6 +2287,12 @@
       <c r="H40" s="1">
         <v>3</v>
       </c>
+      <c r="I40" s="1">
+        <v>948</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2106,6 +2328,12 @@
       <c r="H41" s="1">
         <v>4</v>
       </c>
+      <c r="I41" s="1">
+        <v>948</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K41" s="1" t="s">
         <v>32</v>
       </c>
@@ -2141,6 +2369,12 @@
       <c r="H42" s="1">
         <v>4</v>
       </c>
+      <c r="I42" s="1">
+        <v>948</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K42" s="1" t="s">
         <v>32</v>
       </c>
@@ -2176,6 +2410,12 @@
       <c r="H43" s="1">
         <v>4</v>
       </c>
+      <c r="I43" s="1">
+        <v>948</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K43" s="1" t="s">
         <v>32</v>
       </c>
@@ -2211,6 +2451,12 @@
       <c r="H44" s="1">
         <v>5</v>
       </c>
+      <c r="I44" s="1">
+        <v>948</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K44" s="1" t="s">
         <v>32</v>
       </c>
@@ -2246,6 +2492,12 @@
       <c r="H45" s="1">
         <v>5</v>
       </c>
+      <c r="I45" s="1">
+        <v>948</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K45" s="1" t="s">
         <v>32</v>
       </c>
@@ -2281,6 +2533,12 @@
       <c r="H46" s="1">
         <v>5</v>
       </c>
+      <c r="I46" s="1">
+        <v>948</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K46" s="1" t="s">
         <v>32</v>
       </c>
@@ -2316,6 +2574,12 @@
       <c r="H47" s="1">
         <v>6</v>
       </c>
+      <c r="I47" s="1">
+        <v>948</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K47" s="1" t="s">
         <v>32</v>
       </c>
@@ -2351,6 +2615,12 @@
       <c r="H48" s="1">
         <v>6</v>
       </c>
+      <c r="I48" s="1">
+        <v>948</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K48" s="1" t="s">
         <v>32</v>
       </c>
@@ -2386,6 +2656,12 @@
       <c r="H49" s="1">
         <v>6</v>
       </c>
+      <c r="I49" s="1">
+        <v>948</v>
+      </c>
+      <c r="J49" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K49" s="1" t="s">
         <v>32</v>
       </c>
@@ -2421,6 +2697,12 @@
       <c r="H50" s="1">
         <v>7</v>
       </c>
+      <c r="I50" s="1">
+        <v>948</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K50" s="1" t="s">
         <v>32</v>
       </c>
@@ -2456,6 +2738,12 @@
       <c r="H51" s="1">
         <v>7</v>
       </c>
+      <c r="I51" s="1">
+        <v>948</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K51" s="1" t="s">
         <v>32</v>
       </c>
@@ -2491,6 +2779,12 @@
       <c r="H52" s="1">
         <v>7</v>
       </c>
+      <c r="I52" s="1">
+        <v>948</v>
+      </c>
+      <c r="J52" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K52" s="1" t="s">
         <v>32</v>
       </c>
@@ -2526,6 +2820,12 @@
       <c r="H53" s="1">
         <v>8</v>
       </c>
+      <c r="I53" s="1">
+        <v>948</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K53" s="1" t="s">
         <v>32</v>
       </c>
@@ -2561,6 +2861,12 @@
       <c r="H54" s="1">
         <v>8</v>
       </c>
+      <c r="I54" s="1">
+        <v>948</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K54" s="1" t="s">
         <v>32</v>
       </c>
@@ -2596,6 +2902,12 @@
       <c r="H55" s="1">
         <v>8</v>
       </c>
+      <c r="I55" s="1">
+        <v>948</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K55" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,6 +2943,12 @@
       <c r="H56" s="1">
         <v>9</v>
       </c>
+      <c r="I56" s="1">
+        <v>948</v>
+      </c>
+      <c r="J56" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K56" s="1" t="s">
         <v>32</v>
       </c>
@@ -2666,6 +2984,12 @@
       <c r="H57" s="1">
         <v>9</v>
       </c>
+      <c r="I57" s="1">
+        <v>948</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K57" s="1" t="s">
         <v>32</v>
       </c>
@@ -2701,6 +3025,12 @@
       <c r="H58" s="1">
         <v>9</v>
       </c>
+      <c r="I58" s="1">
+        <v>948</v>
+      </c>
+      <c r="J58" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K58" s="1" t="s">
         <v>32</v>
       </c>
@@ -2736,6 +3066,12 @@
       <c r="H59" s="1">
         <v>9</v>
       </c>
+      <c r="I59" s="1">
+        <v>948</v>
+      </c>
+      <c r="J59" s="1">
+        <v>1068306</v>
+      </c>
       <c r="K59" s="1" t="s">
         <v>32</v>
       </c>
@@ -2771,6 +3107,12 @@
       <c r="H60" s="1">
         <v>3</v>
       </c>
+      <c r="I60" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J60" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K60" s="1" t="s">
         <v>38</v>
       </c>
@@ -2806,6 +3148,12 @@
       <c r="H61" s="1">
         <v>3</v>
       </c>
+      <c r="I61" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J61" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K61" s="1" t="s">
         <v>38</v>
       </c>
@@ -2841,6 +3189,12 @@
       <c r="H62" s="1">
         <v>2</v>
       </c>
+      <c r="I62" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J62" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K62" s="1" t="s">
         <v>38</v>
       </c>
@@ -2876,6 +3230,12 @@
       <c r="H63" s="1">
         <v>2</v>
       </c>
+      <c r="I63" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J63" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K63" s="1" t="s">
         <v>38</v>
       </c>
@@ -2911,6 +3271,12 @@
       <c r="H64" s="1">
         <v>1</v>
       </c>
+      <c r="I64" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J64" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K64" s="1" t="s">
         <v>38</v>
       </c>
@@ -2946,6 +3312,12 @@
       <c r="H65" s="1">
         <v>3</v>
       </c>
+      <c r="I65" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J65" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K65" s="1" t="s">
         <v>38</v>
       </c>
@@ -2981,6 +3353,12 @@
       <c r="H66" s="1">
         <v>3</v>
       </c>
+      <c r="I66" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K66" s="1" t="s">
         <v>38</v>
       </c>
@@ -3016,6 +3394,12 @@
       <c r="H67" s="1">
         <v>2</v>
       </c>
+      <c r="I67" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J67" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K67" s="1" t="s">
         <v>38</v>
       </c>
@@ -3051,6 +3435,12 @@
       <c r="H68" s="1">
         <v>1</v>
       </c>
+      <c r="I68" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J68" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K68" s="1" t="s">
         <v>38</v>
       </c>
@@ -3086,6 +3476,12 @@
       <c r="H69" s="1">
         <v>3</v>
       </c>
+      <c r="I69" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J69" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K69" s="1" t="s">
         <v>38</v>
       </c>
@@ -3121,6 +3517,12 @@
       <c r="H70" s="1">
         <v>4</v>
       </c>
+      <c r="I70" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J70" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K70" s="1" t="s">
         <v>38</v>
       </c>
@@ -3156,6 +3558,12 @@
       <c r="H71" s="1">
         <v>1</v>
       </c>
+      <c r="I71" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J71" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K71" s="1" t="s">
         <v>38</v>
       </c>
@@ -3191,6 +3599,12 @@
       <c r="H72" s="1">
         <v>1</v>
       </c>
+      <c r="I72" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J72" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K72" s="1" t="s">
         <v>38</v>
       </c>
@@ -3226,6 +3640,12 @@
       <c r="H73" s="1">
         <v>2</v>
       </c>
+      <c r="I73" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J73" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K73" s="1" t="s">
         <v>38</v>
       </c>
@@ -3261,6 +3681,12 @@
       <c r="H74" s="1">
         <v>1</v>
       </c>
+      <c r="I74" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J74" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K74" s="1" t="s">
         <v>38</v>
       </c>
@@ -3296,6 +3722,12 @@
       <c r="H75" s="1">
         <v>1</v>
       </c>
+      <c r="I75" s="1">
+        <v>1014</v>
+      </c>
+      <c r="J75" s="1">
+        <v>1088635</v>
+      </c>
       <c r="K75" s="1" t="s">
         <v>38</v>
       </c>
@@ -3331,6 +3763,12 @@
       <c r="H76" s="1">
         <v>1</v>
       </c>
+      <c r="I76" s="1">
+        <v>900</v>
+      </c>
+      <c r="J76" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K76" t="s">
         <v>34</v>
       </c>
@@ -3366,6 +3804,12 @@
       <c r="H77" s="1">
         <v>2</v>
       </c>
+      <c r="I77" s="1">
+        <v>900</v>
+      </c>
+      <c r="J77" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K77" t="s">
         <v>34</v>
       </c>
@@ -3401,6 +3845,12 @@
       <c r="H78" s="1">
         <v>3</v>
       </c>
+      <c r="I78" s="1">
+        <v>900</v>
+      </c>
+      <c r="J78" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K78" t="s">
         <v>34</v>
       </c>
@@ -3436,6 +3886,12 @@
       <c r="H79" s="1">
         <v>3</v>
       </c>
+      <c r="I79" s="1">
+        <v>900</v>
+      </c>
+      <c r="J79" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K79" t="s">
         <v>34</v>
       </c>
@@ -3471,6 +3927,12 @@
       <c r="H80" s="1">
         <v>4</v>
       </c>
+      <c r="I80" s="1">
+        <v>900</v>
+      </c>
+      <c r="J80" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K80" t="s">
         <v>34</v>
       </c>
@@ -3506,6 +3968,12 @@
       <c r="H81" s="1">
         <v>5</v>
       </c>
+      <c r="I81" s="1">
+        <v>900</v>
+      </c>
+      <c r="J81" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K81" t="s">
         <v>34</v>
       </c>
@@ -3541,6 +4009,12 @@
       <c r="H82" s="1">
         <v>6</v>
       </c>
+      <c r="I82" s="1">
+        <v>900</v>
+      </c>
+      <c r="J82" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K82" t="s">
         <v>34</v>
       </c>
@@ -3576,6 +4050,12 @@
       <c r="H83" s="1">
         <v>2</v>
       </c>
+      <c r="I83" s="1">
+        <v>900</v>
+      </c>
+      <c r="J83" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K83" t="s">
         <v>34</v>
       </c>
@@ -3611,6 +4091,12 @@
       <c r="H84" s="1">
         <v>1</v>
       </c>
+      <c r="I84" s="1">
+        <v>900</v>
+      </c>
+      <c r="J84" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K84" t="s">
         <v>34</v>
       </c>
@@ -3646,6 +4132,12 @@
       <c r="H85" s="1">
         <v>2</v>
       </c>
+      <c r="I85" s="1">
+        <v>900</v>
+      </c>
+      <c r="J85" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K85" t="s">
         <v>34</v>
       </c>
@@ -3681,6 +4173,12 @@
       <c r="H86" s="1">
         <v>3</v>
       </c>
+      <c r="I86" s="1">
+        <v>900</v>
+      </c>
+      <c r="J86" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K86" t="s">
         <v>34</v>
       </c>
@@ -3716,6 +4214,12 @@
       <c r="H87" s="1">
         <v>1</v>
       </c>
+      <c r="I87" s="1">
+        <v>900</v>
+      </c>
+      <c r="J87" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K87" t="s">
         <v>34</v>
       </c>
@@ -3751,6 +4255,12 @@
       <c r="H88" s="1">
         <v>5</v>
       </c>
+      <c r="I88" s="1">
+        <v>900</v>
+      </c>
+      <c r="J88" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K88" t="s">
         <v>34</v>
       </c>
@@ -3786,6 +4296,12 @@
       <c r="H89" s="1">
         <v>6</v>
       </c>
+      <c r="I89" s="1">
+        <v>900</v>
+      </c>
+      <c r="J89" s="1">
+        <v>1079546</v>
+      </c>
       <c r="K89" t="s">
         <v>34</v>
       </c>
@@ -3821,6 +4337,12 @@
       <c r="H90" s="1">
         <v>1</v>
       </c>
+      <c r="I90" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J90" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K90" s="1" t="s">
         <v>36</v>
       </c>
@@ -3856,6 +4378,12 @@
       <c r="H91" s="1">
         <v>1</v>
       </c>
+      <c r="I91" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J91" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K91" s="1" t="s">
         <v>36</v>
       </c>
@@ -3891,6 +4419,12 @@
       <c r="H92" s="1">
         <v>1</v>
       </c>
+      <c r="I92" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J92" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K92" s="1" t="s">
         <v>36</v>
       </c>
@@ -3926,6 +4460,12 @@
       <c r="H93" s="1">
         <v>1</v>
       </c>
+      <c r="I93" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J93" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K93" s="1" t="s">
         <v>36</v>
       </c>
@@ -3961,6 +4501,12 @@
       <c r="H94" s="1">
         <v>1</v>
       </c>
+      <c r="I94" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J94" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K94" s="1" t="s">
         <v>36</v>
       </c>
@@ -3996,6 +4542,12 @@
       <c r="H95" s="1">
         <v>1</v>
       </c>
+      <c r="I95" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J95" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K95" s="1" t="s">
         <v>36</v>
       </c>
@@ -4031,6 +4583,12 @@
       <c r="H96" s="1">
         <v>1</v>
       </c>
+      <c r="I96" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J96" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K96" s="1" t="s">
         <v>36</v>
       </c>
@@ -4066,6 +4624,12 @@
       <c r="H97" s="1">
         <v>1</v>
       </c>
+      <c r="I97" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J97" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K97" s="1" t="s">
         <v>36</v>
       </c>
@@ -4101,10 +4665,19 @@
       <c r="H98" s="1">
         <v>1</v>
       </c>
+      <c r="I98" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J98" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K98" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L98" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M98" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4133,10 +4706,19 @@
       <c r="H99" s="1">
         <v>1</v>
       </c>
+      <c r="I99" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J99" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K99" s="1" t="s">
         <v>36</v>
       </c>
       <c r="L99" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M99" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4165,6 +4747,12 @@
       <c r="H100" s="1">
         <v>1</v>
       </c>
+      <c r="I100" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J100" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K100" s="1" t="s">
         <v>36</v>
       </c>
@@ -4200,6 +4788,12 @@
       <c r="H101" s="1">
         <v>1</v>
       </c>
+      <c r="I101" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J101" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K101" s="1" t="s">
         <v>36</v>
       </c>
@@ -4235,6 +4829,12 @@
       <c r="H102" s="1">
         <v>1</v>
       </c>
+      <c r="I102" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J102" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K102" s="1" t="s">
         <v>36</v>
       </c>
@@ -4270,6 +4870,12 @@
       <c r="H103" s="1">
         <v>1</v>
       </c>
+      <c r="I103" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J103" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K103" s="1" t="s">
         <v>36</v>
       </c>
@@ -4305,6 +4911,12 @@
       <c r="H104" s="1">
         <v>1</v>
       </c>
+      <c r="I104" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J104" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K104" s="1" t="s">
         <v>36</v>
       </c>
@@ -4340,6 +4952,12 @@
       <c r="H105" s="1">
         <v>1</v>
       </c>
+      <c r="I105" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J105" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K105" s="1" t="s">
         <v>36</v>
       </c>
@@ -4375,6 +4993,12 @@
       <c r="H106" s="1">
         <v>1</v>
       </c>
+      <c r="I106" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J106" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K106" s="1" t="s">
         <v>36</v>
       </c>
@@ -4410,6 +5034,12 @@
       <c r="H107" s="1">
         <v>1</v>
       </c>
+      <c r="I107" s="1">
+        <v>2180</v>
+      </c>
+      <c r="J107" s="1">
+        <v>1165443</v>
+      </c>
       <c r="K107" s="1" t="s">
         <v>36</v>
       </c>
@@ -4445,6 +5075,12 @@
       <c r="H108" s="1">
         <v>1</v>
       </c>
+      <c r="I108" s="1">
+        <v>1756</v>
+      </c>
+      <c r="J108" s="1">
+        <v>1019120</v>
+      </c>
       <c r="K108" s="1" t="s">
         <v>35</v>
       </c>
@@ -4480,6 +5116,12 @@
       <c r="H109" s="1">
         <v>1</v>
       </c>
+      <c r="I109" s="1">
+        <v>1756</v>
+      </c>
+      <c r="J109" s="1">
+        <v>1019120</v>
+      </c>
       <c r="K109" s="1" t="s">
         <v>50</v>
       </c>
@@ -4515,6 +5157,12 @@
       <c r="H110" s="1">
         <v>1</v>
       </c>
+      <c r="I110" s="1">
+        <v>1756</v>
+      </c>
+      <c r="J110" s="1">
+        <v>1019120</v>
+      </c>
       <c r="K110" s="1" t="s">
         <v>51</v>
       </c>
@@ -4550,6 +5198,12 @@
       <c r="H111" s="1">
         <v>1</v>
       </c>
+      <c r="I111" s="1">
+        <v>1756</v>
+      </c>
+      <c r="J111" s="1">
+        <v>1019120</v>
+      </c>
       <c r="K111" s="1" t="s">
         <v>52</v>
       </c>
@@ -4585,6 +5239,12 @@
       <c r="H112" s="1">
         <v>1</v>
       </c>
+      <c r="I112" s="1">
+        <v>1756</v>
+      </c>
+      <c r="J112" s="1">
+        <v>1019120</v>
+      </c>
       <c r="K112" s="1" t="s">
         <v>53</v>
       </c>
@@ -4620,6 +5280,12 @@
       <c r="H113" s="1">
         <v>1</v>
       </c>
+      <c r="I113" s="1">
+        <v>1756</v>
+      </c>
+      <c r="J113" s="1">
+        <v>1019120</v>
+      </c>
       <c r="K113" s="1" t="s">
         <v>54</v>
       </c>
@@ -4655,6 +5321,12 @@
       <c r="H114" s="1">
         <v>1</v>
       </c>
+      <c r="I114" s="1">
+        <v>1756</v>
+      </c>
+      <c r="J114" s="1">
+        <v>1019120</v>
+      </c>
       <c r="K114" s="1" t="s">
         <v>55</v>
       </c>
@@ -4690,6 +5362,12 @@
       <c r="H115" s="1">
         <v>1</v>
       </c>
+      <c r="I115" s="1">
+        <v>5309</v>
+      </c>
+      <c r="J115" s="1">
+        <v>1159783</v>
+      </c>
       <c r="K115" s="1">
         <v>41</v>
       </c>
@@ -4725,6 +5403,12 @@
       <c r="H116" s="1">
         <v>1</v>
       </c>
+      <c r="I116" s="1">
+        <v>5309</v>
+      </c>
+      <c r="J116" s="1">
+        <v>1159783</v>
+      </c>
       <c r="K116" s="1">
         <v>41</v>
       </c>
@@ -4760,6 +5444,12 @@
       <c r="H117" s="1">
         <v>1</v>
       </c>
+      <c r="I117" s="1">
+        <v>5309</v>
+      </c>
+      <c r="J117" s="1">
+        <v>1159783</v>
+      </c>
       <c r="K117" s="1">
         <v>41</v>
       </c>
@@ -4795,6 +5485,12 @@
       <c r="H118" s="1">
         <v>1</v>
       </c>
+      <c r="I118" s="1">
+        <v>5309</v>
+      </c>
+      <c r="J118" s="1">
+        <v>1159783</v>
+      </c>
       <c r="K118" s="1">
         <v>41</v>
       </c>
@@ -4830,6 +5526,12 @@
       <c r="H119" s="1">
         <v>1</v>
       </c>
+      <c r="I119" s="1">
+        <v>5309</v>
+      </c>
+      <c r="J119" s="1">
+        <v>1159783</v>
+      </c>
       <c r="K119" s="1">
         <v>41</v>
       </c>
@@ -4865,6 +5567,12 @@
       <c r="H120" s="1">
         <v>1</v>
       </c>
+      <c r="I120" s="1">
+        <v>5309</v>
+      </c>
+      <c r="J120" s="1">
+        <v>1159783</v>
+      </c>
       <c r="K120" s="1">
         <v>41</v>
       </c>
@@ -4900,6 +5608,12 @@
       <c r="H121" s="1">
         <v>1</v>
       </c>
+      <c r="I121" s="1">
+        <v>5309</v>
+      </c>
+      <c r="J121" s="1">
+        <v>1159783</v>
+      </c>
       <c r="K121" s="1">
         <v>41</v>
       </c>
@@ -4935,6 +5649,12 @@
       <c r="H122" s="1">
         <v>1</v>
       </c>
+      <c r="I122" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J122" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K122" s="1" t="s">
         <v>37</v>
       </c>
@@ -4970,6 +5690,12 @@
       <c r="H123" s="1">
         <v>1</v>
       </c>
+      <c r="I123" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J123" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K123" s="1" t="s">
         <v>37</v>
       </c>
@@ -5005,6 +5731,12 @@
       <c r="H124" s="1">
         <v>1</v>
       </c>
+      <c r="I124" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J124" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K124" s="1" t="s">
         <v>37</v>
       </c>
@@ -5040,6 +5772,12 @@
       <c r="H125" s="1">
         <v>2</v>
       </c>
+      <c r="I125" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J125" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K125" s="1" t="s">
         <v>37</v>
       </c>
@@ -5075,6 +5813,12 @@
       <c r="H126" s="1">
         <v>2</v>
       </c>
+      <c r="I126" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J126" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K126" s="1" t="s">
         <v>37</v>
       </c>
@@ -5110,6 +5854,12 @@
       <c r="H127" s="1">
         <v>3</v>
       </c>
+      <c r="I127" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J127" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K127" s="1" t="s">
         <v>37</v>
       </c>
@@ -5145,6 +5895,12 @@
       <c r="H128" s="1">
         <v>3</v>
       </c>
+      <c r="I128" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J128" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K128" s="1" t="s">
         <v>37</v>
       </c>
@@ -5180,6 +5936,12 @@
       <c r="H129" s="1">
         <v>3</v>
       </c>
+      <c r="I129" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J129" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K129" s="1" t="s">
         <v>37</v>
       </c>
@@ -5215,6 +5977,12 @@
       <c r="H130" s="1">
         <v>3</v>
       </c>
+      <c r="I130" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J130" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K130" s="1" t="s">
         <v>37</v>
       </c>
@@ -5250,6 +6018,12 @@
       <c r="H131" s="1">
         <v>3</v>
       </c>
+      <c r="I131" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J131" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K131" s="1" t="s">
         <v>37</v>
       </c>
@@ -5285,6 +6059,12 @@
       <c r="H132" s="1">
         <v>4</v>
       </c>
+      <c r="I132" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J132" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K132" s="1" t="s">
         <v>37</v>
       </c>
@@ -5320,6 +6100,12 @@
       <c r="H133" s="1">
         <v>4</v>
       </c>
+      <c r="I133" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J133" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K133" s="1" t="s">
         <v>37</v>
       </c>
@@ -5355,6 +6141,12 @@
       <c r="H134" s="1">
         <v>4</v>
       </c>
+      <c r="I134" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J134" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K134" s="1" t="s">
         <v>37</v>
       </c>
@@ -5390,6 +6182,12 @@
       <c r="H135" s="1">
         <v>1</v>
       </c>
+      <c r="I135" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J135" s="1">
+        <v>1019972</v>
+      </c>
       <c r="K135" s="1" t="s">
         <v>37</v>
       </c>
@@ -5425,6 +6223,12 @@
       <c r="H136" s="1">
         <v>1</v>
       </c>
+      <c r="I136" s="1">
+        <v>2497</v>
+      </c>
+      <c r="J136" s="1">
+        <v>1116139</v>
+      </c>
       <c r="K136" s="1">
         <v>26</v>
       </c>
@@ -5459,6 +6263,12 @@
       </c>
       <c r="H137" s="1">
         <v>1</v>
+      </c>
+      <c r="I137" s="1">
+        <v>2497</v>
+      </c>
+      <c r="J137" s="1">
+        <v>1116139</v>
       </c>
       <c r="K137" s="1">
         <v>26</v>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -797,7 +797,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="2">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="2">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="ShopItemData" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="457">
   <si>
     <t>string</t>
   </si>
@@ -251,14 +252,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>纺织店</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>装备</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>纺织品</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -267,24 +260,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>19,38</t>
-  </si>
-  <si>
-    <t>19,39</t>
-  </si>
-  <si>
-    <t>19,40</t>
-  </si>
-  <si>
-    <t>19,41</t>
-  </si>
-  <si>
-    <t>19,42</t>
-  </si>
-  <si>
-    <t>19,43</t>
-  </si>
-  <si>
     <t>魔法商店</t>
   </si>
   <si>
@@ -319,6 +294,1207 @@
   </si>
   <si>
     <t>1000,500|1001,500|1002,500|1003,500|1004,500|1005,500|1006,500|1007,500|1008,500|1009,500|1010,500|1011,500</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>长剑</t>
+  </si>
+  <si>
+    <t>铁枪</t>
+  </si>
+  <si>
+    <t>战斧</t>
+  </si>
+  <si>
+    <t>蛇皮鞭</t>
+  </si>
+  <si>
+    <t>荆棘鞭</t>
+  </si>
+  <si>
+    <t>锁子甲</t>
+  </si>
+  <si>
+    <t>铁铠甲</t>
+  </si>
+  <si>
+    <t>士兵长靴</t>
+  </si>
+  <si>
+    <t>士兵头盔</t>
+  </si>
+  <si>
+    <t>锄头</t>
+  </si>
+  <si>
+    <t>洒水壶</t>
+  </si>
+  <si>
+    <t>斧头</t>
+  </si>
+  <si>
+    <t>镰刀</t>
+  </si>
+  <si>
+    <t>鱼竿</t>
+  </si>
+  <si>
+    <t>铸造配方</t>
+  </si>
+  <si>
+    <t>防具</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁块</t>
+  </si>
+  <si>
+    <t>布衣</t>
+  </si>
+  <si>
+    <t>皮铠</t>
+  </si>
+  <si>
+    <t>布鞋</t>
+  </si>
+  <si>
+    <t>皮鞋</t>
+  </si>
+  <si>
+    <t>草帽</t>
+  </si>
+  <si>
+    <t>法师帽</t>
+  </si>
+  <si>
+    <t>其他</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>缝纫配方</t>
+  </si>
+  <si>
+    <t>皮革</t>
+  </si>
+  <si>
+    <t>毛线</t>
+  </si>
+  <si>
+    <t>布片</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>itemName</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>未知的物品</t>
+  </si>
+  <si>
+    <t>失败的徒手</t>
+  </si>
+  <si>
+    <t>失败的搅拌</t>
+  </si>
+  <si>
+    <t>失败的烘烤</t>
+  </si>
+  <si>
+    <t>失败的蒸煮</t>
+  </si>
+  <si>
+    <t>失败的酿造</t>
+  </si>
+  <si>
+    <t>失败的铸造</t>
+  </si>
+  <si>
+    <t>失败的缝纫</t>
+  </si>
+  <si>
+    <t>失败的绘写</t>
+  </si>
+  <si>
+    <t>传送卷轴</t>
+  </si>
+  <si>
+    <t>鱼饵</t>
+  </si>
+  <si>
+    <t>食物配方</t>
+  </si>
+  <si>
+    <t>酒水配方</t>
+  </si>
+  <si>
+    <t>书写配方</t>
+  </si>
+  <si>
+    <t>牧草</t>
+  </si>
+  <si>
+    <t>木材</t>
+  </si>
+  <si>
+    <t>原木</t>
+  </si>
+  <si>
+    <t>木柴</t>
+  </si>
+  <si>
+    <t>木棒</t>
+  </si>
+  <si>
+    <t>干草</t>
+  </si>
+  <si>
+    <t>纯净水</t>
+  </si>
+  <si>
+    <t>石块</t>
+  </si>
+  <si>
+    <t>龟壳</t>
+  </si>
+  <si>
+    <t>兽皮</t>
+  </si>
+  <si>
+    <t>石英砂</t>
+  </si>
+  <si>
+    <t>草药茶</t>
+  </si>
+  <si>
+    <t>风晶石</t>
+  </si>
+  <si>
+    <t>琥珀</t>
+  </si>
+  <si>
+    <t>狼牙</t>
+  </si>
+  <si>
+    <t>粘土</t>
+  </si>
+  <si>
+    <t>尖刺</t>
+  </si>
+  <si>
+    <t>蛛丝</t>
+  </si>
+  <si>
+    <t>铁矿</t>
+  </si>
+  <si>
+    <t>盐矿</t>
+  </si>
+  <si>
+    <t>肥皂</t>
+  </si>
+  <si>
+    <t>土晶石</t>
+  </si>
+  <si>
+    <t>迷幻菇</t>
+  </si>
+  <si>
+    <t>眼球</t>
+  </si>
+  <si>
+    <t>植物的藤</t>
+  </si>
+  <si>
+    <t>鹿角</t>
+  </si>
+  <si>
+    <t>魔兽皮毛</t>
+  </si>
+  <si>
+    <t>奇美拉之翼</t>
+  </si>
+  <si>
+    <t>电偶瓶</t>
+  </si>
+  <si>
+    <t>海胆</t>
+  </si>
+  <si>
+    <t>珊瑚</t>
+  </si>
+  <si>
+    <t>彩色羽毛</t>
+  </si>
+  <si>
+    <t>火晶石</t>
+  </si>
+  <si>
+    <t>玻璃瓶</t>
+  </si>
+  <si>
+    <t>水晶石</t>
+  </si>
+  <si>
+    <t>珍珠</t>
+  </si>
+  <si>
+    <t>松果</t>
+  </si>
+  <si>
+    <t>神奇泥浆</t>
+  </si>
+  <si>
+    <t>银块</t>
+  </si>
+  <si>
+    <t>蛇皮</t>
+  </si>
+  <si>
+    <t>蜂刺</t>
+  </si>
+  <si>
+    <t>象牙</t>
+  </si>
+  <si>
+    <t>兽角</t>
+  </si>
+  <si>
+    <t>水晶球</t>
+  </si>
+  <si>
+    <t>蝎尾</t>
+  </si>
+  <si>
+    <t>仙人掌</t>
+  </si>
+  <si>
+    <t>脏绷带</t>
+  </si>
+  <si>
+    <t>幽魂</t>
+  </si>
+  <si>
+    <t>金块</t>
+  </si>
+  <si>
+    <t>远古的硬币</t>
+  </si>
+  <si>
+    <t>铁钉</t>
+  </si>
+  <si>
+    <t>遗骨</t>
+  </si>
+  <si>
+    <t>妖精粉</t>
+  </si>
+  <si>
+    <t>雪球</t>
+  </si>
+  <si>
+    <t>毒淤泥</t>
+  </si>
+  <si>
+    <t>亡者之土</t>
+  </si>
+  <si>
+    <t>咒术药水</t>
+  </si>
+  <si>
+    <t>诅咒宝珠</t>
+  </si>
+  <si>
+    <t>人狼之证</t>
+  </si>
+  <si>
+    <t>魔族之血</t>
+  </si>
+  <si>
+    <t>冰晶石</t>
+  </si>
+  <si>
+    <t>冰的结晶</t>
+  </si>
+  <si>
+    <t>石化之眼</t>
+  </si>
+  <si>
+    <t>夜之幕</t>
+  </si>
+  <si>
+    <t>星的眼泪</t>
+  </si>
+  <si>
+    <t>冰牛角</t>
+  </si>
+  <si>
+    <t>寒冰气息</t>
+  </si>
+  <si>
+    <t>寒冰火种</t>
+  </si>
+  <si>
+    <t>幻影水晶</t>
+  </si>
+  <si>
+    <t>雷鸣宝珠</t>
+  </si>
+  <si>
+    <t>彩色的布</t>
+  </si>
+  <si>
+    <t>鳞片</t>
+  </si>
+  <si>
+    <t>刀刃</t>
+  </si>
+  <si>
+    <t>骑士之证</t>
+  </si>
+  <si>
+    <t>马尾</t>
+  </si>
+  <si>
+    <t>粘液</t>
+  </si>
+  <si>
+    <t>贵族徽章</t>
+  </si>
+  <si>
+    <t>武道精华</t>
+  </si>
+  <si>
+    <t>贤者晶石</t>
+  </si>
+  <si>
+    <t>防水皮革</t>
+  </si>
+  <si>
+    <t>羊毛</t>
+  </si>
+  <si>
+    <t>白磷粉末</t>
+  </si>
+  <si>
+    <t>暮光结晶</t>
+  </si>
+  <si>
+    <t>魔力之土</t>
+  </si>
+  <si>
+    <t>迷幻孢子</t>
+  </si>
+  <si>
+    <t>力量果实</t>
+  </si>
+  <si>
+    <t>恶魔花瓣</t>
+  </si>
+  <si>
+    <t>月之光华</t>
+  </si>
+  <si>
+    <t>萤火树汁</t>
+  </si>
+  <si>
+    <t>暗夜之露</t>
+  </si>
+  <si>
+    <t>魅惑药水</t>
+  </si>
+  <si>
+    <t>图腾号角</t>
+  </si>
+  <si>
+    <t>空白卷轴</t>
+  </si>
+  <si>
+    <t>废铁</t>
+  </si>
+  <si>
+    <t>焦炭</t>
+  </si>
+  <si>
+    <t>钢</t>
+  </si>
+  <si>
+    <t>猪粪</t>
+  </si>
+  <si>
+    <t>鸭绒</t>
+  </si>
+  <si>
+    <t>兔子脚</t>
+  </si>
+  <si>
+    <t>芜菁</t>
+  </si>
+  <si>
+    <t>卷心菜</t>
+  </si>
+  <si>
+    <t>葱</t>
+  </si>
+  <si>
+    <t>萝卜</t>
+  </si>
+  <si>
+    <t>紫甘蓝</t>
+  </si>
+  <si>
+    <t>黄瓜</t>
+  </si>
+  <si>
+    <t>西兰花</t>
+  </si>
+  <si>
+    <t>番茄</t>
+  </si>
+  <si>
+    <t>胡萝卜</t>
+  </si>
+  <si>
+    <t>西瓜</t>
+  </si>
+  <si>
+    <t>辣椒</t>
+  </si>
+  <si>
+    <t>奇异果</t>
+  </si>
+  <si>
+    <t>茄子</t>
+  </si>
+  <si>
+    <t>豌豆</t>
+  </si>
+  <si>
+    <t>土豆</t>
+  </si>
+  <si>
+    <t>大蒜</t>
+  </si>
+  <si>
+    <t>芦笋</t>
+  </si>
+  <si>
+    <t>南瓜</t>
+  </si>
+  <si>
+    <t>玉米</t>
+  </si>
+  <si>
+    <t>大麦</t>
+  </si>
+  <si>
+    <t>啤酒花</t>
+  </si>
+  <si>
+    <t>葡萄</t>
+  </si>
+  <si>
+    <t>菠萝</t>
+  </si>
+  <si>
+    <t>咖啡</t>
+  </si>
+  <si>
+    <t>草莓</t>
+  </si>
+  <si>
+    <t>蓝莓</t>
+  </si>
+  <si>
+    <t>红薯</t>
+  </si>
+  <si>
+    <t>甜菜</t>
+  </si>
+  <si>
+    <t>芜菁种子</t>
+  </si>
+  <si>
+    <t>卷心菜种子</t>
+  </si>
+  <si>
+    <t>葱种子</t>
+  </si>
+  <si>
+    <t>萝卜种子</t>
+  </si>
+  <si>
+    <t>紫甘蓝种子</t>
+  </si>
+  <si>
+    <t>黄瓜种子</t>
+  </si>
+  <si>
+    <t>西兰花种子</t>
+  </si>
+  <si>
+    <t>番茄种子</t>
+  </si>
+  <si>
+    <t>胡萝卜种子</t>
+  </si>
+  <si>
+    <t>西瓜种子</t>
+  </si>
+  <si>
+    <t>辣椒种子</t>
+  </si>
+  <si>
+    <t>奇异果种子</t>
+  </si>
+  <si>
+    <t>茄子种子</t>
+  </si>
+  <si>
+    <t>豌豆种子</t>
+  </si>
+  <si>
+    <t>土豆种子</t>
+  </si>
+  <si>
+    <t>大蒜种子</t>
+  </si>
+  <si>
+    <t>芦笋种子</t>
+  </si>
+  <si>
+    <t>南瓜种子</t>
+  </si>
+  <si>
+    <t>玉米种子</t>
+  </si>
+  <si>
+    <t>大麦种子</t>
+  </si>
+  <si>
+    <t>啤酒花种子</t>
+  </si>
+  <si>
+    <t>葡萄种子</t>
+  </si>
+  <si>
+    <t>菠萝种子</t>
+  </si>
+  <si>
+    <t>咖啡种子</t>
+  </si>
+  <si>
+    <t>草莓种子</t>
+  </si>
+  <si>
+    <t>蓝莓种子</t>
+  </si>
+  <si>
+    <t>红薯种子</t>
+  </si>
+  <si>
+    <t>甜菜种子</t>
+  </si>
+  <si>
+    <t>诅咒之剑</t>
+  </si>
+  <si>
+    <t>烈焰之刃</t>
+  </si>
+  <si>
+    <t>大地之剑</t>
+  </si>
+  <si>
+    <t>冰之刃</t>
+  </si>
+  <si>
+    <t>骑士长枪</t>
+  </si>
+  <si>
+    <t>血腥之矛</t>
+  </si>
+  <si>
+    <t>三叉戟</t>
+  </si>
+  <si>
+    <t>毒蜥之牙</t>
+  </si>
+  <si>
+    <t>恶魔之斧</t>
+  </si>
+  <si>
+    <t>女王之鞭</t>
+  </si>
+  <si>
+    <t>蛇牙鞭</t>
+  </si>
+  <si>
+    <t>暴雪斧</t>
+  </si>
+  <si>
+    <t>秘银长剑</t>
+  </si>
+  <si>
+    <t>幻影长枪</t>
+  </si>
+  <si>
+    <t>雷神之鞭</t>
+  </si>
+  <si>
+    <t>死亡之鞭</t>
+  </si>
+  <si>
+    <t>毛皮斗篷</t>
+  </si>
+  <si>
+    <t>红莲之铠</t>
+  </si>
+  <si>
+    <t>铁龟铠</t>
+  </si>
+  <si>
+    <t>华丽背心</t>
+  </si>
+  <si>
+    <t>鳞铠</t>
+  </si>
+  <si>
+    <t>暗之袍</t>
+  </si>
+  <si>
+    <t>疾风背心</t>
+  </si>
+  <si>
+    <t>魔法铠甲</t>
+  </si>
+  <si>
+    <t>钢刃锁甲</t>
+  </si>
+  <si>
+    <t>丝织长袍</t>
+  </si>
+  <si>
+    <t>水之羽衣</t>
+  </si>
+  <si>
+    <t>贵族长裙</t>
+  </si>
+  <si>
+    <t>幸运之衣</t>
+  </si>
+  <si>
+    <t>登山者之靴</t>
+  </si>
+  <si>
+    <t>运动鞋</t>
+  </si>
+  <si>
+    <t>贵族长靴</t>
+  </si>
+  <si>
+    <t>武道鞋</t>
+  </si>
+  <si>
+    <t>骑士护胫</t>
+  </si>
+  <si>
+    <t>贤者之履</t>
+  </si>
+  <si>
+    <t>风神之履</t>
+  </si>
+  <si>
+    <t>踏浪长靴</t>
+  </si>
+  <si>
+    <t>阳光草帽</t>
+  </si>
+  <si>
+    <t>尖角头盔</t>
+  </si>
+  <si>
+    <t>幸运头巾</t>
+  </si>
+  <si>
+    <t>绅士礼帽</t>
+  </si>
+  <si>
+    <t>贵族头巾</t>
+  </si>
+  <si>
+    <t>战争头盔</t>
+  </si>
+  <si>
+    <t>缝纫机</t>
+  </si>
+  <si>
+    <t>锻造炉</t>
+  </si>
+  <si>
+    <t>烘烤炉</t>
+  </si>
+  <si>
+    <t>炖煮锅</t>
+  </si>
+  <si>
+    <t>冷餐台</t>
+  </si>
+  <si>
+    <t>酿造桶</t>
+  </si>
+  <si>
+    <t>绘写台</t>
+  </si>
+  <si>
+    <t>冰箱</t>
+  </si>
+  <si>
+    <t>储物箱(木)</t>
+  </si>
+  <si>
+    <t>储物箱(银)</t>
+  </si>
+  <si>
+    <t>储物箱(金)</t>
+  </si>
+  <si>
+    <t>普通柜台</t>
+  </si>
+  <si>
+    <t>服饰架</t>
+  </si>
+  <si>
+    <t>沙发</t>
+  </si>
+  <si>
+    <t>搅拌器</t>
+  </si>
+  <si>
+    <t>双人床</t>
+  </si>
+  <si>
+    <t>鲫鱼</t>
+  </si>
+  <si>
+    <t>小龙虾</t>
+  </si>
+  <si>
+    <t>鲤鱼</t>
+  </si>
+  <si>
+    <t>鲮鱼</t>
+  </si>
+  <si>
+    <t>河蟹</t>
+  </si>
+  <si>
+    <t>鲶鱼</t>
+  </si>
+  <si>
+    <t>丁鱼</t>
+  </si>
+  <si>
+    <t>锦鲤</t>
+  </si>
+  <si>
+    <t>金线鱼</t>
+  </si>
+  <si>
+    <t>梭鲈</t>
+  </si>
+  <si>
+    <t>兰寿金鱼</t>
+  </si>
+  <si>
+    <t>樱桃鲑鱼</t>
+  </si>
+  <si>
+    <t>虹鳟鱼</t>
+  </si>
+  <si>
+    <t>鲷鱼</t>
+  </si>
+  <si>
+    <t>金鳟鱼</t>
+  </si>
+  <si>
+    <t>霓虹脂鲤</t>
+  </si>
+  <si>
+    <t>桃花鱼</t>
+  </si>
+  <si>
+    <t>鲑鱼</t>
+  </si>
+  <si>
+    <t>孔雀鱼</t>
+  </si>
+  <si>
+    <t>银龙鱼</t>
+  </si>
+  <si>
+    <t>洞穴天使鱼</t>
+  </si>
+  <si>
+    <t>沙丁鱼</t>
+  </si>
+  <si>
+    <t>竹荚鱼</t>
+  </si>
+  <si>
+    <t>海鳗</t>
+  </si>
+  <si>
+    <t>章鱼</t>
+  </si>
+  <si>
+    <t>比目鱼</t>
+  </si>
+  <si>
+    <t>河豚</t>
+  </si>
+  <si>
+    <t>水母</t>
+  </si>
+  <si>
+    <t>条石鲷</t>
+  </si>
+  <si>
+    <t>红鲷鱼</t>
+  </si>
+  <si>
+    <t>蓝蟹</t>
+  </si>
+  <si>
+    <t>鲯鳅鱼</t>
+  </si>
+  <si>
+    <t>龙虾</t>
+  </si>
+  <si>
+    <t>金枪鱼</t>
+  </si>
+  <si>
+    <t>斑马狮子鱼</t>
+  </si>
+  <si>
+    <t>米饭</t>
+  </si>
+  <si>
+    <t>发酵粉</t>
+  </si>
+  <si>
+    <t>盐</t>
+  </si>
+  <si>
+    <t>酸味香料</t>
+  </si>
+  <si>
+    <t>蜂蜜</t>
+  </si>
+  <si>
+    <t>牛奶</t>
+  </si>
+  <si>
+    <t>鸡蛋</t>
+  </si>
+  <si>
+    <t>猪肉</t>
+  </si>
+  <si>
+    <t>面粉</t>
+  </si>
+  <si>
+    <t>咖啡粉</t>
+  </si>
+  <si>
+    <t>海苔</t>
+  </si>
+  <si>
+    <t>黄油</t>
+  </si>
+  <si>
+    <t>腌芜菁</t>
+  </si>
+  <si>
+    <t>蔬菜沙拉</t>
+  </si>
+  <si>
+    <t>三明治</t>
+  </si>
+  <si>
+    <t>腌萝卜</t>
+  </si>
+  <si>
+    <t>拉面</t>
+  </si>
+  <si>
+    <t>蜂蜜蛋糕</t>
+  </si>
+  <si>
+    <t>披萨</t>
+  </si>
+  <si>
+    <t>腌黄瓜</t>
+  </si>
+  <si>
+    <t>烤西兰花</t>
+  </si>
+  <si>
+    <t>水煮蛋</t>
+  </si>
+  <si>
+    <t>烤肉串</t>
+  </si>
+  <si>
+    <t>饭团</t>
+  </si>
+  <si>
+    <t>面包</t>
+  </si>
+  <si>
+    <t>烤海苔</t>
+  </si>
+  <si>
+    <t>烤肉饼</t>
+  </si>
+  <si>
+    <t>汉堡</t>
+  </si>
+  <si>
+    <t>辣蟹堡</t>
+  </si>
+  <si>
+    <t>土豆泥</t>
+  </si>
+  <si>
+    <t>海鲜饭</t>
+  </si>
+  <si>
+    <t>烤玉米</t>
+  </si>
+  <si>
+    <t>蔬菜汁</t>
+  </si>
+  <si>
+    <t>西瓜果汁</t>
+  </si>
+  <si>
+    <t>奇异果汁</t>
+  </si>
+  <si>
+    <t>葡萄汁</t>
+  </si>
+  <si>
+    <t>菠萝汁</t>
+  </si>
+  <si>
+    <t>草莓汁</t>
+  </si>
+  <si>
+    <t>蓝莓汁</t>
+  </si>
+  <si>
+    <t>玉米汁</t>
+  </si>
+  <si>
+    <t>烤蜜薯</t>
+  </si>
+  <si>
+    <t>甜菜汁</t>
+  </si>
+  <si>
+    <t>奶酪</t>
+  </si>
+  <si>
+    <t>烤茄子</t>
+  </si>
+  <si>
+    <t>饺子</t>
+  </si>
+  <si>
+    <t>炖菜</t>
+  </si>
+  <si>
+    <t>烤芦笋</t>
+  </si>
+  <si>
+    <t>红菜汤</t>
+  </si>
+  <si>
+    <t>豌豆汤</t>
+  </si>
+  <si>
+    <t>草莓牛奶</t>
+  </si>
+  <si>
+    <t>莓莓果汁</t>
+  </si>
+  <si>
+    <t>鲑鱼饭团</t>
+  </si>
+  <si>
+    <t>拿铁</t>
+  </si>
+  <si>
+    <t>黑咖啡</t>
+  </si>
+  <si>
+    <t>葡萄酒</t>
+  </si>
+  <si>
+    <t>伏特加</t>
+  </si>
+  <si>
+    <t>啤酒</t>
+  </si>
+  <si>
+    <t>朗姆</t>
+  </si>
+  <si>
+    <t>野蜂拉格</t>
+  </si>
+  <si>
+    <t>双莓白兰地</t>
+  </si>
+  <si>
+    <t>绯红之吻</t>
+  </si>
+  <si>
+    <t>阳光男孩</t>
+  </si>
+  <si>
+    <t>盐烤鲮鱼</t>
+  </si>
+  <si>
+    <t>盐烤丁鱼</t>
+  </si>
+  <si>
+    <t>盐烤虹鳟鱼</t>
+  </si>
+  <si>
+    <t>烤鲷鱼</t>
+  </si>
+  <si>
+    <t>盐烤金鳟鱼</t>
+  </si>
+  <si>
+    <t>盐烤鲑鱼</t>
+  </si>
+  <si>
+    <t>烤沙丁鱼串</t>
+  </si>
+  <si>
+    <t>烤竹荚鱼</t>
+  </si>
+  <si>
+    <t>烤海鳗</t>
+  </si>
+  <si>
+    <t>烤比目鱼</t>
+  </si>
+  <si>
+    <t>烤河豚鱼</t>
+  </si>
+  <si>
+    <t>烤条石鲷</t>
+  </si>
+  <si>
+    <t>烤红鲷鱼</t>
+  </si>
+  <si>
+    <t>烤蓝蟹</t>
+  </si>
+  <si>
+    <t>烤龙虾</t>
+  </si>
+  <si>
+    <t>烤金枪鱼</t>
+  </si>
+  <si>
+    <t>煮蟹肉</t>
+  </si>
+  <si>
+    <t>海鲜浓汤</t>
+  </si>
+  <si>
+    <t>鳗鱼饭</t>
+  </si>
+  <si>
+    <t>鲫鱼蔬菜汤</t>
+  </si>
+  <si>
+    <t>鲮鱼丸</t>
+  </si>
+  <si>
+    <t>鲑鱼刺身</t>
+  </si>
+  <si>
+    <t>章鱼小丸子</t>
+  </si>
+  <si>
+    <t>炖煮条石鲷</t>
+  </si>
+  <si>
+    <t>红鲷刺身</t>
+  </si>
+  <si>
+    <t>河豚刺身</t>
+  </si>
+  <si>
+    <t>螃蟹煲</t>
+  </si>
+  <si>
+    <t>金枪鱼刺身</t>
+  </si>
+  <si>
+    <t>龙虾鱼子酱</t>
+  </si>
+  <si>
+    <t>凉茶</t>
+  </si>
+  <si>
+    <t>回春卷轴</t>
+  </si>
+  <si>
+    <t>振奋卷轴</t>
+  </si>
+  <si>
+    <t>昏睡卷轴</t>
+  </si>
+  <si>
+    <t>感电卷轴</t>
+  </si>
+  <si>
+    <t>冰氛卷轴</t>
+  </si>
+  <si>
+    <t>火氛卷轴</t>
+  </si>
+  <si>
+    <t>沉默卷轴</t>
+  </si>
+  <si>
+    <t>减速卷轴</t>
+  </si>
+  <si>
+    <t>闪避卷轴</t>
+  </si>
+  <si>
+    <t>力量卷轴</t>
+  </si>
+  <si>
+    <t>魅惑卷轴</t>
+  </si>
+  <si>
+    <t>动物产物</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -410,7 +1586,38 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -686,7 +1893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -771,10 +1978,10 @@
         <v>29</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>30</v>
@@ -4027,7 +5234,7 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>40</v>
+        <v>456</v>
       </c>
       <c r="B83" s="1">
         <v>1005</v>
@@ -4320,7 +5527,7 @@
         <v>1006</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D90" s="1">
         <v>3002</v>
@@ -5052,7 +6259,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B108" s="1">
         <v>1008</v>
@@ -5093,7 +6300,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B109" s="1">
         <v>1008</v>
@@ -5123,7 +6330,7 @@
         <v>1019120</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L109" s="1" t="b">
         <v>0</v>
@@ -5134,7 +6341,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B110" s="1">
         <v>1008</v>
@@ -5164,7 +6371,7 @@
         <v>1019120</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L110" s="1" t="b">
         <v>0</v>
@@ -5175,7 +6382,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B111" s="1">
         <v>1008</v>
@@ -5184,7 +6391,7 @@
         <v>45</v>
       </c>
       <c r="D111" s="1">
-        <v>1702</v>
+        <v>1612</v>
       </c>
       <c r="E111" s="1">
         <v>0</v>
@@ -5205,7 +6412,7 @@
         <v>1019120</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="L111" s="1" t="b">
         <v>0</v>
@@ -5216,7 +6423,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B112" s="1">
         <v>1008</v>
@@ -5225,7 +6432,7 @@
         <v>45</v>
       </c>
       <c r="D112" s="1">
-        <v>1654</v>
+        <v>1613</v>
       </c>
       <c r="E112" s="1">
         <v>0</v>
@@ -5246,7 +6453,7 @@
         <v>1019120</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="L112" s="1" t="b">
         <v>0</v>
@@ -5257,16 +6464,16 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B113" s="1">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D113" s="1">
-        <v>1803</v>
+        <v>1652</v>
       </c>
       <c r="E113" s="1">
         <v>0</v>
@@ -5287,7 +6494,7 @@
         <v>1019120</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L113" s="1" t="b">
         <v>0</v>
@@ -5298,16 +6505,16 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B114" s="1">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D114" s="1">
-        <v>22</v>
+        <v>1654</v>
       </c>
       <c r="E114" s="1">
         <v>0</v>
@@ -5328,7 +6535,7 @@
         <v>1019120</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L114" s="1" t="b">
         <v>0</v>
@@ -5339,16 +6546,16 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B115" s="1">
         <v>1009</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D115" s="1">
-        <v>1613</v>
+        <v>1702</v>
       </c>
       <c r="E115" s="1">
         <v>0</v>
@@ -5363,13 +6570,13 @@
         <v>1</v>
       </c>
       <c r="I115" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J115" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K115" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L115" s="1" t="b">
         <v>0</v>
@@ -5380,16 +6587,16 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B116" s="1">
         <v>1009</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D116" s="1">
-        <v>1650</v>
+        <v>1803</v>
       </c>
       <c r="E116" s="1">
         <v>0</v>
@@ -5404,13 +6611,13 @@
         <v>1</v>
       </c>
       <c r="I116" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J116" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K116" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L116" s="1" t="b">
         <v>0</v>
@@ -5421,16 +6628,16 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="B117" s="1">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D117" s="1">
-        <v>1651</v>
+        <v>22</v>
       </c>
       <c r="E117" s="1">
         <v>0</v>
@@ -5445,13 +6652,13 @@
         <v>1</v>
       </c>
       <c r="I117" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J117" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K117" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L117" s="1" t="b">
         <v>0</v>
@@ -5462,16 +6669,16 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="B118" s="1">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D118" s="1">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="E118" s="1">
         <v>0</v>
@@ -5486,13 +6693,13 @@
         <v>1</v>
       </c>
       <c r="I118" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J118" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K118" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L118" s="1" t="b">
         <v>0</v>
@@ -5503,16 +6710,16 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="B119" s="1">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D119" s="1">
-        <v>1701</v>
+        <v>2001</v>
       </c>
       <c r="E119" s="1">
         <v>0</v>
@@ -5527,13 +6734,13 @@
         <v>1</v>
       </c>
       <c r="I119" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J119" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K119" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L119" s="1" t="b">
         <v>0</v>
@@ -5544,16 +6751,16 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="B120" s="1">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D120" s="1">
-        <v>1800</v>
+        <v>2002</v>
       </c>
       <c r="E120" s="1">
         <v>0</v>
@@ -5568,13 +6775,13 @@
         <v>1</v>
       </c>
       <c r="I120" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J120" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K120" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L120" s="1" t="b">
         <v>0</v>
@@ -5585,16 +6792,16 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="B121" s="1">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D121" s="1">
-        <v>23</v>
+        <v>2003</v>
       </c>
       <c r="E121" s="1">
         <v>0</v>
@@ -5609,13 +6816,13 @@
         <v>1</v>
       </c>
       <c r="I121" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J121" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K121" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L121" s="1" t="b">
         <v>0</v>
@@ -5626,16 +6833,16 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B122" s="1">
         <v>1010</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D122" s="1">
-        <v>11</v>
+        <v>298</v>
       </c>
       <c r="E122" s="1">
         <v>0</v>
@@ -5650,13 +6857,13 @@
         <v>1</v>
       </c>
       <c r="I122" s="1">
-        <v>3056</v>
+        <v>1756</v>
       </c>
       <c r="J122" s="1">
-        <v>1019972</v>
+        <v>1019120</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L122" s="1" t="b">
         <v>0</v>
@@ -5667,16 +6874,16 @@
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B123" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D123" s="1">
-        <v>295</v>
+        <v>1650</v>
       </c>
       <c r="E123" s="1">
         <v>0</v>
@@ -5691,13 +6898,13 @@
         <v>1</v>
       </c>
       <c r="I123" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J123" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K123" s="1">
+        <v>41</v>
       </c>
       <c r="L123" s="1" t="b">
         <v>0</v>
@@ -5708,16 +6915,16 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B124" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D124" s="1">
-        <v>24</v>
+        <v>1651</v>
       </c>
       <c r="E124" s="1">
         <v>0</v>
@@ -5732,13 +6939,13 @@
         <v>1</v>
       </c>
       <c r="I124" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J124" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K124" s="1">
+        <v>41</v>
       </c>
       <c r="L124" s="1" t="b">
         <v>0</v>
@@ -5749,16 +6956,16 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B125" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D125" s="1">
-        <v>4000</v>
+        <v>1700</v>
       </c>
       <c r="E125" s="1">
         <v>0</v>
@@ -5770,16 +6977,16 @@
         <v>100</v>
       </c>
       <c r="H125" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I125" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J125" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K125" s="1">
+        <v>41</v>
       </c>
       <c r="L125" s="1" t="b">
         <v>0</v>
@@ -5790,16 +6997,16 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B126" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D126" s="1">
-        <v>4001</v>
+        <v>1701</v>
       </c>
       <c r="E126" s="1">
         <v>0</v>
@@ -5811,16 +7018,16 @@
         <v>100</v>
       </c>
       <c r="H126" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I126" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J126" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K126" s="1">
+        <v>41</v>
       </c>
       <c r="L126" s="1" t="b">
         <v>0</v>
@@ -5831,16 +7038,16 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B127" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D127" s="1">
-        <v>4002</v>
+        <v>1800</v>
       </c>
       <c r="E127" s="1">
         <v>0</v>
@@ -5852,16 +7059,16 @@
         <v>100</v>
       </c>
       <c r="H127" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I127" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J127" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K127" s="1">
+        <v>41</v>
       </c>
       <c r="L127" s="1" t="b">
         <v>0</v>
@@ -5872,16 +7079,16 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B128" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D128" s="1">
-        <v>4003</v>
+        <v>1802</v>
       </c>
       <c r="E128" s="1">
         <v>0</v>
@@ -5893,16 +7100,16 @@
         <v>100</v>
       </c>
       <c r="H128" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I128" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J128" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K128" s="1">
+        <v>41</v>
       </c>
       <c r="L128" s="1" t="b">
         <v>0</v>
@@ -5913,16 +7120,16 @@
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B129" s="1">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D129" s="1">
-        <v>4004</v>
+        <v>23</v>
       </c>
       <c r="E129" s="1">
         <v>0</v>
@@ -5934,16 +7141,16 @@
         <v>100</v>
       </c>
       <c r="H129" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I129" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J129" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K129" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K129" s="1">
+        <v>41</v>
       </c>
       <c r="L129" s="1" t="b">
         <v>0</v>
@@ -5954,16 +7161,16 @@
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B130" s="1">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D130" s="1">
-        <v>4005</v>
+        <v>271</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -5975,16 +7182,16 @@
         <v>100</v>
       </c>
       <c r="H130" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I130" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J130" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K130" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K130" s="1">
+        <v>41</v>
       </c>
       <c r="L130" s="1" t="b">
         <v>0</v>
@@ -5995,16 +7202,16 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B131" s="1">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D131" s="1">
-        <v>4006</v>
+        <v>277</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -6016,16 +7223,16 @@
         <v>100</v>
       </c>
       <c r="H131" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I131" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J131" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K131" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K131" s="1">
+        <v>41</v>
       </c>
       <c r="L131" s="1" t="b">
         <v>0</v>
@@ -6036,16 +7243,16 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B132" s="1">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D132" s="1">
-        <v>4007</v>
+        <v>204</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -6057,16 +7264,16 @@
         <v>100</v>
       </c>
       <c r="H132" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I132" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J132" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K132" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K132" s="1">
+        <v>41</v>
       </c>
       <c r="L132" s="1" t="b">
         <v>0</v>
@@ -6077,16 +7284,16 @@
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B133" s="1">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D133" s="1">
-        <v>4008</v>
+        <v>11</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -6098,7 +7305,7 @@
         <v>100</v>
       </c>
       <c r="H133" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I133" s="1">
         <v>3056</v>
@@ -6118,16 +7325,16 @@
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B134" s="1">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D134" s="1">
-        <v>4009</v>
+        <v>295</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -6139,7 +7346,7 @@
         <v>100</v>
       </c>
       <c r="H134" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I134" s="1">
         <v>3056</v>
@@ -6159,16 +7366,16 @@
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B135" s="1">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D135" s="1">
-        <v>4010</v>
+        <v>24</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
@@ -6200,16 +7407,16 @@
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B136" s="1">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D136" s="1">
-        <v>12</v>
+        <v>4000</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
@@ -6221,16 +7428,16 @@
         <v>100</v>
       </c>
       <c r="H136" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I136" s="1">
-        <v>2497</v>
+        <v>3056</v>
       </c>
       <c r="J136" s="1">
-        <v>1116139</v>
-      </c>
-      <c r="K136" s="1">
-        <v>26</v>
+        <v>1019972</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L136" s="1" t="b">
         <v>0</v>
@@ -6241,16 +7448,16 @@
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B137" s="1">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D137" s="1">
-        <v>2004</v>
+        <v>4001</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -6262,21 +7469,472 @@
         <v>100</v>
       </c>
       <c r="H137" s="1">
+        <v>2</v>
+      </c>
+      <c r="I137" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J137" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L137" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B138" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D138" s="1">
+        <v>4002</v>
+      </c>
+      <c r="E138" s="1">
+        <v>0</v>
+      </c>
+      <c r="F138" s="1">
+        <v>0</v>
+      </c>
+      <c r="G138" s="1">
+        <v>100</v>
+      </c>
+      <c r="H138" s="1">
+        <v>3</v>
+      </c>
+      <c r="I138" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J138" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L138" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B139" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D139" s="1">
+        <v>4003</v>
+      </c>
+      <c r="E139" s="1">
+        <v>0</v>
+      </c>
+      <c r="F139" s="1">
+        <v>0</v>
+      </c>
+      <c r="G139" s="1">
+        <v>100</v>
+      </c>
+      <c r="H139" s="1">
+        <v>3</v>
+      </c>
+      <c r="I139" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J139" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L139" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M139" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B140" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D140" s="1">
+        <v>4004</v>
+      </c>
+      <c r="E140" s="1">
+        <v>0</v>
+      </c>
+      <c r="F140" s="1">
+        <v>0</v>
+      </c>
+      <c r="G140" s="1">
+        <v>100</v>
+      </c>
+      <c r="H140" s="1">
+        <v>3</v>
+      </c>
+      <c r="I140" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J140" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L140" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B141" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D141" s="1">
+        <v>4005</v>
+      </c>
+      <c r="E141" s="1">
+        <v>0</v>
+      </c>
+      <c r="F141" s="1">
+        <v>0</v>
+      </c>
+      <c r="G141" s="1">
+        <v>100</v>
+      </c>
+      <c r="H141" s="1">
+        <v>3</v>
+      </c>
+      <c r="I141" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J141" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L141" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B142" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D142" s="1">
+        <v>4006</v>
+      </c>
+      <c r="E142" s="1">
+        <v>0</v>
+      </c>
+      <c r="F142" s="1">
+        <v>0</v>
+      </c>
+      <c r="G142" s="1">
+        <v>100</v>
+      </c>
+      <c r="H142" s="1">
+        <v>3</v>
+      </c>
+      <c r="I142" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J142" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L142" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B143" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D143" s="1">
+        <v>4007</v>
+      </c>
+      <c r="E143" s="1">
+        <v>0</v>
+      </c>
+      <c r="F143" s="1">
+        <v>0</v>
+      </c>
+      <c r="G143" s="1">
+        <v>100</v>
+      </c>
+      <c r="H143" s="1">
+        <v>4</v>
+      </c>
+      <c r="I143" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J143" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L143" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B144" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D144" s="1">
+        <v>4008</v>
+      </c>
+      <c r="E144" s="1">
+        <v>0</v>
+      </c>
+      <c r="F144" s="1">
+        <v>0</v>
+      </c>
+      <c r="G144" s="1">
+        <v>100</v>
+      </c>
+      <c r="H144" s="1">
+        <v>4</v>
+      </c>
+      <c r="I144" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J144" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K144" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L144" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B145" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D145" s="1">
+        <v>4009</v>
+      </c>
+      <c r="E145" s="1">
+        <v>0</v>
+      </c>
+      <c r="F145" s="1">
+        <v>0</v>
+      </c>
+      <c r="G145" s="1">
+        <v>100</v>
+      </c>
+      <c r="H145" s="1">
+        <v>4</v>
+      </c>
+      <c r="I145" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J145" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L145" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B146" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D146" s="1">
+        <v>4010</v>
+      </c>
+      <c r="E146" s="1">
+        <v>0</v>
+      </c>
+      <c r="F146" s="1">
+        <v>0</v>
+      </c>
+      <c r="G146" s="1">
+        <v>100</v>
+      </c>
+      <c r="H146" s="1">
         <v>1</v>
       </c>
-      <c r="I137" s="1">
+      <c r="I146" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J146" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L146" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M146" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B147" s="1">
+        <v>1014</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D147" s="1">
+        <v>12</v>
+      </c>
+      <c r="E147" s="1">
+        <v>0</v>
+      </c>
+      <c r="F147" s="1">
+        <v>0</v>
+      </c>
+      <c r="G147" s="1">
+        <v>100</v>
+      </c>
+      <c r="H147" s="1">
+        <v>1</v>
+      </c>
+      <c r="I147" s="1">
         <v>2497</v>
       </c>
-      <c r="J137" s="1">
+      <c r="J147" s="1">
         <v>1116139</v>
       </c>
-      <c r="K137" s="1">
+      <c r="K147" s="1">
         <v>26</v>
       </c>
-      <c r="L137" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M137" s="1">
+      <c r="L147" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B148" s="1">
+        <v>1014</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D148" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E148" s="1">
+        <v>0</v>
+      </c>
+      <c r="F148" s="1">
+        <v>0</v>
+      </c>
+      <c r="G148" s="1">
+        <v>100</v>
+      </c>
+      <c r="H148" s="1">
+        <v>1</v>
+      </c>
+      <c r="I148" s="1">
+        <v>2497</v>
+      </c>
+      <c r="J148" s="1">
+        <v>1116139</v>
+      </c>
+      <c r="K148" s="1">
+        <v>26</v>
+      </c>
+      <c r="L148" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M148" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6290,6 +7948,3169 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:B395"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B49">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>135</v>
+      </c>
+      <c r="B52">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>136</v>
+      </c>
+      <c r="B53">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>137</v>
+      </c>
+      <c r="B54">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>138</v>
+      </c>
+      <c r="B55">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>143</v>
+      </c>
+      <c r="B60">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>144</v>
+      </c>
+      <c r="B61">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>145</v>
+      </c>
+      <c r="B62">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>146</v>
+      </c>
+      <c r="B63">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>147</v>
+      </c>
+      <c r="B64">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>150</v>
+      </c>
+      <c r="B67">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>151</v>
+      </c>
+      <c r="B68">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>153</v>
+      </c>
+      <c r="B70">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+      <c r="B71">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>155</v>
+      </c>
+      <c r="B72">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>156</v>
+      </c>
+      <c r="B73">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>157</v>
+      </c>
+      <c r="B74">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>158</v>
+      </c>
+      <c r="B75">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>160</v>
+      </c>
+      <c r="B77">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>161</v>
+      </c>
+      <c r="B78">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>162</v>
+      </c>
+      <c r="B79">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>163</v>
+      </c>
+      <c r="B80">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>164</v>
+      </c>
+      <c r="B81">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>165</v>
+      </c>
+      <c r="B82">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>166</v>
+      </c>
+      <c r="B83">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>167</v>
+      </c>
+      <c r="B84">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>169</v>
+      </c>
+      <c r="B86">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>170</v>
+      </c>
+      <c r="B87">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>171</v>
+      </c>
+      <c r="B88">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>172</v>
+      </c>
+      <c r="B89">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>173</v>
+      </c>
+      <c r="B90">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>84</v>
+      </c>
+      <c r="B91">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>174</v>
+      </c>
+      <c r="B92">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>175</v>
+      </c>
+      <c r="B93">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>176</v>
+      </c>
+      <c r="B94">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>177</v>
+      </c>
+      <c r="B95">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>178</v>
+      </c>
+      <c r="B96">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>85</v>
+      </c>
+      <c r="B97">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>179</v>
+      </c>
+      <c r="B98">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>180</v>
+      </c>
+      <c r="B99">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>181</v>
+      </c>
+      <c r="B100">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>182</v>
+      </c>
+      <c r="B101">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>183</v>
+      </c>
+      <c r="B102">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>184</v>
+      </c>
+      <c r="B103">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>185</v>
+      </c>
+      <c r="B104">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>186</v>
+      </c>
+      <c r="B105">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>187</v>
+      </c>
+      <c r="B106">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>188</v>
+      </c>
+      <c r="B107">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>189</v>
+      </c>
+      <c r="B108">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>190</v>
+      </c>
+      <c r="B109">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>191</v>
+      </c>
+      <c r="B110">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>192</v>
+      </c>
+      <c r="B111">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>193</v>
+      </c>
+      <c r="B112">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>194</v>
+      </c>
+      <c r="B113">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>195</v>
+      </c>
+      <c r="B114">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>196</v>
+      </c>
+      <c r="B115">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>197</v>
+      </c>
+      <c r="B116">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>198</v>
+      </c>
+      <c r="B117">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>75</v>
+      </c>
+      <c r="B118">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>199</v>
+      </c>
+      <c r="B119">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>200</v>
+      </c>
+      <c r="B120">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>201</v>
+      </c>
+      <c r="B121">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>202</v>
+      </c>
+      <c r="B122">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>203</v>
+      </c>
+      <c r="B123">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>204</v>
+      </c>
+      <c r="B124">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>205</v>
+      </c>
+      <c r="B125">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>206</v>
+      </c>
+      <c r="B126">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>207</v>
+      </c>
+      <c r="B127">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>208</v>
+      </c>
+      <c r="B128">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>209</v>
+      </c>
+      <c r="B129">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>210</v>
+      </c>
+      <c r="B130">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>211</v>
+      </c>
+      <c r="B131">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>212</v>
+      </c>
+      <c r="B132">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>213</v>
+      </c>
+      <c r="B133">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>214</v>
+      </c>
+      <c r="B134">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>215</v>
+      </c>
+      <c r="B135">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>216</v>
+      </c>
+      <c r="B136">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>217</v>
+      </c>
+      <c r="B137">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>218</v>
+      </c>
+      <c r="B138">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>219</v>
+      </c>
+      <c r="B139">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>220</v>
+      </c>
+      <c r="B140">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>221</v>
+      </c>
+      <c r="B141">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>222</v>
+      </c>
+      <c r="B142">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>223</v>
+      </c>
+      <c r="B143">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>224</v>
+      </c>
+      <c r="B144">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>225</v>
+      </c>
+      <c r="B145">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>226</v>
+      </c>
+      <c r="B146">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>227</v>
+      </c>
+      <c r="B147">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>228</v>
+      </c>
+      <c r="B148">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>229</v>
+      </c>
+      <c r="B149">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>230</v>
+      </c>
+      <c r="B150">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>231</v>
+      </c>
+      <c r="B151">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>232</v>
+      </c>
+      <c r="B152">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>233</v>
+      </c>
+      <c r="B153">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>234</v>
+      </c>
+      <c r="B154">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>235</v>
+      </c>
+      <c r="B155">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>236</v>
+      </c>
+      <c r="B156">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>237</v>
+      </c>
+      <c r="B157">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>238</v>
+      </c>
+      <c r="B158">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>239</v>
+      </c>
+      <c r="B159">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>240</v>
+      </c>
+      <c r="B160">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>241</v>
+      </c>
+      <c r="B161">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>242</v>
+      </c>
+      <c r="B162">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>243</v>
+      </c>
+      <c r="B163">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>244</v>
+      </c>
+      <c r="B164">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>245</v>
+      </c>
+      <c r="B165">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>246</v>
+      </c>
+      <c r="B166">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>247</v>
+      </c>
+      <c r="B167">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>248</v>
+      </c>
+      <c r="B168">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>249</v>
+      </c>
+      <c r="B169">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>250</v>
+      </c>
+      <c r="B170">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>251</v>
+      </c>
+      <c r="B171">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>252</v>
+      </c>
+      <c r="B172">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>253</v>
+      </c>
+      <c r="B173">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>254</v>
+      </c>
+      <c r="B174">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>255</v>
+      </c>
+      <c r="B175">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>256</v>
+      </c>
+      <c r="B176">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>257</v>
+      </c>
+      <c r="B177">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>258</v>
+      </c>
+      <c r="B178">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>59</v>
+      </c>
+      <c r="B179">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>259</v>
+      </c>
+      <c r="B180">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>260</v>
+      </c>
+      <c r="B181">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>261</v>
+      </c>
+      <c r="B182">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>262</v>
+      </c>
+      <c r="B183">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>60</v>
+      </c>
+      <c r="B184">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>263</v>
+      </c>
+      <c r="B185">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>264</v>
+      </c>
+      <c r="B186">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>265</v>
+      </c>
+      <c r="B187">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>61</v>
+      </c>
+      <c r="B188">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>266</v>
+      </c>
+      <c r="B189">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>267</v>
+      </c>
+      <c r="B190">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>62</v>
+      </c>
+      <c r="B191">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>63</v>
+      </c>
+      <c r="B192">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>268</v>
+      </c>
+      <c r="B193">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>269</v>
+      </c>
+      <c r="B194">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>270</v>
+      </c>
+      <c r="B195">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>271</v>
+      </c>
+      <c r="B196">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>272</v>
+      </c>
+      <c r="B197">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>273</v>
+      </c>
+      <c r="B198">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>274</v>
+      </c>
+      <c r="B199">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>76</v>
+      </c>
+      <c r="B200">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>77</v>
+      </c>
+      <c r="B201">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>64</v>
+      </c>
+      <c r="B202">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>275</v>
+      </c>
+      <c r="B203">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>65</v>
+      </c>
+      <c r="B204">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>276</v>
+      </c>
+      <c r="B205">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>277</v>
+      </c>
+      <c r="B206">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>278</v>
+      </c>
+      <c r="B207">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>279</v>
+      </c>
+      <c r="B208">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>280</v>
+      </c>
+      <c r="B209">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>281</v>
+      </c>
+      <c r="B210">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>282</v>
+      </c>
+      <c r="B211">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>283</v>
+      </c>
+      <c r="B212">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>284</v>
+      </c>
+      <c r="B213">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>285</v>
+      </c>
+      <c r="B214">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>286</v>
+      </c>
+      <c r="B215">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>287</v>
+      </c>
+      <c r="B216">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>78</v>
+      </c>
+      <c r="B217">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>79</v>
+      </c>
+      <c r="B218">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>66</v>
+      </c>
+      <c r="B219">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>288</v>
+      </c>
+      <c r="B220">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>289</v>
+      </c>
+      <c r="B221">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>290</v>
+      </c>
+      <c r="B222">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>291</v>
+      </c>
+      <c r="B223">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>292</v>
+      </c>
+      <c r="B224">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>293</v>
+      </c>
+      <c r="B225">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>294</v>
+      </c>
+      <c r="B226">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>295</v>
+      </c>
+      <c r="B227">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>80</v>
+      </c>
+      <c r="B228">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>296</v>
+      </c>
+      <c r="B229">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>81</v>
+      </c>
+      <c r="B230">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>67</v>
+      </c>
+      <c r="B231">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>297</v>
+      </c>
+      <c r="B232">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>298</v>
+      </c>
+      <c r="B233">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>299</v>
+      </c>
+      <c r="B234">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>300</v>
+      </c>
+      <c r="B235">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>301</v>
+      </c>
+      <c r="B236">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>68</v>
+      </c>
+      <c r="B237">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>69</v>
+      </c>
+      <c r="B238">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>70</v>
+      </c>
+      <c r="B239">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>71</v>
+      </c>
+      <c r="B240">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>72</v>
+      </c>
+      <c r="B241">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>302</v>
+      </c>
+      <c r="B242">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>303</v>
+      </c>
+      <c r="B243">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>304</v>
+      </c>
+      <c r="B244">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>305</v>
+      </c>
+      <c r="B245">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>306</v>
+      </c>
+      <c r="B246">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>307</v>
+      </c>
+      <c r="B247">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>308</v>
+      </c>
+      <c r="B248">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>309</v>
+      </c>
+      <c r="B249">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>310</v>
+      </c>
+      <c r="B250">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>311</v>
+      </c>
+      <c r="B251">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>312</v>
+      </c>
+      <c r="B252">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>313</v>
+      </c>
+      <c r="B253">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>314</v>
+      </c>
+      <c r="B254">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>315</v>
+      </c>
+      <c r="B255">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>316</v>
+      </c>
+      <c r="B256">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>317</v>
+      </c>
+      <c r="B257">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>318</v>
+      </c>
+      <c r="B258">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>319</v>
+      </c>
+      <c r="B259">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>320</v>
+      </c>
+      <c r="B260">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>321</v>
+      </c>
+      <c r="B261">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>322</v>
+      </c>
+      <c r="B262">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>323</v>
+      </c>
+      <c r="B263">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>324</v>
+      </c>
+      <c r="B264">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>325</v>
+      </c>
+      <c r="B265">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>326</v>
+      </c>
+      <c r="B266">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>327</v>
+      </c>
+      <c r="B267">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>328</v>
+      </c>
+      <c r="B268">
+        <v>4013</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>329</v>
+      </c>
+      <c r="B269">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>330</v>
+      </c>
+      <c r="B270">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>331</v>
+      </c>
+      <c r="B271">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>332</v>
+      </c>
+      <c r="B272">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>333</v>
+      </c>
+      <c r="B273">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>334</v>
+      </c>
+      <c r="B274">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>335</v>
+      </c>
+      <c r="B275">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>336</v>
+      </c>
+      <c r="B276">
+        <v>4022</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>337</v>
+      </c>
+      <c r="B277">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>338</v>
+      </c>
+      <c r="B278">
+        <v>4024</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>339</v>
+      </c>
+      <c r="B279">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>340</v>
+      </c>
+      <c r="B280">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>341</v>
+      </c>
+      <c r="B281">
+        <v>4103</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>342</v>
+      </c>
+      <c r="B282">
+        <v>4105</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>343</v>
+      </c>
+      <c r="B283">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>344</v>
+      </c>
+      <c r="B284">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>345</v>
+      </c>
+      <c r="B285">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>346</v>
+      </c>
+      <c r="B286">
+        <v>4111</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>347</v>
+      </c>
+      <c r="B287">
+        <v>4112</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>348</v>
+      </c>
+      <c r="B288">
+        <v>4113</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>349</v>
+      </c>
+      <c r="B289">
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>350</v>
+      </c>
+      <c r="B290">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>351</v>
+      </c>
+      <c r="B291">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>352</v>
+      </c>
+      <c r="B292">
+        <v>4117</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>353</v>
+      </c>
+      <c r="B293">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>354</v>
+      </c>
+      <c r="B294">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>355</v>
+      </c>
+      <c r="B295">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>356</v>
+      </c>
+      <c r="B296">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>357</v>
+      </c>
+      <c r="B297">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>358</v>
+      </c>
+      <c r="B298">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>359</v>
+      </c>
+      <c r="B299">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>360</v>
+      </c>
+      <c r="B300">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>361</v>
+      </c>
+      <c r="B301">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>362</v>
+      </c>
+      <c r="B302">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>363</v>
+      </c>
+      <c r="B303">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>364</v>
+      </c>
+      <c r="B304">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>365</v>
+      </c>
+      <c r="B305">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>366</v>
+      </c>
+      <c r="B306">
+        <v>3101</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307" t="s">
+        <v>367</v>
+      </c>
+      <c r="B307">
+        <v>3102</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308" t="s">
+        <v>368</v>
+      </c>
+      <c r="B308">
+        <v>3103</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309" t="s">
+        <v>369</v>
+      </c>
+      <c r="B309">
+        <v>3104</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310" t="s">
+        <v>370</v>
+      </c>
+      <c r="B310">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311" t="s">
+        <v>371</v>
+      </c>
+      <c r="B311">
+        <v>3106</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A312" t="s">
+        <v>372</v>
+      </c>
+      <c r="B312">
+        <v>3107</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A313" t="s">
+        <v>373</v>
+      </c>
+      <c r="B313">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314" t="s">
+        <v>374</v>
+      </c>
+      <c r="B314">
+        <v>3109</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315" t="s">
+        <v>375</v>
+      </c>
+      <c r="B315">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316" t="s">
+        <v>376</v>
+      </c>
+      <c r="B316">
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317" t="s">
+        <v>377</v>
+      </c>
+      <c r="B317">
+        <v>3112</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318" t="s">
+        <v>378</v>
+      </c>
+      <c r="B318">
+        <v>3113</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319" t="s">
+        <v>379</v>
+      </c>
+      <c r="B319">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320" t="s">
+        <v>380</v>
+      </c>
+      <c r="B320">
+        <v>3115</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A321" t="s">
+        <v>381</v>
+      </c>
+      <c r="B321">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A322" t="s">
+        <v>382</v>
+      </c>
+      <c r="B322">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A323" t="s">
+        <v>383</v>
+      </c>
+      <c r="B323">
+        <v>3118</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A324" t="s">
+        <v>384</v>
+      </c>
+      <c r="B324">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A325" t="s">
+        <v>385</v>
+      </c>
+      <c r="B325">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A326" t="s">
+        <v>386</v>
+      </c>
+      <c r="B326">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A327" t="s">
+        <v>387</v>
+      </c>
+      <c r="B327">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A328" t="s">
+        <v>388</v>
+      </c>
+      <c r="B328">
+        <v>3123</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A329" t="s">
+        <v>389</v>
+      </c>
+      <c r="B329">
+        <v>3124</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A330" t="s">
+        <v>390</v>
+      </c>
+      <c r="B330">
+        <v>3125</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A331" t="s">
+        <v>391</v>
+      </c>
+      <c r="B331">
+        <v>3126</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A332" t="s">
+        <v>392</v>
+      </c>
+      <c r="B332">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A333" t="s">
+        <v>393</v>
+      </c>
+      <c r="B333">
+        <v>3128</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A334" t="s">
+        <v>394</v>
+      </c>
+      <c r="B334">
+        <v>3129</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A335" t="s">
+        <v>395</v>
+      </c>
+      <c r="B335">
+        <v>3130</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A336" t="s">
+        <v>396</v>
+      </c>
+      <c r="B336">
+        <v>3131</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A337" t="s">
+        <v>397</v>
+      </c>
+      <c r="B337">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A338" t="s">
+        <v>398</v>
+      </c>
+      <c r="B338">
+        <v>3133</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A339" t="s">
+        <v>399</v>
+      </c>
+      <c r="B339">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A340" t="s">
+        <v>400</v>
+      </c>
+      <c r="B340">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A341" t="s">
+        <v>401</v>
+      </c>
+      <c r="B341">
+        <v>3136</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A342" t="s">
+        <v>402</v>
+      </c>
+      <c r="B342">
+        <v>3137</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A343" t="s">
+        <v>403</v>
+      </c>
+      <c r="B343">
+        <v>3138</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A344" t="s">
+        <v>404</v>
+      </c>
+      <c r="B344">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A345" t="s">
+        <v>405</v>
+      </c>
+      <c r="B345">
+        <v>3140</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A346" t="s">
+        <v>406</v>
+      </c>
+      <c r="B346">
+        <v>3141</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A347" t="s">
+        <v>407</v>
+      </c>
+      <c r="B347">
+        <v>3142</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A348" t="s">
+        <v>408</v>
+      </c>
+      <c r="B348">
+        <v>3143</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A349" t="s">
+        <v>409</v>
+      </c>
+      <c r="B349">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A350" t="s">
+        <v>410</v>
+      </c>
+      <c r="B350">
+        <v>3145</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A351" t="s">
+        <v>411</v>
+      </c>
+      <c r="B351">
+        <v>3146</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A352" t="s">
+        <v>412</v>
+      </c>
+      <c r="B352">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A353" t="s">
+        <v>413</v>
+      </c>
+      <c r="B353">
+        <v>3148</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A354" t="s">
+        <v>414</v>
+      </c>
+      <c r="B354">
+        <v>3149</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A355" t="s">
+        <v>415</v>
+      </c>
+      <c r="B355">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A356" t="s">
+        <v>416</v>
+      </c>
+      <c r="B356">
+        <v>3151</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A357" t="s">
+        <v>417</v>
+      </c>
+      <c r="B357">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A358" t="s">
+        <v>418</v>
+      </c>
+      <c r="B358">
+        <v>3153</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A359" t="s">
+        <v>419</v>
+      </c>
+      <c r="B359">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A360" t="s">
+        <v>420</v>
+      </c>
+      <c r="B360">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A361" t="s">
+        <v>421</v>
+      </c>
+      <c r="B361">
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A362" t="s">
+        <v>422</v>
+      </c>
+      <c r="B362">
+        <v>3157</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A363" t="s">
+        <v>423</v>
+      </c>
+      <c r="B363">
+        <v>3158</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A364" t="s">
+        <v>424</v>
+      </c>
+      <c r="B364">
+        <v>3159</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A365" t="s">
+        <v>425</v>
+      </c>
+      <c r="B365">
+        <v>3160</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A366" t="s">
+        <v>426</v>
+      </c>
+      <c r="B366">
+        <v>3161</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A367" t="s">
+        <v>427</v>
+      </c>
+      <c r="B367">
+        <v>3162</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A368" t="s">
+        <v>428</v>
+      </c>
+      <c r="B368">
+        <v>3163</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A369" t="s">
+        <v>429</v>
+      </c>
+      <c r="B369">
+        <v>3164</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A370" t="s">
+        <v>430</v>
+      </c>
+      <c r="B370">
+        <v>3165</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A371" t="s">
+        <v>431</v>
+      </c>
+      <c r="B371">
+        <v>3166</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A372" t="s">
+        <v>432</v>
+      </c>
+      <c r="B372">
+        <v>3167</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A373" t="s">
+        <v>433</v>
+      </c>
+      <c r="B373">
+        <v>3168</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A374" t="s">
+        <v>434</v>
+      </c>
+      <c r="B374">
+        <v>3169</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A375" t="s">
+        <v>435</v>
+      </c>
+      <c r="B375">
+        <v>3170</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A376" t="s">
+        <v>436</v>
+      </c>
+      <c r="B376">
+        <v>3171</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A377" t="s">
+        <v>437</v>
+      </c>
+      <c r="B377">
+        <v>3172</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A378" t="s">
+        <v>438</v>
+      </c>
+      <c r="B378">
+        <v>3173</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A379" t="s">
+        <v>439</v>
+      </c>
+      <c r="B379">
+        <v>3174</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A380" t="s">
+        <v>440</v>
+      </c>
+      <c r="B380">
+        <v>3175</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A381" t="s">
+        <v>441</v>
+      </c>
+      <c r="B381">
+        <v>3176</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A382" t="s">
+        <v>442</v>
+      </c>
+      <c r="B382">
+        <v>3177</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A383" t="s">
+        <v>443</v>
+      </c>
+      <c r="B383">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A384" t="s">
+        <v>444</v>
+      </c>
+      <c r="B384">
+        <v>3179</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A385" t="s">
+        <v>445</v>
+      </c>
+      <c r="B385">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A386" t="s">
+        <v>446</v>
+      </c>
+      <c r="B386">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A387" t="s">
+        <v>447</v>
+      </c>
+      <c r="B387">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A388" t="s">
+        <v>448</v>
+      </c>
+      <c r="B388">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A389" t="s">
+        <v>449</v>
+      </c>
+      <c r="B389">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A390" t="s">
+        <v>450</v>
+      </c>
+      <c r="B390">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A391" t="s">
+        <v>451</v>
+      </c>
+      <c r="B391">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A392" t="s">
+        <v>452</v>
+      </c>
+      <c r="B392">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A393" t="s">
+        <v>453</v>
+      </c>
+      <c r="B393">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A394" t="s">
+        <v>454</v>
+      </c>
+      <c r="B394">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A395" t="s">
+        <v>455</v>
+      </c>
+      <c r="B395">
+        <v>4010</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:O48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -6316,7 +11137,7 @@
         <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N2" t="s">
         <v>26</v>
@@ -6339,15 +11160,15 @@
         <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="K24" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.2">
       <c r="D26" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="3:7" x14ac:dyDescent="0.2">

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="457">
   <si>
     <t>string</t>
   </si>
@@ -1586,38 +1586,7 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1893,7 +1862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M148"/>
+  <dimension ref="A1:M156"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -4873,7 +4842,7 @@
       <c r="C74" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74" s="5">
         <v>2200</v>
       </c>
       <c r="E74" s="1">
@@ -4914,7 +4883,7 @@
       <c r="C75" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75" s="5">
         <v>2201</v>
       </c>
       <c r="E75" s="1">
@@ -4947,21 +4916,21 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B76" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D76" s="1">
-        <v>3000</v>
+        <v>14</v>
+      </c>
+      <c r="D76" s="5">
+        <v>2202</v>
       </c>
       <c r="E76" s="1">
-        <v>1</v>
-      </c>
-      <c r="F76" s="1">
+        <v>2</v>
+      </c>
+      <c r="F76" s="2">
         <v>0</v>
       </c>
       <c r="G76" s="1">
@@ -4971,16 +4940,16 @@
         <v>1</v>
       </c>
       <c r="I76" s="1">
-        <v>900</v>
+        <v>1014</v>
       </c>
       <c r="J76" s="1">
-        <v>1079546</v>
-      </c>
-      <c r="K76" t="s">
-        <v>34</v>
+        <v>1088635</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L76" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="1">
         <v>0</v>
@@ -4988,40 +4957,40 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B77" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D77" s="1">
-        <v>3002</v>
+        <v>14</v>
+      </c>
+      <c r="D77" s="5">
+        <v>2203</v>
       </c>
       <c r="E77" s="1">
-        <v>1</v>
-      </c>
-      <c r="F77" s="1">
+        <v>2</v>
+      </c>
+      <c r="F77" s="2">
         <v>0</v>
       </c>
       <c r="G77" s="1">
         <v>100</v>
       </c>
       <c r="H77" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77" s="1">
-        <v>900</v>
+        <v>1014</v>
       </c>
       <c r="J77" s="1">
-        <v>1079546</v>
-      </c>
-      <c r="K77" t="s">
-        <v>34</v>
+        <v>1088635</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L77" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="1">
         <v>0</v>
@@ -5029,40 +4998,40 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B78" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D78" s="1">
-        <v>3004</v>
+        <v>14</v>
+      </c>
+      <c r="D78" s="5">
+        <v>2204</v>
       </c>
       <c r="E78" s="1">
-        <v>1</v>
-      </c>
-      <c r="F78" s="1">
+        <v>2</v>
+      </c>
+      <c r="F78" s="2">
         <v>0</v>
       </c>
       <c r="G78" s="1">
         <v>100</v>
       </c>
       <c r="H78" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I78" s="1">
-        <v>900</v>
+        <v>1014</v>
       </c>
       <c r="J78" s="1">
-        <v>1079546</v>
-      </c>
-      <c r="K78" t="s">
-        <v>34</v>
+        <v>1088635</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L78" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="1">
         <v>0</v>
@@ -5070,40 +5039,40 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B79" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D79" s="1">
-        <v>3006</v>
+        <v>14</v>
+      </c>
+      <c r="D79" s="5">
+        <v>2205</v>
       </c>
       <c r="E79" s="1">
-        <v>1</v>
-      </c>
-      <c r="F79" s="1">
+        <v>2</v>
+      </c>
+      <c r="F79" s="2">
         <v>0</v>
       </c>
       <c r="G79" s="1">
         <v>100</v>
       </c>
       <c r="H79" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I79" s="1">
-        <v>900</v>
+        <v>1014</v>
       </c>
       <c r="J79" s="1">
-        <v>1079546</v>
-      </c>
-      <c r="K79" t="s">
-        <v>34</v>
+        <v>1088635</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L79" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="1">
         <v>0</v>
@@ -5111,40 +5080,40 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B80" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D80" s="1">
-        <v>3008</v>
+        <v>14</v>
+      </c>
+      <c r="D80" s="5">
+        <v>2206</v>
       </c>
       <c r="E80" s="1">
-        <v>1</v>
-      </c>
-      <c r="F80" s="1">
+        <v>2</v>
+      </c>
+      <c r="F80" s="2">
         <v>0</v>
       </c>
       <c r="G80" s="1">
         <v>100</v>
       </c>
       <c r="H80" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I80" s="1">
-        <v>900</v>
+        <v>1014</v>
       </c>
       <c r="J80" s="1">
-        <v>1079546</v>
-      </c>
-      <c r="K80" t="s">
-        <v>34</v>
+        <v>1088635</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L80" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="1">
         <v>0</v>
@@ -5152,40 +5121,40 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B81" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D81" s="1">
-        <v>3010</v>
+        <v>14</v>
+      </c>
+      <c r="D81" s="5">
+        <v>2207</v>
       </c>
       <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="1">
+        <v>2</v>
+      </c>
+      <c r="F81" s="2">
         <v>0</v>
       </c>
       <c r="G81" s="1">
         <v>100</v>
       </c>
       <c r="H81" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I81" s="1">
-        <v>900</v>
+        <v>1014</v>
       </c>
       <c r="J81" s="1">
-        <v>1079546</v>
-      </c>
-      <c r="K81" t="s">
-        <v>34</v>
+        <v>1088635</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L81" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="1">
         <v>0</v>
@@ -5193,40 +5162,40 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B82" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D82" s="1">
-        <v>3012</v>
+        <v>14</v>
+      </c>
+      <c r="D82" s="5">
+        <v>2208</v>
       </c>
       <c r="E82" s="1">
-        <v>1</v>
-      </c>
-      <c r="F82" s="1">
+        <v>2</v>
+      </c>
+      <c r="F82" s="2">
         <v>0</v>
       </c>
       <c r="G82" s="1">
         <v>100</v>
       </c>
       <c r="H82" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I82" s="1">
-        <v>900</v>
+        <v>1014</v>
       </c>
       <c r="J82" s="1">
-        <v>1079546</v>
-      </c>
-      <c r="K82" t="s">
-        <v>34</v>
+        <v>1088635</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L82" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="1">
         <v>0</v>
@@ -5234,40 +5203,40 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>456</v>
+        <v>16</v>
       </c>
       <c r="B83" s="1">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D83" s="1">
-        <v>301</v>
+        <v>14</v>
+      </c>
+      <c r="D83" s="5">
+        <v>2209</v>
       </c>
       <c r="E83" s="1">
-        <v>0</v>
-      </c>
-      <c r="F83" s="1">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2">
         <v>0</v>
       </c>
       <c r="G83" s="1">
         <v>100</v>
       </c>
       <c r="H83" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I83" s="1">
-        <v>900</v>
+        <v>1014</v>
       </c>
       <c r="J83" s="1">
-        <v>1079546</v>
-      </c>
-      <c r="K83" t="s">
-        <v>34</v>
+        <v>1088635</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="L83" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="1">
         <v>0</v>
@@ -5275,19 +5244,19 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B84" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D84" s="5">
-        <v>3007</v>
+      <c r="D84" s="1">
+        <v>3000</v>
       </c>
       <c r="E84" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -5316,19 +5285,19 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B85" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D85" s="1">
-        <v>302</v>
+        <v>3002</v>
       </c>
       <c r="E85" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -5357,19 +5326,19 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B86" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D86" s="1">
-        <v>283</v>
+        <v>3004</v>
       </c>
       <c r="E86" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -5398,19 +5367,19 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B87" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D87" s="1">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="E87" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -5419,7 +5388,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I87" s="1">
         <v>900</v>
@@ -5439,19 +5408,19 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B88" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D88" s="5">
-        <v>3006</v>
+      <c r="D88" s="1">
+        <v>3008</v>
       </c>
       <c r="E88" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -5460,7 +5429,7 @@
         <v>100</v>
       </c>
       <c r="H88" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I88" s="1">
         <v>900</v>
@@ -5480,19 +5449,19 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B89" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D89" s="1">
-        <v>276</v>
+        <v>3010</v>
       </c>
       <c r="E89" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -5501,7 +5470,7 @@
         <v>100</v>
       </c>
       <c r="H89" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I89" s="1">
         <v>900</v>
@@ -5521,19 +5490,19 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B90" s="1">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="D90" s="1">
-        <v>3002</v>
+        <v>3012</v>
       </c>
       <c r="E90" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -5542,16 +5511,16 @@
         <v>100</v>
       </c>
       <c r="H90" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I90" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J90" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>36</v>
+        <v>1079546</v>
+      </c>
+      <c r="K90" t="s">
+        <v>34</v>
       </c>
       <c r="L90" s="1" t="b">
         <v>0</v>
@@ -5562,16 +5531,16 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="B91" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D91" s="1">
-        <v>3011</v>
+        <v>301</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -5583,16 +5552,16 @@
         <v>100</v>
       </c>
       <c r="H91" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I91" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J91" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>36</v>
+        <v>1079546</v>
+      </c>
+      <c r="K91" t="s">
+        <v>34</v>
       </c>
       <c r="L91" s="1" t="b">
         <v>0</v>
@@ -5603,16 +5572,16 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B92" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D92" s="1">
-        <v>3009</v>
+        <v>22</v>
+      </c>
+      <c r="D92" s="5">
+        <v>3007</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
@@ -5627,13 +5596,13 @@
         <v>1</v>
       </c>
       <c r="I92" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J92" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>36</v>
+        <v>1079546</v>
+      </c>
+      <c r="K92" t="s">
+        <v>34</v>
       </c>
       <c r="L92" s="1" t="b">
         <v>0</v>
@@ -5644,16 +5613,16 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B93" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D93" s="1">
-        <v>3000</v>
+        <v>302</v>
       </c>
       <c r="E93" s="1">
         <v>0</v>
@@ -5665,16 +5634,16 @@
         <v>100</v>
       </c>
       <c r="H93" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I93" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J93" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>36</v>
+        <v>1079546</v>
+      </c>
+      <c r="K93" t="s">
+        <v>34</v>
       </c>
       <c r="L93" s="1" t="b">
         <v>0</v>
@@ -5685,16 +5654,16 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B94" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D94" s="1">
-        <v>3001</v>
+        <v>283</v>
       </c>
       <c r="E94" s="1">
         <v>0</v>
@@ -5706,16 +5675,16 @@
         <v>100</v>
       </c>
       <c r="H94" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I94" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J94" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>36</v>
+        <v>1079546</v>
+      </c>
+      <c r="K94" t="s">
+        <v>34</v>
       </c>
       <c r="L94" s="1" t="b">
         <v>0</v>
@@ -5726,16 +5695,16 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B95" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D95" s="1">
-        <v>3003</v>
+        <v>3008</v>
       </c>
       <c r="E95" s="1">
         <v>0</v>
@@ -5750,13 +5719,13 @@
         <v>1</v>
       </c>
       <c r="I95" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J95" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>36</v>
+        <v>1079546</v>
+      </c>
+      <c r="K95" t="s">
+        <v>34</v>
       </c>
       <c r="L95" s="1" t="b">
         <v>0</v>
@@ -5767,16 +5736,16 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B96" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D96" s="1">
-        <v>3005</v>
+        <v>22</v>
+      </c>
+      <c r="D96" s="5">
+        <v>3006</v>
       </c>
       <c r="E96" s="1">
         <v>0</v>
@@ -5788,16 +5757,16 @@
         <v>100</v>
       </c>
       <c r="H96" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I96" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J96" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>36</v>
+        <v>1079546</v>
+      </c>
+      <c r="K96" t="s">
+        <v>34</v>
       </c>
       <c r="L96" s="1" t="b">
         <v>0</v>
@@ -5808,16 +5777,16 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B97" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D97" s="1">
-        <v>200</v>
+        <v>276</v>
       </c>
       <c r="E97" s="1">
         <v>0</v>
@@ -5829,16 +5798,16 @@
         <v>100</v>
       </c>
       <c r="H97" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I97" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J97" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>36</v>
+        <v>1079546</v>
+      </c>
+      <c r="K97" t="s">
+        <v>34</v>
       </c>
       <c r="L97" s="1" t="b">
         <v>0</v>
@@ -5855,10 +5824,10 @@
         <v>1006</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D98" s="1">
-        <v>20</v>
+        <v>3002</v>
       </c>
       <c r="E98" s="1">
         <v>0</v>
@@ -5899,7 +5868,7 @@
         <v>41</v>
       </c>
       <c r="D99" s="1">
-        <v>21</v>
+        <v>3011</v>
       </c>
       <c r="E99" s="1">
         <v>0</v>
@@ -5931,16 +5900,16 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B100" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D100" s="1">
-        <v>3142</v>
+        <v>3009</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
@@ -5972,16 +5941,16 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B101" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D101" s="1">
-        <v>3143</v>
+        <v>3000</v>
       </c>
       <c r="E101" s="1">
         <v>0</v>
@@ -6013,16 +5982,16 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B102" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D102" s="1">
-        <v>3144</v>
+        <v>3001</v>
       </c>
       <c r="E102" s="1">
         <v>0</v>
@@ -6054,16 +6023,16 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B103" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D103" s="1">
-        <v>3108</v>
+        <v>3003</v>
       </c>
       <c r="E103" s="1">
         <v>0</v>
@@ -6095,16 +6064,16 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B104" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D104" s="1">
-        <v>3109</v>
+        <v>3005</v>
       </c>
       <c r="E104" s="1">
         <v>0</v>
@@ -6136,16 +6105,16 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B105" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D105" s="1">
-        <v>3120</v>
+        <v>200</v>
       </c>
       <c r="E105" s="1">
         <v>0</v>
@@ -6177,16 +6146,16 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B106" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D106" s="1">
-        <v>3100</v>
+        <v>20</v>
       </c>
       <c r="E106" s="1">
         <v>0</v>
@@ -6218,16 +6187,16 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B107" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D107" s="1">
-        <v>3156</v>
+        <v>21</v>
       </c>
       <c r="E107" s="1">
         <v>0</v>
@@ -6259,16 +6228,16 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B108" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D108" s="1">
-        <v>1600</v>
+        <v>3142</v>
       </c>
       <c r="E108" s="1">
         <v>0</v>
@@ -6283,13 +6252,13 @@
         <v>1</v>
       </c>
       <c r="I108" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J108" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L108" s="1" t="b">
         <v>0</v>
@@ -6300,16 +6269,16 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B109" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D109" s="1">
-        <v>1605</v>
+        <v>3143</v>
       </c>
       <c r="E109" s="1">
         <v>0</v>
@@ -6324,13 +6293,13 @@
         <v>1</v>
       </c>
       <c r="I109" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J109" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L109" s="1" t="b">
         <v>0</v>
@@ -6341,16 +6310,16 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B110" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D110" s="1">
-        <v>1609</v>
+        <v>3144</v>
       </c>
       <c r="E110" s="1">
         <v>0</v>
@@ -6365,13 +6334,13 @@
         <v>1</v>
       </c>
       <c r="I110" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J110" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L110" s="1" t="b">
         <v>0</v>
@@ -6382,16 +6351,16 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B111" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D111" s="1">
-        <v>1612</v>
+        <v>3108</v>
       </c>
       <c r="E111" s="1">
         <v>0</v>
@@ -6406,13 +6375,13 @@
         <v>1</v>
       </c>
       <c r="I111" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J111" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L111" s="1" t="b">
         <v>0</v>
@@ -6423,16 +6392,16 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B112" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D112" s="1">
-        <v>1613</v>
+        <v>3109</v>
       </c>
       <c r="E112" s="1">
         <v>0</v>
@@ -6447,13 +6416,13 @@
         <v>1</v>
       </c>
       <c r="I112" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J112" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L112" s="1" t="b">
         <v>0</v>
@@ -6464,16 +6433,16 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B113" s="1">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D113" s="1">
-        <v>1652</v>
+        <v>3120</v>
       </c>
       <c r="E113" s="1">
         <v>0</v>
@@ -6488,13 +6457,13 @@
         <v>1</v>
       </c>
       <c r="I113" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J113" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L113" s="1" t="b">
         <v>0</v>
@@ -6505,16 +6474,16 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B114" s="1">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D114" s="1">
-        <v>1654</v>
+        <v>3100</v>
       </c>
       <c r="E114" s="1">
         <v>0</v>
@@ -6529,13 +6498,13 @@
         <v>1</v>
       </c>
       <c r="I114" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J114" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L114" s="1" t="b">
         <v>0</v>
@@ -6546,16 +6515,16 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B115" s="1">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D115" s="1">
-        <v>1702</v>
+        <v>3156</v>
       </c>
       <c r="E115" s="1">
         <v>0</v>
@@ -6570,13 +6539,13 @@
         <v>1</v>
       </c>
       <c r="I115" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J115" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L115" s="1" t="b">
         <v>0</v>
@@ -6587,16 +6556,16 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B116" s="1">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D116" s="1">
-        <v>1803</v>
+        <v>1600</v>
       </c>
       <c r="E116" s="1">
         <v>0</v>
@@ -6628,16 +6597,16 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B117" s="1">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D117" s="1">
-        <v>22</v>
+        <v>1605</v>
       </c>
       <c r="E117" s="1">
         <v>0</v>
@@ -6669,16 +6638,16 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B118" s="1">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D118" s="1">
-        <v>2000</v>
+        <v>1609</v>
       </c>
       <c r="E118" s="1">
         <v>0</v>
@@ -6710,16 +6679,16 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B119" s="1">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D119" s="1">
-        <v>2001</v>
+        <v>1612</v>
       </c>
       <c r="E119" s="1">
         <v>0</v>
@@ -6751,16 +6720,16 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="B120" s="1">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D120" s="1">
-        <v>2002</v>
+        <v>1613</v>
       </c>
       <c r="E120" s="1">
         <v>0</v>
@@ -6792,16 +6761,16 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B121" s="1">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D121" s="1">
-        <v>2003</v>
+        <v>1652</v>
       </c>
       <c r="E121" s="1">
         <v>0</v>
@@ -6833,16 +6802,16 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B122" s="1">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D122" s="1">
-        <v>298</v>
+        <v>1654</v>
       </c>
       <c r="E122" s="1">
         <v>0</v>
@@ -6874,16 +6843,16 @@
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B123" s="1">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D123" s="1">
-        <v>1650</v>
+        <v>1702</v>
       </c>
       <c r="E123" s="1">
         <v>0</v>
@@ -6898,13 +6867,13 @@
         <v>1</v>
       </c>
       <c r="I123" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J123" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K123" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L123" s="1" t="b">
         <v>0</v>
@@ -6915,16 +6884,16 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B124" s="1">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D124" s="1">
-        <v>1651</v>
+        <v>1803</v>
       </c>
       <c r="E124" s="1">
         <v>0</v>
@@ -6939,13 +6908,13 @@
         <v>1</v>
       </c>
       <c r="I124" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J124" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K124" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L124" s="1" t="b">
         <v>0</v>
@@ -6956,16 +6925,16 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B125" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D125" s="1">
-        <v>1700</v>
+        <v>22</v>
       </c>
       <c r="E125" s="1">
         <v>0</v>
@@ -6980,13 +6949,13 @@
         <v>1</v>
       </c>
       <c r="I125" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J125" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K125" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L125" s="1" t="b">
         <v>0</v>
@@ -6997,16 +6966,16 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B126" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D126" s="1">
-        <v>1701</v>
+        <v>2000</v>
       </c>
       <c r="E126" s="1">
         <v>0</v>
@@ -7021,13 +6990,13 @@
         <v>1</v>
       </c>
       <c r="I126" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J126" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K126" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L126" s="1" t="b">
         <v>0</v>
@@ -7038,16 +7007,16 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B127" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D127" s="1">
-        <v>1800</v>
+        <v>2001</v>
       </c>
       <c r="E127" s="1">
         <v>0</v>
@@ -7062,13 +7031,13 @@
         <v>1</v>
       </c>
       <c r="I127" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J127" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K127" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L127" s="1" t="b">
         <v>0</v>
@@ -7079,16 +7048,16 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B128" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D128" s="1">
-        <v>1802</v>
+        <v>2002</v>
       </c>
       <c r="E128" s="1">
         <v>0</v>
@@ -7103,13 +7072,13 @@
         <v>1</v>
       </c>
       <c r="I128" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J128" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K128" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L128" s="1" t="b">
         <v>0</v>
@@ -7123,13 +7092,13 @@
         <v>82</v>
       </c>
       <c r="B129" s="1">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D129" s="1">
-        <v>23</v>
+        <v>2003</v>
       </c>
       <c r="E129" s="1">
         <v>0</v>
@@ -7144,13 +7113,13 @@
         <v>1</v>
       </c>
       <c r="I129" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J129" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K129" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L129" s="1" t="b">
         <v>0</v>
@@ -7164,13 +7133,13 @@
         <v>82</v>
       </c>
       <c r="B130" s="1">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D130" s="1">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -7185,13 +7154,13 @@
         <v>1</v>
       </c>
       <c r="I130" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J130" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K130" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L130" s="1" t="b">
         <v>0</v>
@@ -7202,16 +7171,16 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="B131" s="1">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D131" s="1">
-        <v>277</v>
+        <v>1650</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -7243,16 +7212,16 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="B132" s="1">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D132" s="1">
-        <v>204</v>
+        <v>1651</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -7284,16 +7253,16 @@
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B133" s="1">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D133" s="1">
-        <v>11</v>
+        <v>1700</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -7308,13 +7277,13 @@
         <v>1</v>
       </c>
       <c r="I133" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J133" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K133" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K133" s="1">
+        <v>41</v>
       </c>
       <c r="L133" s="1" t="b">
         <v>0</v>
@@ -7325,16 +7294,16 @@
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B134" s="1">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D134" s="1">
-        <v>295</v>
+        <v>1701</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -7349,13 +7318,13 @@
         <v>1</v>
       </c>
       <c r="I134" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J134" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K134" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K134" s="1">
+        <v>41</v>
       </c>
       <c r="L134" s="1" t="b">
         <v>0</v>
@@ -7366,16 +7335,16 @@
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B135" s="1">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D135" s="1">
-        <v>24</v>
+        <v>1800</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
@@ -7390,13 +7359,13 @@
         <v>1</v>
       </c>
       <c r="I135" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J135" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K135" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K135" s="1">
+        <v>41</v>
       </c>
       <c r="L135" s="1" t="b">
         <v>0</v>
@@ -7407,16 +7376,16 @@
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B136" s="1">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D136" s="1">
-        <v>4000</v>
+        <v>1802</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
@@ -7428,16 +7397,16 @@
         <v>100</v>
       </c>
       <c r="H136" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I136" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J136" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K136" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K136" s="1">
+        <v>41</v>
       </c>
       <c r="L136" s="1" t="b">
         <v>0</v>
@@ -7448,16 +7417,16 @@
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="B137" s="1">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D137" s="1">
-        <v>4001</v>
+        <v>23</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -7469,16 +7438,16 @@
         <v>100</v>
       </c>
       <c r="H137" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I137" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J137" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K137" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K137" s="1">
+        <v>41</v>
       </c>
       <c r="L137" s="1" t="b">
         <v>0</v>
@@ -7489,16 +7458,16 @@
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="B138" s="1">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D138" s="1">
-        <v>4002</v>
+        <v>271</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -7510,16 +7479,16 @@
         <v>100</v>
       </c>
       <c r="H138" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I138" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J138" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K138" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K138" s="1">
+        <v>41</v>
       </c>
       <c r="L138" s="1" t="b">
         <v>0</v>
@@ -7530,16 +7499,16 @@
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="B139" s="1">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D139" s="1">
-        <v>4003</v>
+        <v>277</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -7551,16 +7520,16 @@
         <v>100</v>
       </c>
       <c r="H139" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I139" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J139" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K139" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K139" s="1">
+        <v>41</v>
       </c>
       <c r="L139" s="1" t="b">
         <v>0</v>
@@ -7571,16 +7540,16 @@
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="B140" s="1">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D140" s="1">
-        <v>4004</v>
+        <v>204</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -7592,16 +7561,16 @@
         <v>100</v>
       </c>
       <c r="H140" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I140" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J140" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K140" s="1" t="s">
-        <v>37</v>
+        <v>1159783</v>
+      </c>
+      <c r="K140" s="1">
+        <v>41</v>
       </c>
       <c r="L140" s="1" t="b">
         <v>0</v>
@@ -7621,7 +7590,7 @@
         <v>48</v>
       </c>
       <c r="D141" s="1">
-        <v>4005</v>
+        <v>11</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
@@ -7633,7 +7602,7 @@
         <v>100</v>
       </c>
       <c r="H141" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I141" s="1">
         <v>3056</v>
@@ -7662,7 +7631,7 @@
         <v>48</v>
       </c>
       <c r="D142" s="1">
-        <v>4006</v>
+        <v>295</v>
       </c>
       <c r="E142" s="1">
         <v>0</v>
@@ -7674,7 +7643,7 @@
         <v>100</v>
       </c>
       <c r="H142" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I142" s="1">
         <v>3056</v>
@@ -7703,7 +7672,7 @@
         <v>48</v>
       </c>
       <c r="D143" s="1">
-        <v>4007</v>
+        <v>24</v>
       </c>
       <c r="E143" s="1">
         <v>0</v>
@@ -7715,7 +7684,7 @@
         <v>100</v>
       </c>
       <c r="H143" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I143" s="1">
         <v>3056</v>
@@ -7744,7 +7713,7 @@
         <v>48</v>
       </c>
       <c r="D144" s="1">
-        <v>4008</v>
+        <v>4000</v>
       </c>
       <c r="E144" s="1">
         <v>0</v>
@@ -7756,7 +7725,7 @@
         <v>100</v>
       </c>
       <c r="H144" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I144" s="1">
         <v>3056</v>
@@ -7785,7 +7754,7 @@
         <v>48</v>
       </c>
       <c r="D145" s="1">
-        <v>4009</v>
+        <v>4001</v>
       </c>
       <c r="E145" s="1">
         <v>0</v>
@@ -7797,7 +7766,7 @@
         <v>100</v>
       </c>
       <c r="H145" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I145" s="1">
         <v>3056</v>
@@ -7826,7 +7795,7 @@
         <v>48</v>
       </c>
       <c r="D146" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="E146" s="1">
         <v>0</v>
@@ -7838,7 +7807,7 @@
         <v>100</v>
       </c>
       <c r="H146" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I146" s="1">
         <v>3056</v>
@@ -7858,16 +7827,16 @@
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B147" s="1">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D147" s="1">
-        <v>12</v>
+        <v>4003</v>
       </c>
       <c r="E147" s="1">
         <v>0</v>
@@ -7879,16 +7848,16 @@
         <v>100</v>
       </c>
       <c r="H147" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I147" s="1">
-        <v>2497</v>
+        <v>3056</v>
       </c>
       <c r="J147" s="1">
-        <v>1116139</v>
-      </c>
-      <c r="K147" s="1">
-        <v>26</v>
+        <v>1019972</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L147" s="1" t="b">
         <v>0</v>
@@ -7899,16 +7868,16 @@
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B148" s="1">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D148" s="1">
-        <v>2004</v>
+        <v>4004</v>
       </c>
       <c r="E148" s="1">
         <v>0</v>
@@ -7920,21 +7889,349 @@
         <v>100</v>
       </c>
       <c r="H148" s="1">
+        <v>3</v>
+      </c>
+      <c r="I148" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J148" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L148" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B149" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D149" s="1">
+        <v>4005</v>
+      </c>
+      <c r="E149" s="1">
+        <v>0</v>
+      </c>
+      <c r="F149" s="1">
+        <v>0</v>
+      </c>
+      <c r="G149" s="1">
+        <v>100</v>
+      </c>
+      <c r="H149" s="1">
+        <v>3</v>
+      </c>
+      <c r="I149" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J149" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L149" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M149" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B150" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D150" s="1">
+        <v>4006</v>
+      </c>
+      <c r="E150" s="1">
+        <v>0</v>
+      </c>
+      <c r="F150" s="1">
+        <v>0</v>
+      </c>
+      <c r="G150" s="1">
+        <v>100</v>
+      </c>
+      <c r="H150" s="1">
+        <v>3</v>
+      </c>
+      <c r="I150" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J150" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K150" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L150" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M150" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B151" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D151" s="1">
+        <v>4007</v>
+      </c>
+      <c r="E151" s="1">
+        <v>0</v>
+      </c>
+      <c r="F151" s="1">
+        <v>0</v>
+      </c>
+      <c r="G151" s="1">
+        <v>100</v>
+      </c>
+      <c r="H151" s="1">
+        <v>4</v>
+      </c>
+      <c r="I151" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J151" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L151" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M151" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B152" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D152" s="1">
+        <v>4008</v>
+      </c>
+      <c r="E152" s="1">
+        <v>0</v>
+      </c>
+      <c r="F152" s="1">
+        <v>0</v>
+      </c>
+      <c r="G152" s="1">
+        <v>100</v>
+      </c>
+      <c r="H152" s="1">
+        <v>4</v>
+      </c>
+      <c r="I152" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J152" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L152" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M152" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B153" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D153" s="1">
+        <v>4009</v>
+      </c>
+      <c r="E153" s="1">
+        <v>0</v>
+      </c>
+      <c r="F153" s="1">
+        <v>0</v>
+      </c>
+      <c r="G153" s="1">
+        <v>100</v>
+      </c>
+      <c r="H153" s="1">
+        <v>4</v>
+      </c>
+      <c r="I153" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J153" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L153" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M153" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B154" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D154" s="1">
+        <v>4010</v>
+      </c>
+      <c r="E154" s="1">
+        <v>0</v>
+      </c>
+      <c r="F154" s="1">
+        <v>0</v>
+      </c>
+      <c r="G154" s="1">
+        <v>100</v>
+      </c>
+      <c r="H154" s="1">
         <v>1</v>
       </c>
-      <c r="I148" s="1">
+      <c r="I154" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J154" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L154" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M154" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B155" s="1">
+        <v>1014</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D155" s="1">
+        <v>12</v>
+      </c>
+      <c r="E155" s="1">
+        <v>0</v>
+      </c>
+      <c r="F155" s="1">
+        <v>0</v>
+      </c>
+      <c r="G155" s="1">
+        <v>100</v>
+      </c>
+      <c r="H155" s="1">
+        <v>1</v>
+      </c>
+      <c r="I155" s="1">
         <v>2497</v>
       </c>
-      <c r="J148" s="1">
+      <c r="J155" s="1">
         <v>1116139</v>
       </c>
-      <c r="K148" s="1">
+      <c r="K155" s="1">
         <v>26</v>
       </c>
-      <c r="L148" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M148" s="1">
+      <c r="L155" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M155" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B156" s="1">
+        <v>1014</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D156" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E156" s="1">
+        <v>0</v>
+      </c>
+      <c r="F156" s="1">
+        <v>0</v>
+      </c>
+      <c r="G156" s="1">
+        <v>100</v>
+      </c>
+      <c r="H156" s="1">
+        <v>1</v>
+      </c>
+      <c r="I156" s="1">
+        <v>2497</v>
+      </c>
+      <c r="J156" s="1">
+        <v>1116139</v>
+      </c>
+      <c r="K156" s="1">
+        <v>26</v>
+      </c>
+      <c r="L156" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M156" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -5253,7 +5253,7 @@
         <v>22</v>
       </c>
       <c r="D84" s="1">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -5294,7 +5294,7 @@
         <v>22</v>
       </c>
       <c r="D85" s="1">
-        <v>3002</v>
+        <v>3501</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -5335,7 +5335,7 @@
         <v>22</v>
       </c>
       <c r="D86" s="1">
-        <v>3004</v>
+        <v>3502</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -5376,7 +5376,7 @@
         <v>22</v>
       </c>
       <c r="D87" s="1">
-        <v>3006</v>
+        <v>3503</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -5417,7 +5417,7 @@
         <v>22</v>
       </c>
       <c r="D88" s="1">
-        <v>3008</v>
+        <v>3505</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -5458,7 +5458,7 @@
         <v>22</v>
       </c>
       <c r="D89" s="1">
-        <v>3010</v>
+        <v>3504</v>
       </c>
       <c r="E89" s="1">
         <v>1</v>
@@ -5499,7 +5499,7 @@
         <v>22</v>
       </c>
       <c r="D90" s="1">
-        <v>3012</v>
+        <v>3506</v>
       </c>
       <c r="E90" s="1">
         <v>1</v>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -154,9 +154,6 @@
     <t>shopItemType</t>
   </si>
   <si>
-    <t>buyLimitOne</t>
-  </si>
-  <si>
     <t>buyAction</t>
   </si>
   <si>
@@ -1495,6 +1492,10 @@
   </si>
   <si>
     <t>动物产物</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>buyLimitOne</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1912,13 +1913,13 @@
         <v>1</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
@@ -1944,22 +1945,22 @@
         <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="L3" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -1994,7 +1995,7 @@
         <v>1068306</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L4" s="1" t="b">
         <v>0</v>
@@ -2035,7 +2036,7 @@
         <v>1068306</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L5" s="1" t="b">
         <v>0</v>
@@ -2076,7 +2077,7 @@
         <v>1068306</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L6" s="1" t="b">
         <v>0</v>
@@ -2117,7 +2118,7 @@
         <v>1068306</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L7" s="1" t="b">
         <v>0</v>
@@ -2158,7 +2159,7 @@
         <v>1068306</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L8" s="1" t="b">
         <v>0</v>
@@ -2199,7 +2200,7 @@
         <v>1068306</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L9" s="1" t="b">
         <v>0</v>
@@ -2240,7 +2241,7 @@
         <v>1068306</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L10" s="1" t="b">
         <v>0</v>
@@ -2281,7 +2282,7 @@
         <v>1068306</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L11" s="1" t="b">
         <v>0</v>
@@ -2322,7 +2323,7 @@
         <v>1068306</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L12" s="1" t="b">
         <v>0</v>
@@ -2363,7 +2364,7 @@
         <v>1068306</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L13" s="1" t="b">
         <v>0</v>
@@ -2404,7 +2405,7 @@
         <v>1068306</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L14" s="1" t="b">
         <v>0</v>
@@ -2445,7 +2446,7 @@
         <v>1068306</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L15" s="1" t="b">
         <v>0</v>
@@ -2486,7 +2487,7 @@
         <v>1068306</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L16" s="1" t="b">
         <v>0</v>
@@ -2527,7 +2528,7 @@
         <v>1068306</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L17" s="1" t="b">
         <v>0</v>
@@ -2568,7 +2569,7 @@
         <v>1068306</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L18" s="1" t="b">
         <v>0</v>
@@ -2609,7 +2610,7 @@
         <v>1068306</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L19" s="1" t="b">
         <v>0</v>
@@ -2650,7 +2651,7 @@
         <v>1068306</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L20" s="1" t="b">
         <v>0</v>
@@ -2691,7 +2692,7 @@
         <v>1068306</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L21" s="1" t="b">
         <v>0</v>
@@ -2732,7 +2733,7 @@
         <v>1068306</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L22" s="1" t="b">
         <v>0</v>
@@ -2773,7 +2774,7 @@
         <v>1068306</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L23" s="1" t="b">
         <v>0</v>
@@ -2814,7 +2815,7 @@
         <v>1068306</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L24" s="1" t="b">
         <v>0</v>
@@ -2855,7 +2856,7 @@
         <v>1068306</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L25" s="1" t="b">
         <v>0</v>
@@ -2896,7 +2897,7 @@
         <v>1068306</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L26" s="1" t="b">
         <v>0</v>
@@ -2937,7 +2938,7 @@
         <v>1068306</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L27" s="1" t="b">
         <v>0</v>
@@ -2978,7 +2979,7 @@
         <v>1068306</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L28" s="1" t="b">
         <v>0</v>
@@ -3019,7 +3020,7 @@
         <v>1068306</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L29" s="1" t="b">
         <v>0</v>
@@ -3060,7 +3061,7 @@
         <v>1068306</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L30" s="1" t="b">
         <v>0</v>
@@ -3101,7 +3102,7 @@
         <v>1068306</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L31" s="1" t="b">
         <v>0</v>
@@ -3142,7 +3143,7 @@
         <v>1068306</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L32" s="1" t="b">
         <v>0</v>
@@ -3183,7 +3184,7 @@
         <v>1068306</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L33" s="1" t="b">
         <v>0</v>
@@ -3224,7 +3225,7 @@
         <v>1068306</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L34" s="1" t="b">
         <v>0</v>
@@ -3265,7 +3266,7 @@
         <v>1068306</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L35" s="1" t="b">
         <v>0</v>
@@ -3306,7 +3307,7 @@
         <v>1068306</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L36" s="1" t="b">
         <v>0</v>
@@ -3347,7 +3348,7 @@
         <v>1068306</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L37" s="1" t="b">
         <v>0</v>
@@ -3388,7 +3389,7 @@
         <v>1068306</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L38" s="1" t="b">
         <v>0</v>
@@ -3429,7 +3430,7 @@
         <v>1068306</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L39" s="1" t="b">
         <v>0</v>
@@ -3470,7 +3471,7 @@
         <v>1068306</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L40" s="1" t="b">
         <v>0</v>
@@ -3511,7 +3512,7 @@
         <v>1068306</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L41" s="1" t="b">
         <v>0</v>
@@ -3552,7 +3553,7 @@
         <v>1068306</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L42" s="1" t="b">
         <v>0</v>
@@ -3593,7 +3594,7 @@
         <v>1068306</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L43" s="1" t="b">
         <v>0</v>
@@ -3634,7 +3635,7 @@
         <v>1068306</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L44" s="1" t="b">
         <v>0</v>
@@ -3675,7 +3676,7 @@
         <v>1068306</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L45" s="1" t="b">
         <v>0</v>
@@ -3716,7 +3717,7 @@
         <v>1068306</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L46" s="1" t="b">
         <v>0</v>
@@ -3757,7 +3758,7 @@
         <v>1068306</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L47" s="1" t="b">
         <v>0</v>
@@ -3798,7 +3799,7 @@
         <v>1068306</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L48" s="1" t="b">
         <v>0</v>
@@ -3839,7 +3840,7 @@
         <v>1068306</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L49" s="1" t="b">
         <v>0</v>
@@ -3880,7 +3881,7 @@
         <v>1068306</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L50" s="1" t="b">
         <v>0</v>
@@ -3921,7 +3922,7 @@
         <v>1068306</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L51" s="1" t="b">
         <v>0</v>
@@ -3962,7 +3963,7 @@
         <v>1068306</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L52" s="1" t="b">
         <v>0</v>
@@ -4003,7 +4004,7 @@
         <v>1068306</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L53" s="1" t="b">
         <v>0</v>
@@ -4044,7 +4045,7 @@
         <v>1068306</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L54" s="1" t="b">
         <v>0</v>
@@ -4085,7 +4086,7 @@
         <v>1068306</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L55" s="1" t="b">
         <v>0</v>
@@ -4126,7 +4127,7 @@
         <v>1068306</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L56" s="1" t="b">
         <v>0</v>
@@ -4167,7 +4168,7 @@
         <v>1068306</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L57" s="1" t="b">
         <v>0</v>
@@ -4208,7 +4209,7 @@
         <v>1068306</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L58" s="1" t="b">
         <v>0</v>
@@ -4249,7 +4250,7 @@
         <v>1068306</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L59" s="1" t="b">
         <v>0</v>
@@ -4290,7 +4291,7 @@
         <v>1088635</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L60" s="1" t="b">
         <v>1</v>
@@ -4331,7 +4332,7 @@
         <v>1088635</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L61" s="1" t="b">
         <v>1</v>
@@ -4372,7 +4373,7 @@
         <v>1088635</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L62" s="1" t="b">
         <v>1</v>
@@ -4413,7 +4414,7 @@
         <v>1088635</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L63" s="1" t="b">
         <v>1</v>
@@ -4454,7 +4455,7 @@
         <v>1088635</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L64" s="1" t="b">
         <v>1</v>
@@ -4495,7 +4496,7 @@
         <v>1088635</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L65" s="1" t="b">
         <v>1</v>
@@ -4536,7 +4537,7 @@
         <v>1088635</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L66" s="1" t="b">
         <v>1</v>
@@ -4577,7 +4578,7 @@
         <v>1088635</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L67" s="1" t="b">
         <v>1</v>
@@ -4618,7 +4619,7 @@
         <v>1088635</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L68" s="1" t="b">
         <v>1</v>
@@ -4659,7 +4660,7 @@
         <v>1088635</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L69" s="1" t="b">
         <v>1</v>
@@ -4700,7 +4701,7 @@
         <v>1088635</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L70" s="1" t="b">
         <v>1</v>
@@ -4741,7 +4742,7 @@
         <v>1088635</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L71" s="1" t="b">
         <v>1</v>
@@ -4782,7 +4783,7 @@
         <v>1088635</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L72" s="1" t="b">
         <v>1</v>
@@ -4823,7 +4824,7 @@
         <v>1088635</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L73" s="1" t="b">
         <v>1</v>
@@ -4864,7 +4865,7 @@
         <v>1088635</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L74" s="1" t="b">
         <v>1</v>
@@ -4905,7 +4906,7 @@
         <v>1088635</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L75" s="1" t="b">
         <v>1</v>
@@ -4946,7 +4947,7 @@
         <v>1088635</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L76" s="1" t="b">
         <v>1</v>
@@ -4987,7 +4988,7 @@
         <v>1088635</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L77" s="1" t="b">
         <v>1</v>
@@ -5028,7 +5029,7 @@
         <v>1088635</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L78" s="1" t="b">
         <v>1</v>
@@ -5069,7 +5070,7 @@
         <v>1088635</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L79" s="1" t="b">
         <v>1</v>
@@ -5110,7 +5111,7 @@
         <v>1088635</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L80" s="1" t="b">
         <v>1</v>
@@ -5151,7 +5152,7 @@
         <v>1088635</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L81" s="1" t="b">
         <v>1</v>
@@ -5192,7 +5193,7 @@
         <v>1088635</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L82" s="1" t="b">
         <v>1</v>
@@ -5233,7 +5234,7 @@
         <v>1088635</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L83" s="1" t="b">
         <v>1</v>
@@ -5244,13 +5245,13 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B84" s="1">
         <v>1004</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D84" s="1">
         <v>3500</v>
@@ -5274,10 +5275,10 @@
         <v>1079546</v>
       </c>
       <c r="K84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L84" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="1">
         <v>0</v>
@@ -5285,13 +5286,13 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B85" s="1">
         <v>1004</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D85" s="1">
         <v>3501</v>
@@ -5315,10 +5316,10 @@
         <v>1079546</v>
       </c>
       <c r="K85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L85" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="1">
         <v>0</v>
@@ -5326,13 +5327,13 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B86" s="1">
         <v>1004</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D86" s="1">
         <v>3502</v>
@@ -5356,10 +5357,10 @@
         <v>1079546</v>
       </c>
       <c r="K86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L86" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="1">
         <v>0</v>
@@ -5367,13 +5368,13 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B87" s="1">
         <v>1004</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D87" s="1">
         <v>3503</v>
@@ -5397,10 +5398,10 @@
         <v>1079546</v>
       </c>
       <c r="K87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L87" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="1">
         <v>0</v>
@@ -5408,13 +5409,13 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B88" s="1">
         <v>1004</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D88" s="1">
         <v>3505</v>
@@ -5438,10 +5439,10 @@
         <v>1079546</v>
       </c>
       <c r="K88" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L88" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="1">
         <v>0</v>
@@ -5449,13 +5450,13 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B89" s="1">
         <v>1004</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D89" s="1">
         <v>3504</v>
@@ -5479,10 +5480,10 @@
         <v>1079546</v>
       </c>
       <c r="K89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L89" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="1">
         <v>0</v>
@@ -5490,13 +5491,13 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B90" s="1">
         <v>1004</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D90" s="1">
         <v>3506</v>
@@ -5520,10 +5521,10 @@
         <v>1079546</v>
       </c>
       <c r="K90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L90" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="1">
         <v>0</v>
@@ -5531,13 +5532,13 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B91" s="1">
         <v>1005</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D91" s="1">
         <v>301</v>
@@ -5561,7 +5562,7 @@
         <v>1079546</v>
       </c>
       <c r="K91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L91" s="1" t="b">
         <v>0</v>
@@ -5572,13 +5573,13 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B92" s="1">
         <v>1005</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D92" s="5">
         <v>3007</v>
@@ -5602,7 +5603,7 @@
         <v>1079546</v>
       </c>
       <c r="K92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L92" s="1" t="b">
         <v>0</v>
@@ -5613,13 +5614,13 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B93" s="1">
         <v>1005</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D93" s="1">
         <v>302</v>
@@ -5643,7 +5644,7 @@
         <v>1079546</v>
       </c>
       <c r="K93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L93" s="1" t="b">
         <v>0</v>
@@ -5654,13 +5655,13 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B94" s="1">
         <v>1005</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D94" s="1">
         <v>283</v>
@@ -5684,7 +5685,7 @@
         <v>1079546</v>
       </c>
       <c r="K94" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L94" s="1" t="b">
         <v>0</v>
@@ -5695,13 +5696,13 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B95" s="1">
         <v>1005</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D95" s="1">
         <v>3008</v>
@@ -5725,7 +5726,7 @@
         <v>1079546</v>
       </c>
       <c r="K95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L95" s="1" t="b">
         <v>0</v>
@@ -5736,13 +5737,13 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B96" s="1">
         <v>1005</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D96" s="5">
         <v>3006</v>
@@ -5766,7 +5767,7 @@
         <v>1079546</v>
       </c>
       <c r="K96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L96" s="1" t="b">
         <v>0</v>
@@ -5777,13 +5778,13 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B97" s="1">
         <v>1005</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D97" s="1">
         <v>276</v>
@@ -5807,7 +5808,7 @@
         <v>1079546</v>
       </c>
       <c r="K97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L97" s="1" t="b">
         <v>0</v>
@@ -5818,13 +5819,13 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B98" s="1">
         <v>1006</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D98" s="1">
         <v>3002</v>
@@ -5848,7 +5849,7 @@
         <v>1165443</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L98" s="1" t="b">
         <v>0</v>
@@ -5859,13 +5860,13 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B99" s="1">
         <v>1006</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D99" s="1">
         <v>3011</v>
@@ -5889,7 +5890,7 @@
         <v>1165443</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L99" s="1" t="b">
         <v>0</v>
@@ -5900,13 +5901,13 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B100" s="1">
         <v>1006</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D100" s="1">
         <v>3009</v>
@@ -5930,7 +5931,7 @@
         <v>1165443</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L100" s="1" t="b">
         <v>0</v>
@@ -5941,13 +5942,13 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B101" s="1">
         <v>1006</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D101" s="1">
         <v>3000</v>
@@ -5971,7 +5972,7 @@
         <v>1165443</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L101" s="1" t="b">
         <v>0</v>
@@ -5982,13 +5983,13 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B102" s="1">
         <v>1006</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D102" s="1">
         <v>3001</v>
@@ -6012,7 +6013,7 @@
         <v>1165443</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L102" s="1" t="b">
         <v>0</v>
@@ -6023,13 +6024,13 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B103" s="1">
         <v>1006</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D103" s="1">
         <v>3003</v>
@@ -6053,7 +6054,7 @@
         <v>1165443</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L103" s="1" t="b">
         <v>0</v>
@@ -6064,13 +6065,13 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B104" s="1">
         <v>1006</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D104" s="1">
         <v>3005</v>
@@ -6094,7 +6095,7 @@
         <v>1165443</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L104" s="1" t="b">
         <v>0</v>
@@ -6105,13 +6106,13 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B105" s="1">
         <v>1006</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D105" s="1">
         <v>200</v>
@@ -6135,7 +6136,7 @@
         <v>1165443</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L105" s="1" t="b">
         <v>0</v>
@@ -6146,13 +6147,13 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B106" s="1">
         <v>1006</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D106" s="1">
         <v>20</v>
@@ -6176,7 +6177,7 @@
         <v>1165443</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L106" s="1" t="b">
         <v>0</v>
@@ -6187,13 +6188,13 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B107" s="1">
         <v>1006</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D107" s="1">
         <v>21</v>
@@ -6217,7 +6218,7 @@
         <v>1165443</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L107" s="1" t="b">
         <v>0</v>
@@ -6228,13 +6229,13 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B108" s="1">
         <v>1007</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D108" s="1">
         <v>3142</v>
@@ -6258,7 +6259,7 @@
         <v>1165443</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L108" s="1" t="b">
         <v>0</v>
@@ -6269,13 +6270,13 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B109" s="1">
         <v>1007</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D109" s="1">
         <v>3143</v>
@@ -6299,7 +6300,7 @@
         <v>1165443</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L109" s="1" t="b">
         <v>0</v>
@@ -6310,13 +6311,13 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B110" s="1">
         <v>1007</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D110" s="1">
         <v>3144</v>
@@ -6340,7 +6341,7 @@
         <v>1165443</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L110" s="1" t="b">
         <v>0</v>
@@ -6351,13 +6352,13 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B111" s="1">
         <v>1007</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D111" s="1">
         <v>3108</v>
@@ -6381,7 +6382,7 @@
         <v>1165443</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L111" s="1" t="b">
         <v>0</v>
@@ -6392,13 +6393,13 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B112" s="1">
         <v>1007</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D112" s="1">
         <v>3109</v>
@@ -6422,7 +6423,7 @@
         <v>1165443</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L112" s="1" t="b">
         <v>0</v>
@@ -6433,13 +6434,13 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B113" s="1">
         <v>1007</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D113" s="1">
         <v>3120</v>
@@ -6463,7 +6464,7 @@
         <v>1165443</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L113" s="1" t="b">
         <v>0</v>
@@ -6474,13 +6475,13 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B114" s="1">
         <v>1007</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D114" s="1">
         <v>3100</v>
@@ -6504,7 +6505,7 @@
         <v>1165443</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L114" s="1" t="b">
         <v>0</v>
@@ -6515,13 +6516,13 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B115" s="1">
         <v>1007</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D115" s="1">
         <v>3156</v>
@@ -6545,7 +6546,7 @@
         <v>1165443</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L115" s="1" t="b">
         <v>0</v>
@@ -6556,13 +6557,13 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B116" s="1">
         <v>1008</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D116" s="1">
         <v>1600</v>
@@ -6586,7 +6587,7 @@
         <v>1019120</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L116" s="1" t="b">
         <v>0</v>
@@ -6597,13 +6598,13 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B117" s="1">
         <v>1008</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D117" s="1">
         <v>1605</v>
@@ -6627,7 +6628,7 @@
         <v>1019120</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L117" s="1" t="b">
         <v>0</v>
@@ -6638,13 +6639,13 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B118" s="1">
         <v>1008</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D118" s="1">
         <v>1609</v>
@@ -6668,7 +6669,7 @@
         <v>1019120</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L118" s="1" t="b">
         <v>0</v>
@@ -6679,13 +6680,13 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B119" s="1">
         <v>1008</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D119" s="1">
         <v>1612</v>
@@ -6709,7 +6710,7 @@
         <v>1019120</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L119" s="1" t="b">
         <v>0</v>
@@ -6720,13 +6721,13 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B120" s="1">
         <v>1008</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D120" s="1">
         <v>1613</v>
@@ -6750,7 +6751,7 @@
         <v>1019120</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L120" s="1" t="b">
         <v>0</v>
@@ -6761,13 +6762,13 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B121" s="1">
         <v>1009</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D121" s="1">
         <v>1652</v>
@@ -6791,7 +6792,7 @@
         <v>1019120</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L121" s="1" t="b">
         <v>0</v>
@@ -6802,13 +6803,13 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B122" s="1">
         <v>1009</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D122" s="1">
         <v>1654</v>
@@ -6832,7 +6833,7 @@
         <v>1019120</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L122" s="1" t="b">
         <v>0</v>
@@ -6843,13 +6844,13 @@
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B123" s="1">
         <v>1009</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D123" s="1">
         <v>1702</v>
@@ -6873,7 +6874,7 @@
         <v>1019120</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L123" s="1" t="b">
         <v>0</v>
@@ -6884,13 +6885,13 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B124" s="1">
         <v>1009</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D124" s="1">
         <v>1803</v>
@@ -6914,7 +6915,7 @@
         <v>1019120</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L124" s="1" t="b">
         <v>0</v>
@@ -6925,13 +6926,13 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B125" s="1">
         <v>1010</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D125" s="1">
         <v>22</v>
@@ -6955,7 +6956,7 @@
         <v>1019120</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L125" s="1" t="b">
         <v>0</v>
@@ -6966,13 +6967,13 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B126" s="1">
         <v>1010</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D126" s="1">
         <v>2000</v>
@@ -6996,7 +6997,7 @@
         <v>1019120</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L126" s="1" t="b">
         <v>0</v>
@@ -7007,13 +7008,13 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B127" s="1">
         <v>1010</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D127" s="1">
         <v>2001</v>
@@ -7037,7 +7038,7 @@
         <v>1019120</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L127" s="1" t="b">
         <v>0</v>
@@ -7048,13 +7049,13 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B128" s="1">
         <v>1010</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D128" s="1">
         <v>2002</v>
@@ -7078,7 +7079,7 @@
         <v>1019120</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L128" s="1" t="b">
         <v>0</v>
@@ -7089,13 +7090,13 @@
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B129" s="1">
         <v>1010</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D129" s="1">
         <v>2003</v>
@@ -7119,7 +7120,7 @@
         <v>1019120</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L129" s="1" t="b">
         <v>0</v>
@@ -7130,13 +7131,13 @@
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B130" s="1">
         <v>1010</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D130" s="1">
         <v>298</v>
@@ -7160,7 +7161,7 @@
         <v>1019120</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L130" s="1" t="b">
         <v>0</v>
@@ -7171,13 +7172,13 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B131" s="1">
         <v>1011</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D131" s="1">
         <v>1650</v>
@@ -7212,13 +7213,13 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B132" s="1">
         <v>1011</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D132" s="1">
         <v>1651</v>
@@ -7253,13 +7254,13 @@
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B133" s="1">
         <v>1011</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D133" s="1">
         <v>1700</v>
@@ -7294,13 +7295,13 @@
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B134" s="1">
         <v>1011</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D134" s="1">
         <v>1701</v>
@@ -7335,13 +7336,13 @@
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B135" s="1">
         <v>1011</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D135" s="1">
         <v>1800</v>
@@ -7376,13 +7377,13 @@
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B136" s="1">
         <v>1011</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D136" s="1">
         <v>1802</v>
@@ -7417,13 +7418,13 @@
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B137" s="1">
         <v>1012</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D137" s="1">
         <v>23</v>
@@ -7458,13 +7459,13 @@
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B138" s="1">
         <v>1012</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D138" s="1">
         <v>271</v>
@@ -7499,13 +7500,13 @@
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B139" s="1">
         <v>1012</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D139" s="1">
         <v>277</v>
@@ -7540,13 +7541,13 @@
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B140" s="1">
         <v>1012</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D140" s="1">
         <v>204</v>
@@ -7581,13 +7582,13 @@
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B141" s="1">
         <v>1013</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D141" s="1">
         <v>11</v>
@@ -7611,7 +7612,7 @@
         <v>1019972</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L141" s="1" t="b">
         <v>0</v>
@@ -7622,13 +7623,13 @@
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B142" s="1">
         <v>1013</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D142" s="1">
         <v>295</v>
@@ -7652,7 +7653,7 @@
         <v>1019972</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L142" s="1" t="b">
         <v>0</v>
@@ -7663,13 +7664,13 @@
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B143" s="1">
         <v>1013</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D143" s="1">
         <v>24</v>
@@ -7693,7 +7694,7 @@
         <v>1019972</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L143" s="1" t="b">
         <v>0</v>
@@ -7704,13 +7705,13 @@
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B144" s="1">
         <v>1013</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D144" s="1">
         <v>4000</v>
@@ -7734,7 +7735,7 @@
         <v>1019972</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L144" s="1" t="b">
         <v>0</v>
@@ -7745,13 +7746,13 @@
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B145" s="1">
         <v>1013</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D145" s="1">
         <v>4001</v>
@@ -7775,7 +7776,7 @@
         <v>1019972</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L145" s="1" t="b">
         <v>0</v>
@@ -7786,13 +7787,13 @@
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B146" s="1">
         <v>1013</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D146" s="1">
         <v>4002</v>
@@ -7816,7 +7817,7 @@
         <v>1019972</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L146" s="1" t="b">
         <v>0</v>
@@ -7827,13 +7828,13 @@
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B147" s="1">
         <v>1013</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D147" s="1">
         <v>4003</v>
@@ -7857,7 +7858,7 @@
         <v>1019972</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L147" s="1" t="b">
         <v>0</v>
@@ -7868,13 +7869,13 @@
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B148" s="1">
         <v>1013</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D148" s="1">
         <v>4004</v>
@@ -7898,7 +7899,7 @@
         <v>1019972</v>
       </c>
       <c r="K148" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L148" s="1" t="b">
         <v>0</v>
@@ -7909,13 +7910,13 @@
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B149" s="1">
         <v>1013</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D149" s="1">
         <v>4005</v>
@@ -7939,7 +7940,7 @@
         <v>1019972</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L149" s="1" t="b">
         <v>0</v>
@@ -7950,13 +7951,13 @@
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B150" s="1">
         <v>1013</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D150" s="1">
         <v>4006</v>
@@ -7980,7 +7981,7 @@
         <v>1019972</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L150" s="1" t="b">
         <v>0</v>
@@ -7991,13 +7992,13 @@
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B151" s="1">
         <v>1013</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D151" s="1">
         <v>4007</v>
@@ -8021,7 +8022,7 @@
         <v>1019972</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L151" s="1" t="b">
         <v>0</v>
@@ -8032,13 +8033,13 @@
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B152" s="1">
         <v>1013</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D152" s="1">
         <v>4008</v>
@@ -8062,7 +8063,7 @@
         <v>1019972</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L152" s="1" t="b">
         <v>0</v>
@@ -8073,13 +8074,13 @@
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B153" s="1">
         <v>1013</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D153" s="1">
         <v>4009</v>
@@ -8103,7 +8104,7 @@
         <v>1019972</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L153" s="1" t="b">
         <v>0</v>
@@ -8114,13 +8115,13 @@
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B154" s="1">
         <v>1013</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D154" s="1">
         <v>4010</v>
@@ -8144,7 +8145,7 @@
         <v>1019972</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L154" s="1" t="b">
         <v>0</v>
@@ -8155,13 +8156,13 @@
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B155" s="1">
         <v>1014</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D155" s="1">
         <v>12</v>
@@ -8196,13 +8197,13 @@
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B156" s="1">
         <v>1014</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D156" s="1">
         <v>2004</v>
@@ -8253,20 +8254,20 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" t="s">
         <v>88</v>
-      </c>
-      <c r="B3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -8274,7 +8275,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -8282,7 +8283,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B6">
         <v>21</v>
@@ -8290,7 +8291,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B7">
         <v>22</v>
@@ -8298,7 +8299,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8">
         <v>23</v>
@@ -8306,7 +8307,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9">
         <v>24</v>
@@ -8314,7 +8315,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B10">
         <v>25</v>
@@ -8322,7 +8323,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B11">
         <v>26</v>
@@ -8330,7 +8331,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12">
         <v>27</v>
@@ -8338,7 +8339,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13">
         <v>11</v>
@@ -8346,7 +8347,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B14">
         <v>12</v>
@@ -8354,7 +8355,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B15">
         <v>20</v>
@@ -8362,7 +8363,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B16">
         <v>21</v>
@@ -8370,7 +8371,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17">
         <v>22</v>
@@ -8378,7 +8379,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B18">
         <v>23</v>
@@ -8386,7 +8387,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B19">
         <v>24</v>
@@ -8394,7 +8395,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -8402,7 +8403,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B21">
         <v>101</v>
@@ -8410,7 +8411,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B22">
         <v>102</v>
@@ -8418,7 +8419,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B23">
         <v>103</v>
@@ -8426,7 +8427,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B24">
         <v>104</v>
@@ -8434,7 +8435,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B25">
         <v>105</v>
@@ -8442,7 +8443,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B26">
         <v>200</v>
@@ -8450,7 +8451,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B27">
         <v>201</v>
@@ -8458,7 +8459,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28">
         <v>202</v>
@@ -8466,7 +8467,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B29">
         <v>203</v>
@@ -8474,7 +8475,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B30">
         <v>204</v>
@@ -8482,7 +8483,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31">
         <v>205</v>
@@ -8490,7 +8491,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B32">
         <v>207</v>
@@ -8498,7 +8499,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33">
         <v>208</v>
@@ -8506,7 +8507,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B34">
         <v>210</v>
@@ -8514,7 +8515,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B35">
         <v>211</v>
@@ -8522,7 +8523,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B36">
         <v>212</v>
@@ -8530,7 +8531,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B37">
         <v>213</v>
@@ -8538,7 +8539,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B38">
         <v>214</v>
@@ -8546,7 +8547,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B39">
         <v>215</v>
@@ -8554,7 +8555,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B40">
         <v>216</v>
@@ -8562,7 +8563,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B41">
         <v>217</v>
@@ -8570,7 +8571,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42">
         <v>218</v>
@@ -8578,7 +8579,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B43">
         <v>219</v>
@@ -8586,7 +8587,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B44">
         <v>220</v>
@@ -8594,7 +8595,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B45">
         <v>221</v>
@@ -8602,7 +8603,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B46">
         <v>222</v>
@@ -8610,7 +8611,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B47">
         <v>223</v>
@@ -8618,7 +8619,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B48">
         <v>224</v>
@@ -8626,7 +8627,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B49">
         <v>225</v>
@@ -8634,7 +8635,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B50">
         <v>226</v>
@@ -8642,7 +8643,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B51">
         <v>227</v>
@@ -8650,7 +8651,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B52">
         <v>228</v>
@@ -8658,7 +8659,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B53">
         <v>229</v>
@@ -8666,7 +8667,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B54">
         <v>230</v>
@@ -8674,7 +8675,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B55">
         <v>232</v>
@@ -8682,7 +8683,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B56">
         <v>234</v>
@@ -8690,7 +8691,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B57">
         <v>235</v>
@@ -8698,7 +8699,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B58">
         <v>236</v>
@@ -8706,7 +8707,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B59">
         <v>237</v>
@@ -8714,7 +8715,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B60">
         <v>238</v>
@@ -8722,7 +8723,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B61">
         <v>239</v>
@@ -8730,7 +8731,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B62">
         <v>240</v>
@@ -8738,7 +8739,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B63">
         <v>241</v>
@@ -8746,7 +8747,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B64">
         <v>242</v>
@@ -8754,7 +8755,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B65">
         <v>243</v>
@@ -8762,7 +8763,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B66">
         <v>244</v>
@@ -8770,7 +8771,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B67">
         <v>245</v>
@@ -8778,7 +8779,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B68">
         <v>246</v>
@@ -8786,7 +8787,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B69">
         <v>247</v>
@@ -8794,7 +8795,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B70">
         <v>248</v>
@@ -8802,7 +8803,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B71">
         <v>249</v>
@@ -8810,7 +8811,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B72">
         <v>250</v>
@@ -8818,7 +8819,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B73">
         <v>251</v>
@@ -8826,7 +8827,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B74">
         <v>253</v>
@@ -8834,7 +8835,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B75">
         <v>254</v>
@@ -8842,7 +8843,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B76">
         <v>255</v>
@@ -8850,7 +8851,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B77">
         <v>256</v>
@@ -8858,7 +8859,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B78">
         <v>257</v>
@@ -8866,7 +8867,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B79">
         <v>258</v>
@@ -8874,7 +8875,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B80">
         <v>259</v>
@@ -8882,7 +8883,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B81">
         <v>260</v>
@@ -8890,7 +8891,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B82">
         <v>261</v>
@@ -8898,7 +8899,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B83">
         <v>263</v>
@@ -8906,7 +8907,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B84">
         <v>264</v>
@@ -8914,7 +8915,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B85">
         <v>265</v>
@@ -8922,7 +8923,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B86">
         <v>266</v>
@@ -8930,7 +8931,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B87">
         <v>267</v>
@@ -8938,7 +8939,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B88">
         <v>268</v>
@@ -8946,7 +8947,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B89">
         <v>269</v>
@@ -8954,7 +8955,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B90">
         <v>270</v>
@@ -8962,7 +8963,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B91">
         <v>271</v>
@@ -8970,7 +8971,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B92">
         <v>272</v>
@@ -8978,7 +8979,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B93">
         <v>273</v>
@@ -8986,7 +8987,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B94">
         <v>274</v>
@@ -8994,7 +8995,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B95">
         <v>275</v>
@@ -9002,7 +9003,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B96">
         <v>276</v>
@@ -9010,7 +9011,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B97">
         <v>277</v>
@@ -9018,7 +9019,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B98">
         <v>278</v>
@@ -9026,7 +9027,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B99">
         <v>279</v>
@@ -9034,7 +9035,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B100">
         <v>280</v>
@@ -9042,7 +9043,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B101">
         <v>281</v>
@@ -9050,7 +9051,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B102">
         <v>282</v>
@@ -9058,7 +9059,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B103">
         <v>283</v>
@@ -9066,7 +9067,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B104">
         <v>284</v>
@@ -9074,7 +9075,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B105">
         <v>285</v>
@@ -9082,7 +9083,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B106">
         <v>286</v>
@@ -9090,7 +9091,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B107">
         <v>287</v>
@@ -9098,7 +9099,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B108">
         <v>288</v>
@@ -9106,7 +9107,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B109">
         <v>289</v>
@@ -9114,7 +9115,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B110">
         <v>290</v>
@@ -9122,7 +9123,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B111">
         <v>291</v>
@@ -9130,7 +9131,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B112">
         <v>292</v>
@@ -9138,7 +9139,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B113">
         <v>293</v>
@@ -9146,7 +9147,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B114">
         <v>294</v>
@@ -9154,7 +9155,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B115">
         <v>295</v>
@@ -9162,7 +9163,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B116">
         <v>296</v>
@@ -9170,7 +9171,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B117">
         <v>297</v>
@@ -9178,7 +9179,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B118">
         <v>298</v>
@@ -9186,7 +9187,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B119">
         <v>299</v>
@@ -9194,7 +9195,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B120">
         <v>300</v>
@@ -9202,7 +9203,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B121">
         <v>301</v>
@@ -9210,7 +9211,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B122">
         <v>302</v>
@@ -9218,7 +9219,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B123">
         <v>1001</v>
@@ -9226,7 +9227,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B124">
         <v>1002</v>
@@ -9234,7 +9235,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B125">
         <v>1003</v>
@@ -9242,7 +9243,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B126">
         <v>1004</v>
@@ -9250,7 +9251,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B127">
         <v>1005</v>
@@ -9258,7 +9259,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B128">
         <v>1006</v>
@@ -9266,7 +9267,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B129">
         <v>1007</v>
@@ -9274,7 +9275,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B130">
         <v>1008</v>
@@ -9282,7 +9283,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B131">
         <v>1009</v>
@@ -9290,7 +9291,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B132">
         <v>1010</v>
@@ -9298,7 +9299,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B133">
         <v>1011</v>
@@ -9306,7 +9307,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B134">
         <v>1012</v>
@@ -9314,7 +9315,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B135">
         <v>1013</v>
@@ -9322,7 +9323,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B136">
         <v>1014</v>
@@ -9330,7 +9331,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B137">
         <v>1015</v>
@@ -9338,7 +9339,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B138">
         <v>1016</v>
@@ -9346,7 +9347,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B139">
         <v>1017</v>
@@ -9354,7 +9355,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B140">
         <v>1018</v>
@@ -9362,7 +9363,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B141">
         <v>1019</v>
@@ -9370,7 +9371,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B142">
         <v>1020</v>
@@ -9378,7 +9379,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B143">
         <v>1021</v>
@@ -9386,7 +9387,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B144">
         <v>1022</v>
@@ -9394,7 +9395,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B145">
         <v>1023</v>
@@ -9402,7 +9403,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B146">
         <v>1024</v>
@@ -9410,7 +9411,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B147">
         <v>1025</v>
@@ -9418,7 +9419,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B148">
         <v>1026</v>
@@ -9426,7 +9427,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B149">
         <v>1027</v>
@@ -9434,7 +9435,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B150">
         <v>1028</v>
@@ -9442,7 +9443,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B151">
         <v>1101</v>
@@ -9450,7 +9451,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B152">
         <v>1102</v>
@@ -9458,7 +9459,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B153">
         <v>1103</v>
@@ -9466,7 +9467,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B154">
         <v>1104</v>
@@ -9474,7 +9475,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B155">
         <v>1105</v>
@@ -9482,7 +9483,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B156">
         <v>1106</v>
@@ -9490,7 +9491,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B157">
         <v>1107</v>
@@ -9498,7 +9499,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B158">
         <v>1108</v>
@@ -9506,7 +9507,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B159">
         <v>1109</v>
@@ -9514,7 +9515,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B160">
         <v>1110</v>
@@ -9522,7 +9523,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B161">
         <v>1111</v>
@@ -9530,7 +9531,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B162">
         <v>1112</v>
@@ -9538,7 +9539,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B163">
         <v>1113</v>
@@ -9546,7 +9547,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B164">
         <v>1114</v>
@@ -9554,7 +9555,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B165">
         <v>1115</v>
@@ -9562,7 +9563,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B166">
         <v>1116</v>
@@ -9570,7 +9571,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B167">
         <v>1117</v>
@@ -9578,7 +9579,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B168">
         <v>1118</v>
@@ -9586,7 +9587,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B169">
         <v>1119</v>
@@ -9594,7 +9595,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B170">
         <v>1120</v>
@@ -9602,7 +9603,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B171">
         <v>1121</v>
@@ -9610,7 +9611,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B172">
         <v>1122</v>
@@ -9618,7 +9619,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B173">
         <v>1123</v>
@@ -9626,7 +9627,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B174">
         <v>1124</v>
@@ -9634,7 +9635,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B175">
         <v>1125</v>
@@ -9642,7 +9643,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B176">
         <v>1126</v>
@@ -9650,7 +9651,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B177">
         <v>1127</v>
@@ -9658,7 +9659,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B178">
         <v>1128</v>
@@ -9666,7 +9667,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B179">
         <v>1600</v>
@@ -9674,7 +9675,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B180">
         <v>1601</v>
@@ -9682,7 +9683,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B181">
         <v>1602</v>
@@ -9690,7 +9691,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B182">
         <v>1603</v>
@@ -9698,7 +9699,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B183">
         <v>1604</v>
@@ -9706,7 +9707,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B184">
         <v>1605</v>
@@ -9714,7 +9715,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B185">
         <v>1606</v>
@@ -9722,7 +9723,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B186">
         <v>1607</v>
@@ -9730,7 +9731,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B187">
         <v>1608</v>
@@ -9738,7 +9739,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B188">
         <v>1609</v>
@@ -9746,7 +9747,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B189">
         <v>1610</v>
@@ -9754,7 +9755,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B190">
         <v>1611</v>
@@ -9762,7 +9763,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B191">
         <v>1612</v>
@@ -9770,7 +9771,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B192">
         <v>1613</v>
@@ -9778,7 +9779,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B193">
         <v>1614</v>
@@ -9786,7 +9787,7 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B194">
         <v>1615</v>
@@ -9794,7 +9795,7 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B195">
         <v>1616</v>
@@ -9802,7 +9803,7 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B196">
         <v>1617</v>
@@ -9810,7 +9811,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B197">
         <v>1618</v>
@@ -9818,7 +9819,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B198">
         <v>1619</v>
@@ -9826,7 +9827,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B199">
         <v>1620</v>
@@ -9834,7 +9835,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B200">
         <v>1650</v>
@@ -9842,7 +9843,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B201">
         <v>1651</v>
@@ -9850,7 +9851,7 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B202">
         <v>1652</v>
@@ -9858,7 +9859,7 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B203">
         <v>1653</v>
@@ -9866,7 +9867,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B204">
         <v>1654</v>
@@ -9874,7 +9875,7 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B205">
         <v>1655</v>
@@ -9882,7 +9883,7 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B206">
         <v>1656</v>
@@ -9890,7 +9891,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B207">
         <v>1657</v>
@@ -9898,7 +9899,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B208">
         <v>1658</v>
@@ -9906,7 +9907,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B209">
         <v>1659</v>
@@ -9914,7 +9915,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B210">
         <v>1660</v>
@@ -9922,7 +9923,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B211">
         <v>1661</v>
@@ -9930,7 +9931,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B212">
         <v>1662</v>
@@ -9938,7 +9939,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B213">
         <v>1663</v>
@@ -9946,7 +9947,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B214">
         <v>1664</v>
@@ -9954,7 +9955,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B215">
         <v>1665</v>
@@ -9962,7 +9963,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B216">
         <v>1666</v>
@@ -9970,7 +9971,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B217">
         <v>1700</v>
@@ -9978,7 +9979,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B218">
         <v>1701</v>
@@ -9986,7 +9987,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B219">
         <v>1702</v>
@@ -9994,7 +9995,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B220">
         <v>1703</v>
@@ -10002,7 +10003,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B221">
         <v>1704</v>
@@ -10010,7 +10011,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B222">
         <v>1705</v>
@@ -10018,7 +10019,7 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B223">
         <v>1706</v>
@@ -10026,7 +10027,7 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B224">
         <v>1707</v>
@@ -10034,7 +10035,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B225">
         <v>1708</v>
@@ -10042,7 +10043,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B226">
         <v>1709</v>
@@ -10050,7 +10051,7 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B227">
         <v>1710</v>
@@ -10058,7 +10059,7 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B228">
         <v>1800</v>
@@ -10066,7 +10067,7 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B229">
         <v>1801</v>
@@ -10074,7 +10075,7 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B230">
         <v>1802</v>
@@ -10082,7 +10083,7 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B231">
         <v>1803</v>
@@ -10090,7 +10091,7 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B232">
         <v>1804</v>
@@ -10098,7 +10099,7 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B233">
         <v>1805</v>
@@ -10106,7 +10107,7 @@
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B234">
         <v>1806</v>
@@ -10114,7 +10115,7 @@
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B235">
         <v>1807</v>
@@ -10122,7 +10123,7 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B236">
         <v>1808</v>
@@ -10130,7 +10131,7 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B237">
         <v>2000</v>
@@ -10138,7 +10139,7 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B238">
         <v>2001</v>
@@ -10146,7 +10147,7 @@
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B239">
         <v>2002</v>
@@ -10154,7 +10155,7 @@
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B240">
         <v>2003</v>
@@ -10162,7 +10163,7 @@
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B241">
         <v>2004</v>
@@ -10170,7 +10171,7 @@
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B242">
         <v>2100</v>
@@ -10178,7 +10179,7 @@
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B243">
         <v>2101</v>
@@ -10186,7 +10187,7 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B244">
         <v>2102</v>
@@ -10194,7 +10195,7 @@
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B245">
         <v>2103</v>
@@ -10202,7 +10203,7 @@
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B246">
         <v>2104</v>
@@ -10210,7 +10211,7 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B247">
         <v>2105</v>
@@ -10218,7 +10219,7 @@
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B248">
         <v>2106</v>
@@ -10226,7 +10227,7 @@
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B249">
         <v>2107</v>
@@ -10234,7 +10235,7 @@
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B250">
         <v>2108</v>
@@ -10242,7 +10243,7 @@
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B251">
         <v>2109</v>
@@ -10250,7 +10251,7 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B252">
         <v>2110</v>
@@ -10258,7 +10259,7 @@
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B253">
         <v>2111</v>
@@ -10266,7 +10267,7 @@
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B254">
         <v>2113</v>
@@ -10274,7 +10275,7 @@
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B255">
         <v>2200</v>
@@ -10282,7 +10283,7 @@
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B256">
         <v>2114</v>
@@ -10290,7 +10291,7 @@
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B257">
         <v>2201</v>
@@ -10298,7 +10299,7 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B258">
         <v>4000</v>
@@ -10306,7 +10307,7 @@
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B259">
         <v>4003</v>
@@ -10314,7 +10315,7 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B260">
         <v>4004</v>
@@ -10322,7 +10323,7 @@
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B261">
         <v>4006</v>
@@ -10330,7 +10331,7 @@
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B262">
         <v>4007</v>
@@ -10338,7 +10339,7 @@
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B263">
         <v>4008</v>
@@ -10346,7 +10347,7 @@
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B264">
         <v>4009</v>
@@ -10354,7 +10355,7 @@
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B265">
         <v>4010</v>
@@ -10362,7 +10363,7 @@
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B266">
         <v>4011</v>
@@ -10370,7 +10371,7 @@
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B267">
         <v>4012</v>
@@ -10378,7 +10379,7 @@
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B268">
         <v>4013</v>
@@ -10386,7 +10387,7 @@
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B269">
         <v>4014</v>
@@ -10394,7 +10395,7 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B270">
         <v>4015</v>
@@ -10402,7 +10403,7 @@
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B271">
         <v>4016</v>
@@ -10410,7 +10411,7 @@
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B272">
         <v>4017</v>
@@ -10418,7 +10419,7 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B273">
         <v>4018</v>
@@ -10426,7 +10427,7 @@
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B274">
         <v>4020</v>
@@ -10434,7 +10435,7 @@
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B275">
         <v>4021</v>
@@ -10442,7 +10443,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B276">
         <v>4022</v>
@@ -10450,7 +10451,7 @@
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B277">
         <v>4023</v>
@@ -10458,7 +10459,7 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B278">
         <v>4024</v>
@@ -10466,7 +10467,7 @@
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B279">
         <v>4100</v>
@@ -10474,7 +10475,7 @@
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B280">
         <v>4101</v>
@@ -10482,7 +10483,7 @@
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B281">
         <v>4103</v>
@@ -10490,7 +10491,7 @@
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B282">
         <v>4105</v>
@@ -10498,7 +10499,7 @@
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B283">
         <v>4106</v>
@@ -10506,7 +10507,7 @@
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B284">
         <v>4109</v>
@@ -10514,7 +10515,7 @@
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B285">
         <v>4110</v>
@@ -10522,7 +10523,7 @@
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B286">
         <v>4111</v>
@@ -10530,7 +10531,7 @@
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B287">
         <v>4112</v>
@@ -10538,7 +10539,7 @@
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B288">
         <v>4113</v>
@@ -10546,7 +10547,7 @@
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B289">
         <v>4114</v>
@@ -10554,7 +10555,7 @@
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B290">
         <v>4115</v>
@@ -10562,7 +10563,7 @@
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B291">
         <v>4116</v>
@@ -10570,7 +10571,7 @@
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B292">
         <v>4117</v>
@@ -10578,7 +10579,7 @@
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B293">
         <v>3000</v>
@@ -10586,7 +10587,7 @@
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B294">
         <v>3001</v>
@@ -10594,7 +10595,7 @@
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B295">
         <v>3002</v>
@@ -10602,7 +10603,7 @@
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B296">
         <v>3003</v>
@@ -10610,7 +10611,7 @@
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B297">
         <v>3005</v>
@@ -10618,7 +10619,7 @@
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B298">
         <v>3006</v>
@@ -10626,7 +10627,7 @@
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B299">
         <v>3007</v>
@@ -10634,7 +10635,7 @@
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B300">
         <v>3008</v>
@@ -10642,7 +10643,7 @@
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B301">
         <v>3009</v>
@@ -10650,7 +10651,7 @@
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B302">
         <v>3010</v>
@@ -10658,7 +10659,7 @@
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B303">
         <v>3011</v>
@@ -10666,7 +10667,7 @@
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B304">
         <v>3011</v>
@@ -10674,7 +10675,7 @@
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B305">
         <v>3100</v>
@@ -10682,7 +10683,7 @@
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B306">
         <v>3101</v>
@@ -10690,7 +10691,7 @@
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B307">
         <v>3102</v>
@@ -10698,7 +10699,7 @@
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B308">
         <v>3103</v>
@@ -10706,7 +10707,7 @@
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B309">
         <v>3104</v>
@@ -10714,7 +10715,7 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B310">
         <v>3105</v>
@@ -10722,7 +10723,7 @@
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B311">
         <v>3106</v>
@@ -10730,7 +10731,7 @@
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B312">
         <v>3107</v>
@@ -10738,7 +10739,7 @@
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B313">
         <v>3108</v>
@@ -10746,7 +10747,7 @@
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B314">
         <v>3109</v>
@@ -10754,7 +10755,7 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B315">
         <v>3110</v>
@@ -10762,7 +10763,7 @@
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B316">
         <v>3111</v>
@@ -10770,7 +10771,7 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B317">
         <v>3112</v>
@@ -10778,7 +10779,7 @@
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B318">
         <v>3113</v>
@@ -10786,7 +10787,7 @@
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B319">
         <v>3114</v>
@@ -10794,7 +10795,7 @@
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B320">
         <v>3115</v>
@@ -10802,7 +10803,7 @@
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B321">
         <v>3116</v>
@@ -10810,7 +10811,7 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B322">
         <v>3117</v>
@@ -10818,7 +10819,7 @@
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B323">
         <v>3118</v>
@@ -10826,7 +10827,7 @@
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B324">
         <v>3119</v>
@@ -10834,7 +10835,7 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B325">
         <v>3120</v>
@@ -10842,7 +10843,7 @@
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B326">
         <v>3121</v>
@@ -10850,7 +10851,7 @@
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B327">
         <v>3122</v>
@@ -10858,7 +10859,7 @@
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B328">
         <v>3123</v>
@@ -10866,7 +10867,7 @@
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B329">
         <v>3124</v>
@@ -10874,7 +10875,7 @@
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B330">
         <v>3125</v>
@@ -10882,7 +10883,7 @@
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B331">
         <v>3126</v>
@@ -10890,7 +10891,7 @@
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B332">
         <v>3127</v>
@@ -10898,7 +10899,7 @@
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B333">
         <v>3128</v>
@@ -10906,7 +10907,7 @@
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B334">
         <v>3129</v>
@@ -10914,7 +10915,7 @@
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B335">
         <v>3130</v>
@@ -10922,7 +10923,7 @@
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B336">
         <v>3131</v>
@@ -10930,7 +10931,7 @@
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B337">
         <v>3132</v>
@@ -10938,7 +10939,7 @@
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B338">
         <v>3133</v>
@@ -10946,7 +10947,7 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B339">
         <v>3134</v>
@@ -10954,7 +10955,7 @@
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B340">
         <v>3135</v>
@@ -10962,7 +10963,7 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B341">
         <v>3136</v>
@@ -10970,7 +10971,7 @@
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B342">
         <v>3137</v>
@@ -10978,7 +10979,7 @@
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B343">
         <v>3138</v>
@@ -10986,7 +10987,7 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B344">
         <v>3139</v>
@@ -10994,7 +10995,7 @@
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B345">
         <v>3140</v>
@@ -11002,7 +11003,7 @@
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B346">
         <v>3141</v>
@@ -11010,7 +11011,7 @@
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B347">
         <v>3142</v>
@@ -11018,7 +11019,7 @@
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B348">
         <v>3143</v>
@@ -11026,7 +11027,7 @@
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B349">
         <v>3144</v>
@@ -11034,7 +11035,7 @@
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B350">
         <v>3145</v>
@@ -11042,7 +11043,7 @@
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B351">
         <v>3146</v>
@@ -11050,7 +11051,7 @@
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B352">
         <v>3147</v>
@@ -11058,7 +11059,7 @@
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B353">
         <v>3148</v>
@@ -11066,7 +11067,7 @@
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B354">
         <v>3149</v>
@@ -11074,7 +11075,7 @@
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B355">
         <v>3150</v>
@@ -11082,7 +11083,7 @@
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B356">
         <v>3151</v>
@@ -11090,7 +11091,7 @@
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B357">
         <v>3152</v>
@@ -11098,7 +11099,7 @@
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B358">
         <v>3153</v>
@@ -11106,7 +11107,7 @@
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B359">
         <v>3154</v>
@@ -11114,7 +11115,7 @@
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B360">
         <v>3155</v>
@@ -11122,7 +11123,7 @@
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B361">
         <v>3156</v>
@@ -11130,7 +11131,7 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B362">
         <v>3157</v>
@@ -11138,7 +11139,7 @@
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B363">
         <v>3158</v>
@@ -11146,7 +11147,7 @@
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B364">
         <v>3159</v>
@@ -11154,7 +11155,7 @@
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B365">
         <v>3160</v>
@@ -11162,7 +11163,7 @@
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B366">
         <v>3161</v>
@@ -11170,7 +11171,7 @@
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B367">
         <v>3162</v>
@@ -11178,7 +11179,7 @@
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B368">
         <v>3163</v>
@@ -11186,7 +11187,7 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B369">
         <v>3164</v>
@@ -11194,7 +11195,7 @@
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B370">
         <v>3165</v>
@@ -11202,7 +11203,7 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B371">
         <v>3166</v>
@@ -11210,7 +11211,7 @@
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B372">
         <v>3167</v>
@@ -11218,7 +11219,7 @@
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B373">
         <v>3168</v>
@@ -11226,7 +11227,7 @@
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B374">
         <v>3169</v>
@@ -11234,7 +11235,7 @@
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B375">
         <v>3170</v>
@@ -11242,7 +11243,7 @@
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B376">
         <v>3171</v>
@@ -11250,7 +11251,7 @@
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B377">
         <v>3172</v>
@@ -11258,7 +11259,7 @@
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B378">
         <v>3173</v>
@@ -11266,7 +11267,7 @@
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B379">
         <v>3174</v>
@@ -11274,7 +11275,7 @@
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B380">
         <v>3175</v>
@@ -11282,7 +11283,7 @@
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B381">
         <v>3176</v>
@@ -11290,7 +11291,7 @@
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B382">
         <v>3177</v>
@@ -11298,7 +11299,7 @@
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B383">
         <v>3178</v>
@@ -11306,7 +11307,7 @@
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B384">
         <v>3179</v>
@@ -11314,7 +11315,7 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B385">
         <v>4000</v>
@@ -11322,7 +11323,7 @@
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B386">
         <v>4001</v>
@@ -11330,7 +11331,7 @@
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B387">
         <v>4002</v>
@@ -11338,7 +11339,7 @@
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B388">
         <v>4003</v>
@@ -11346,7 +11347,7 @@
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B389">
         <v>4004</v>
@@ -11354,7 +11355,7 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B390">
         <v>4005</v>
@@ -11362,7 +11363,7 @@
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B391">
         <v>4006</v>
@@ -11370,7 +11371,7 @@
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B392">
         <v>4007</v>
@@ -11378,7 +11379,7 @@
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B393">
         <v>4008</v>
@@ -11386,7 +11387,7 @@
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B394">
         <v>4009</v>
@@ -11394,7 +11395,7 @@
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B395">
         <v>4010</v>
@@ -11413,31 +11414,31 @@
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
         <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
       </c>
       <c r="H2" t="s">
         <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N2" t="s">
         <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N2" t="s">
-        <v>26</v>
       </c>
       <c r="O2">
         <v>41</v>
@@ -11445,27 +11446,27 @@
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" t="s">
         <v>27</v>
-      </c>
-      <c r="D24" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" t="s">
-        <v>28</v>
       </c>
       <c r="H24">
         <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.2">
       <c r="D26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="3:7" x14ac:dyDescent="0.2">

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="457">
   <si>
     <t>string</t>
   </si>
@@ -1863,7 +1863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -7057,8 +7057,8 @@
       <c r="C128" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D128" s="1">
-        <v>2002</v>
+      <c r="D128" s="5">
+        <v>2115</v>
       </c>
       <c r="E128" s="1">
         <v>0</v>
@@ -7098,8 +7098,8 @@
       <c r="C129" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D129" s="1">
-        <v>2003</v>
+      <c r="D129" s="5">
+        <v>2116</v>
       </c>
       <c r="E129" s="1">
         <v>0</v>
@@ -7140,7 +7140,7 @@
         <v>44</v>
       </c>
       <c r="D130" s="1">
-        <v>298</v>
+        <v>2002</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -7172,16 +7172,16 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B131" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D131" s="1">
-        <v>1650</v>
+        <v>2003</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -7196,13 +7196,13 @@
         <v>1</v>
       </c>
       <c r="I131" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J131" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K131" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="L131" s="1" t="b">
         <v>0</v>
@@ -7213,16 +7213,16 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B132" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D132" s="1">
-        <v>1651</v>
+        <v>298</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -7237,13 +7237,13 @@
         <v>1</v>
       </c>
       <c r="I132" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J132" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K132" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="L132" s="1" t="b">
         <v>0</v>
@@ -7263,7 +7263,7 @@
         <v>25</v>
       </c>
       <c r="D133" s="1">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>25</v>
       </c>
       <c r="D134" s="1">
-        <v>1701</v>
+        <v>1651</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -7345,7 +7345,7 @@
         <v>25</v>
       </c>
       <c r="D135" s="1">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
@@ -7386,7 +7386,7 @@
         <v>25</v>
       </c>
       <c r="D136" s="1">
-        <v>1802</v>
+        <v>1701</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
@@ -7418,16 +7418,16 @@
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="B137" s="1">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D137" s="1">
-        <v>23</v>
+        <v>1800</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -7459,16 +7459,16 @@
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="B138" s="1">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D138" s="1">
-        <v>271</v>
+        <v>1802</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -7509,7 +7509,7 @@
         <v>25</v>
       </c>
       <c r="D139" s="1">
-        <v>277</v>
+        <v>23</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -7550,7 +7550,7 @@
         <v>25</v>
       </c>
       <c r="D140" s="1">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -7582,16 +7582,16 @@
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="B141" s="1">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D141" s="1">
-        <v>11</v>
+        <v>277</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
@@ -7606,13 +7606,13 @@
         <v>1</v>
       </c>
       <c r="I141" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J141" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K141" s="1" t="s">
-        <v>36</v>
+        <v>1159783</v>
+      </c>
+      <c r="K141" s="1">
+        <v>41</v>
       </c>
       <c r="L141" s="1" t="b">
         <v>0</v>
@@ -7623,16 +7623,16 @@
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="B142" s="1">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D142" s="1">
-        <v>295</v>
+        <v>204</v>
       </c>
       <c r="E142" s="1">
         <v>0</v>
@@ -7647,13 +7647,13 @@
         <v>1</v>
       </c>
       <c r="I142" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J142" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K142" s="1" t="s">
-        <v>36</v>
+        <v>1159783</v>
+      </c>
+      <c r="K142" s="1">
+        <v>41</v>
       </c>
       <c r="L142" s="1" t="b">
         <v>0</v>
@@ -7673,7 +7673,7 @@
         <v>47</v>
       </c>
       <c r="D143" s="1">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E143" s="1">
         <v>0</v>
@@ -7714,7 +7714,7 @@
         <v>47</v>
       </c>
       <c r="D144" s="1">
-        <v>4000</v>
+        <v>295</v>
       </c>
       <c r="E144" s="1">
         <v>0</v>
@@ -7726,7 +7726,7 @@
         <v>100</v>
       </c>
       <c r="H144" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I144" s="1">
         <v>3056</v>
@@ -7755,7 +7755,7 @@
         <v>47</v>
       </c>
       <c r="D145" s="1">
-        <v>4001</v>
+        <v>24</v>
       </c>
       <c r="E145" s="1">
         <v>0</v>
@@ -7767,7 +7767,7 @@
         <v>100</v>
       </c>
       <c r="H145" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I145" s="1">
         <v>3056</v>
@@ -7796,7 +7796,7 @@
         <v>47</v>
       </c>
       <c r="D146" s="1">
-        <v>4002</v>
+        <v>4000</v>
       </c>
       <c r="E146" s="1">
         <v>0</v>
@@ -7808,7 +7808,7 @@
         <v>100</v>
       </c>
       <c r="H146" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I146" s="1">
         <v>3056</v>
@@ -7837,7 +7837,7 @@
         <v>47</v>
       </c>
       <c r="D147" s="1">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="E147" s="1">
         <v>0</v>
@@ -7849,7 +7849,7 @@
         <v>100</v>
       </c>
       <c r="H147" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I147" s="1">
         <v>3056</v>
@@ -7878,7 +7878,7 @@
         <v>47</v>
       </c>
       <c r="D148" s="1">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="E148" s="1">
         <v>0</v>
@@ -7919,7 +7919,7 @@
         <v>47</v>
       </c>
       <c r="D149" s="1">
-        <v>4005</v>
+        <v>4003</v>
       </c>
       <c r="E149" s="1">
         <v>0</v>
@@ -7960,7 +7960,7 @@
         <v>47</v>
       </c>
       <c r="D150" s="1">
-        <v>4006</v>
+        <v>4004</v>
       </c>
       <c r="E150" s="1">
         <v>0</v>
@@ -8001,7 +8001,7 @@
         <v>47</v>
       </c>
       <c r="D151" s="1">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="E151" s="1">
         <v>0</v>
@@ -8013,7 +8013,7 @@
         <v>100</v>
       </c>
       <c r="H151" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I151" s="1">
         <v>3056</v>
@@ -8042,7 +8042,7 @@
         <v>47</v>
       </c>
       <c r="D152" s="1">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="E152" s="1">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>100</v>
       </c>
       <c r="H152" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I152" s="1">
         <v>3056</v>
@@ -8083,7 +8083,7 @@
         <v>47</v>
       </c>
       <c r="D153" s="1">
-        <v>4009</v>
+        <v>4007</v>
       </c>
       <c r="E153" s="1">
         <v>0</v>
@@ -8124,7 +8124,7 @@
         <v>47</v>
       </c>
       <c r="D154" s="1">
-        <v>4010</v>
+        <v>4008</v>
       </c>
       <c r="E154" s="1">
         <v>0</v>
@@ -8136,7 +8136,7 @@
         <v>100</v>
       </c>
       <c r="H154" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I154" s="1">
         <v>3056</v>
@@ -8156,16 +8156,16 @@
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B155" s="1">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D155" s="1">
-        <v>12</v>
+        <v>4009</v>
       </c>
       <c r="E155" s="1">
         <v>0</v>
@@ -8177,16 +8177,16 @@
         <v>100</v>
       </c>
       <c r="H155" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I155" s="1">
-        <v>2497</v>
+        <v>3056</v>
       </c>
       <c r="J155" s="1">
-        <v>1116139</v>
-      </c>
-      <c r="K155" s="1">
-        <v>26</v>
+        <v>1019972</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="L155" s="1" t="b">
         <v>0</v>
@@ -8197,16 +8197,16 @@
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B156" s="1">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D156" s="1">
-        <v>2004</v>
+        <v>4010</v>
       </c>
       <c r="E156" s="1">
         <v>0</v>
@@ -8221,18 +8221,100 @@
         <v>1</v>
       </c>
       <c r="I156" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J156" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K156" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L156" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M156" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B157" s="1">
+        <v>1014</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D157" s="1">
+        <v>12</v>
+      </c>
+      <c r="E157" s="1">
+        <v>0</v>
+      </c>
+      <c r="F157" s="1">
+        <v>0</v>
+      </c>
+      <c r="G157" s="1">
+        <v>100</v>
+      </c>
+      <c r="H157" s="1">
+        <v>1</v>
+      </c>
+      <c r="I157" s="1">
         <v>2497</v>
       </c>
-      <c r="J156" s="1">
+      <c r="J157" s="1">
         <v>1116139</v>
       </c>
-      <c r="K156" s="1">
+      <c r="K157" s="1">
         <v>26</v>
       </c>
-      <c r="L156" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M156" s="1">
+      <c r="L157" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M157" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A158" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B158" s="1">
+        <v>1014</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D158" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E158" s="1">
+        <v>0</v>
+      </c>
+      <c r="F158" s="1">
+        <v>0</v>
+      </c>
+      <c r="G158" s="1">
+        <v>100</v>
+      </c>
+      <c r="H158" s="1">
+        <v>1</v>
+      </c>
+      <c r="I158" s="1">
+        <v>2497</v>
+      </c>
+      <c r="J158" s="1">
+        <v>1116139</v>
+      </c>
+      <c r="K158" s="1">
+        <v>26</v>
+      </c>
+      <c r="L158" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M158" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="458">
   <si>
     <t>string</t>
   </si>
@@ -1496,6 +1496,10 @@
   </si>
   <si>
     <t>buyLimitOne</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>杂物</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4516,7 +4520,7 @@
         <v>14</v>
       </c>
       <c r="D66" s="3">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
@@ -4528,7 +4532,7 @@
         <v>100</v>
       </c>
       <c r="H66" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I66" s="1">
         <v>1014</v>
@@ -4557,7 +4561,7 @@
         <v>14</v>
       </c>
       <c r="D67" s="3">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
@@ -4569,7 +4573,7 @@
         <v>100</v>
       </c>
       <c r="H67" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I67" s="1">
         <v>1014</v>
@@ -4598,7 +4602,7 @@
         <v>14</v>
       </c>
       <c r="D68" s="3">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
@@ -4610,7 +4614,7 @@
         <v>100</v>
       </c>
       <c r="H68" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I68" s="1">
         <v>1014</v>
@@ -4639,7 +4643,7 @@
         <v>14</v>
       </c>
       <c r="D69" s="3">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
@@ -4651,7 +4655,7 @@
         <v>100</v>
       </c>
       <c r="H69" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I69" s="1">
         <v>1014</v>
@@ -4680,7 +4684,7 @@
         <v>14</v>
       </c>
       <c r="D70" s="3">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
@@ -4692,7 +4696,7 @@
         <v>100</v>
       </c>
       <c r="H70" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I70" s="1">
         <v>1014</v>
@@ -4721,7 +4725,7 @@
         <v>14</v>
       </c>
       <c r="D71" s="3">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
@@ -4761,8 +4765,8 @@
       <c r="C72" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D72" s="3">
-        <v>2113</v>
+      <c r="D72" s="4">
+        <v>2114</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
@@ -4774,7 +4778,7 @@
         <v>100</v>
       </c>
       <c r="H72" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" s="1">
         <v>1014</v>
@@ -4794,16 +4798,16 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B73" s="1">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D73" s="4">
-        <v>2114</v>
+      <c r="D73" s="5">
+        <v>2200</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
@@ -4815,7 +4819,7 @@
         <v>100</v>
       </c>
       <c r="H73" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73" s="1">
         <v>1014</v>
@@ -4844,7 +4848,7 @@
         <v>14</v>
       </c>
       <c r="D74" s="5">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -4885,7 +4889,7 @@
         <v>14</v>
       </c>
       <c r="D75" s="5">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
@@ -4926,7 +4930,7 @@
         <v>14</v>
       </c>
       <c r="D76" s="5">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
@@ -4967,7 +4971,7 @@
         <v>14</v>
       </c>
       <c r="D77" s="5">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
@@ -5008,7 +5012,7 @@
         <v>14</v>
       </c>
       <c r="D78" s="5">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
@@ -5049,7 +5053,7 @@
         <v>14</v>
       </c>
       <c r="D79" s="5">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="E79" s="1">
         <v>2</v>
@@ -5090,7 +5094,7 @@
         <v>14</v>
       </c>
       <c r="D80" s="5">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
@@ -5131,7 +5135,7 @@
         <v>14</v>
       </c>
       <c r="D81" s="5">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
@@ -5172,7 +5176,7 @@
         <v>14</v>
       </c>
       <c r="D82" s="5">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
@@ -5204,21 +5208,21 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B83" s="1">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" s="5">
-        <v>2209</v>
+        <v>21</v>
+      </c>
+      <c r="D83" s="1">
+        <v>3500</v>
       </c>
       <c r="E83" s="1">
-        <v>2</v>
-      </c>
-      <c r="F83" s="2">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1">
         <v>0</v>
       </c>
       <c r="G83" s="1">
@@ -5228,13 +5232,13 @@
         <v>1</v>
       </c>
       <c r="I83" s="1">
-        <v>1014</v>
+        <v>900</v>
       </c>
       <c r="J83" s="1">
-        <v>1088635</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>37</v>
+        <v>1079546</v>
+      </c>
+      <c r="K83" t="s">
+        <v>33</v>
       </c>
       <c r="L83" s="1" t="b">
         <v>1</v>
@@ -5254,7 +5258,7 @@
         <v>21</v>
       </c>
       <c r="D84" s="1">
-        <v>3500</v>
+        <v>3501</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -5266,7 +5270,7 @@
         <v>100</v>
       </c>
       <c r="H84" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" s="1">
         <v>900</v>
@@ -5295,7 +5299,7 @@
         <v>21</v>
       </c>
       <c r="D85" s="1">
-        <v>3501</v>
+        <v>3502</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
@@ -5307,7 +5311,7 @@
         <v>100</v>
       </c>
       <c r="H85" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I85" s="1">
         <v>900</v>
@@ -5336,7 +5340,7 @@
         <v>21</v>
       </c>
       <c r="D86" s="1">
-        <v>3502</v>
+        <v>3503</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -5377,7 +5381,7 @@
         <v>21</v>
       </c>
       <c r="D87" s="1">
-        <v>3503</v>
+        <v>3505</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -5389,7 +5393,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I87" s="1">
         <v>900</v>
@@ -5418,7 +5422,7 @@
         <v>21</v>
       </c>
       <c r="D88" s="1">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -5430,7 +5434,7 @@
         <v>100</v>
       </c>
       <c r="H88" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I88" s="1">
         <v>900</v>
@@ -5459,7 +5463,7 @@
         <v>21</v>
       </c>
       <c r="D89" s="1">
-        <v>3504</v>
+        <v>3506</v>
       </c>
       <c r="E89" s="1">
         <v>1</v>
@@ -5471,7 +5475,7 @@
         <v>100</v>
       </c>
       <c r="H89" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I89" s="1">
         <v>900</v>
@@ -5491,19 +5495,19 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>22</v>
+        <v>455</v>
       </c>
       <c r="B90" s="1">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D90" s="1">
-        <v>3506</v>
+        <v>301</v>
       </c>
       <c r="E90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -5512,7 +5516,7 @@
         <v>100</v>
       </c>
       <c r="H90" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I90" s="1">
         <v>900</v>
@@ -5524,7 +5528,7 @@
         <v>33</v>
       </c>
       <c r="L90" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="1">
         <v>0</v>
@@ -5532,7 +5536,7 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>455</v>
+        <v>39</v>
       </c>
       <c r="B91" s="1">
         <v>1005</v>
@@ -5540,8 +5544,8 @@
       <c r="C91" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D91" s="1">
-        <v>301</v>
+      <c r="D91" s="5">
+        <v>3007</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
@@ -5553,7 +5557,7 @@
         <v>100</v>
       </c>
       <c r="H91" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I91" s="1">
         <v>900</v>
@@ -5581,8 +5585,8 @@
       <c r="C92" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D92" s="5">
-        <v>3007</v>
+      <c r="D92" s="1">
+        <v>302</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
@@ -5594,7 +5598,7 @@
         <v>100</v>
       </c>
       <c r="H92" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92" s="1">
         <v>900</v>
@@ -5623,7 +5627,7 @@
         <v>21</v>
       </c>
       <c r="D93" s="1">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="E93" s="1">
         <v>0</v>
@@ -5635,7 +5639,7 @@
         <v>100</v>
       </c>
       <c r="H93" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I93" s="1">
         <v>900</v>
@@ -5664,7 +5668,7 @@
         <v>21</v>
       </c>
       <c r="D94" s="1">
-        <v>283</v>
+        <v>3008</v>
       </c>
       <c r="E94" s="1">
         <v>0</v>
@@ -5676,7 +5680,7 @@
         <v>100</v>
       </c>
       <c r="H94" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I94" s="1">
         <v>900</v>
@@ -5704,8 +5708,8 @@
       <c r="C95" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D95" s="1">
-        <v>3008</v>
+      <c r="D95" s="5">
+        <v>3006</v>
       </c>
       <c r="E95" s="1">
         <v>0</v>
@@ -5717,7 +5721,7 @@
         <v>100</v>
       </c>
       <c r="H95" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I95" s="1">
         <v>900</v>
@@ -5745,8 +5749,8 @@
       <c r="C96" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D96" s="5">
-        <v>3006</v>
+      <c r="D96" s="1">
+        <v>276</v>
       </c>
       <c r="E96" s="1">
         <v>0</v>
@@ -5758,7 +5762,7 @@
         <v>100</v>
       </c>
       <c r="H96" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I96" s="1">
         <v>900</v>
@@ -5778,16 +5782,16 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B97" s="1">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D97" s="1">
-        <v>276</v>
+        <v>3002</v>
       </c>
       <c r="E97" s="1">
         <v>0</v>
@@ -5799,16 +5803,16 @@
         <v>100</v>
       </c>
       <c r="H97" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I97" s="1">
-        <v>900</v>
+        <v>2180</v>
       </c>
       <c r="J97" s="1">
-        <v>1079546</v>
-      </c>
-      <c r="K97" t="s">
-        <v>33</v>
+        <v>1165443</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L97" s="1" t="b">
         <v>0</v>
@@ -5825,10 +5829,10 @@
         <v>1006</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D98" s="1">
-        <v>3002</v>
+        <v>3011</v>
       </c>
       <c r="E98" s="1">
         <v>0</v>
@@ -5869,7 +5873,7 @@
         <v>40</v>
       </c>
       <c r="D99" s="1">
-        <v>3011</v>
+        <v>3009</v>
       </c>
       <c r="E99" s="1">
         <v>0</v>
@@ -5910,7 +5914,7 @@
         <v>40</v>
       </c>
       <c r="D100" s="1">
-        <v>3009</v>
+        <v>3000</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
@@ -5951,7 +5955,7 @@
         <v>40</v>
       </c>
       <c r="D101" s="1">
-        <v>3000</v>
+        <v>3001</v>
       </c>
       <c r="E101" s="1">
         <v>0</v>
@@ -5992,7 +5996,7 @@
         <v>40</v>
       </c>
       <c r="D102" s="1">
-        <v>3001</v>
+        <v>3003</v>
       </c>
       <c r="E102" s="1">
         <v>0</v>
@@ -6033,7 +6037,7 @@
         <v>40</v>
       </c>
       <c r="D103" s="1">
-        <v>3003</v>
+        <v>3005</v>
       </c>
       <c r="E103" s="1">
         <v>0</v>
@@ -6074,7 +6078,7 @@
         <v>40</v>
       </c>
       <c r="D104" s="1">
-        <v>3005</v>
+        <v>200</v>
       </c>
       <c r="E104" s="1">
         <v>0</v>
@@ -6115,7 +6119,7 @@
         <v>40</v>
       </c>
       <c r="D105" s="1">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="E105" s="1">
         <v>0</v>
@@ -6156,7 +6160,7 @@
         <v>40</v>
       </c>
       <c r="D106" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E106" s="1">
         <v>0</v>
@@ -6188,16 +6192,16 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B107" s="1">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D107" s="1">
-        <v>21</v>
+        <v>3142</v>
       </c>
       <c r="E107" s="1">
         <v>0</v>
@@ -6238,7 +6242,7 @@
         <v>40</v>
       </c>
       <c r="D108" s="1">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="E108" s="1">
         <v>0</v>
@@ -6279,7 +6283,7 @@
         <v>40</v>
       </c>
       <c r="D109" s="1">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="E109" s="1">
         <v>0</v>
@@ -6320,7 +6324,7 @@
         <v>40</v>
       </c>
       <c r="D110" s="1">
-        <v>3144</v>
+        <v>3108</v>
       </c>
       <c r="E110" s="1">
         <v>0</v>
@@ -6361,7 +6365,7 @@
         <v>40</v>
       </c>
       <c r="D111" s="1">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="E111" s="1">
         <v>0</v>
@@ -6402,7 +6406,7 @@
         <v>40</v>
       </c>
       <c r="D112" s="1">
-        <v>3109</v>
+        <v>3120</v>
       </c>
       <c r="E112" s="1">
         <v>0</v>
@@ -6443,7 +6447,7 @@
         <v>40</v>
       </c>
       <c r="D113" s="1">
-        <v>3120</v>
+        <v>3100</v>
       </c>
       <c r="E113" s="1">
         <v>0</v>
@@ -6484,7 +6488,7 @@
         <v>40</v>
       </c>
       <c r="D114" s="1">
-        <v>3100</v>
+        <v>3156</v>
       </c>
       <c r="E114" s="1">
         <v>0</v>
@@ -6516,16 +6520,16 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B115" s="1">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D115" s="1">
-        <v>3156</v>
+        <v>1600</v>
       </c>
       <c r="E115" s="1">
         <v>0</v>
@@ -6540,13 +6544,13 @@
         <v>1</v>
       </c>
       <c r="I115" s="1">
-        <v>2180</v>
+        <v>1756</v>
       </c>
       <c r="J115" s="1">
-        <v>1165443</v>
+        <v>1019120</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L115" s="1" t="b">
         <v>0</v>
@@ -6566,7 +6570,7 @@
         <v>44</v>
       </c>
       <c r="D116" s="1">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="E116" s="1">
         <v>0</v>
@@ -6607,7 +6611,7 @@
         <v>44</v>
       </c>
       <c r="D117" s="1">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="E117" s="1">
         <v>0</v>
@@ -6648,7 +6652,7 @@
         <v>44</v>
       </c>
       <c r="D118" s="1">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="E118" s="1">
         <v>0</v>
@@ -6689,7 +6693,7 @@
         <v>44</v>
       </c>
       <c r="D119" s="1">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="E119" s="1">
         <v>0</v>
@@ -6721,16 +6725,16 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B120" s="1">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D120" s="1">
-        <v>1613</v>
+        <v>1652</v>
       </c>
       <c r="E120" s="1">
         <v>0</v>
@@ -6771,7 +6775,7 @@
         <v>44</v>
       </c>
       <c r="D121" s="1">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="E121" s="1">
         <v>0</v>
@@ -6812,7 +6816,7 @@
         <v>44</v>
       </c>
       <c r="D122" s="1">
-        <v>1654</v>
+        <v>1702</v>
       </c>
       <c r="E122" s="1">
         <v>0</v>
@@ -6853,7 +6857,7 @@
         <v>44</v>
       </c>
       <c r="D123" s="1">
-        <v>1702</v>
+        <v>1803</v>
       </c>
       <c r="E123" s="1">
         <v>0</v>
@@ -6885,16 +6889,16 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B124" s="1">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D124" s="1">
-        <v>1803</v>
+        <v>22</v>
       </c>
       <c r="E124" s="1">
         <v>0</v>
@@ -6935,7 +6939,7 @@
         <v>44</v>
       </c>
       <c r="D125" s="1">
-        <v>22</v>
+        <v>2000</v>
       </c>
       <c r="E125" s="1">
         <v>0</v>
@@ -6976,7 +6980,7 @@
         <v>44</v>
       </c>
       <c r="D126" s="1">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="E126" s="1">
         <v>0</v>
@@ -7016,8 +7020,8 @@
       <c r="C127" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D127" s="1">
-        <v>2001</v>
+      <c r="D127" s="5">
+        <v>2115</v>
       </c>
       <c r="E127" s="1">
         <v>0</v>
@@ -7058,7 +7062,7 @@
         <v>44</v>
       </c>
       <c r="D128" s="5">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E128" s="1">
         <v>0</v>
@@ -7098,8 +7102,8 @@
       <c r="C129" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D129" s="5">
-        <v>2116</v>
+      <c r="D129" s="1">
+        <v>2002</v>
       </c>
       <c r="E129" s="1">
         <v>0</v>
@@ -7140,7 +7144,7 @@
         <v>44</v>
       </c>
       <c r="D130" s="1">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -7181,7 +7185,7 @@
         <v>44</v>
       </c>
       <c r="D131" s="1">
-        <v>2003</v>
+        <v>298</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -7213,16 +7217,16 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="B132" s="1">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D132" s="1">
-        <v>298</v>
+        <v>1650</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -7237,13 +7241,13 @@
         <v>1</v>
       </c>
       <c r="I132" s="1">
-        <v>1756</v>
+        <v>5309</v>
       </c>
       <c r="J132" s="1">
-        <v>1019120</v>
-      </c>
-      <c r="K132" s="1" t="s">
-        <v>34</v>
+        <v>1159783</v>
+      </c>
+      <c r="K132" s="1">
+        <v>41</v>
       </c>
       <c r="L132" s="1" t="b">
         <v>0</v>
@@ -7263,7 +7267,7 @@
         <v>25</v>
       </c>
       <c r="D133" s="1">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -7304,7 +7308,7 @@
         <v>25</v>
       </c>
       <c r="D134" s="1">
-        <v>1651</v>
+        <v>1700</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -7345,7 +7349,7 @@
         <v>25</v>
       </c>
       <c r="D135" s="1">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
@@ -7386,7 +7390,7 @@
         <v>25</v>
       </c>
       <c r="D136" s="1">
-        <v>1701</v>
+        <v>1800</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
@@ -7427,7 +7431,7 @@
         <v>25</v>
       </c>
       <c r="D137" s="1">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -7459,16 +7463,16 @@
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B138" s="1">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D138" s="1">
-        <v>1802</v>
+        <v>23</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -7509,7 +7513,7 @@
         <v>25</v>
       </c>
       <c r="D139" s="1">
-        <v>23</v>
+        <v>271</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -7550,7 +7554,7 @@
         <v>25</v>
       </c>
       <c r="D140" s="1">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -7591,7 +7595,7 @@
         <v>25</v>
       </c>
       <c r="D141" s="1">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
@@ -7623,16 +7627,16 @@
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>81</v>
+        <v>457</v>
       </c>
       <c r="B142" s="1">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D142" s="1">
-        <v>204</v>
+        <v>11</v>
       </c>
       <c r="E142" s="1">
         <v>0</v>
@@ -7647,13 +7651,13 @@
         <v>1</v>
       </c>
       <c r="I142" s="1">
-        <v>5309</v>
+        <v>3056</v>
       </c>
       <c r="J142" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K142" s="1">
-        <v>41</v>
+        <v>1019972</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="L142" s="1" t="b">
         <v>0</v>
@@ -7664,7 +7668,7 @@
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>49</v>
+        <v>457</v>
       </c>
       <c r="B143" s="1">
         <v>1013</v>
@@ -7673,7 +7677,7 @@
         <v>47</v>
       </c>
       <c r="D143" s="1">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="E143" s="1">
         <v>0</v>
@@ -7726,7 +7730,7 @@
         <v>100</v>
       </c>
       <c r="H144" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I144" s="1">
         <v>3056</v>
@@ -7767,7 +7771,7 @@
         <v>100</v>
       </c>
       <c r="H145" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I145" s="1">
         <v>3056</v>
@@ -7808,7 +7812,7 @@
         <v>100</v>
       </c>
       <c r="H146" s="1">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="I146" s="1">
         <v>3056</v>
@@ -7849,7 +7853,7 @@
         <v>100</v>
       </c>
       <c r="H147" s="1">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="I147" s="1">
         <v>3056</v>
@@ -7890,7 +7894,7 @@
         <v>100</v>
       </c>
       <c r="H148" s="1">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I148" s="1">
         <v>3056</v>
@@ -7931,7 +7935,7 @@
         <v>100</v>
       </c>
       <c r="H149" s="1">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I149" s="1">
         <v>3056</v>
@@ -7972,7 +7976,7 @@
         <v>100</v>
       </c>
       <c r="H150" s="1">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I150" s="1">
         <v>3056</v>
@@ -8013,7 +8017,7 @@
         <v>100</v>
       </c>
       <c r="H151" s="1">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I151" s="1">
         <v>3056</v>
@@ -8054,7 +8058,7 @@
         <v>100</v>
       </c>
       <c r="H152" s="1">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="I152" s="1">
         <v>3056</v>
@@ -8095,7 +8099,7 @@
         <v>100</v>
       </c>
       <c r="H153" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="I153" s="1">
         <v>3056</v>
@@ -8136,7 +8140,7 @@
         <v>100</v>
       </c>
       <c r="H154" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="I154" s="1">
         <v>3056</v>
@@ -8177,7 +8181,7 @@
         <v>100</v>
       </c>
       <c r="H155" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="I155" s="1">
         <v>3056</v>
@@ -8218,7 +8222,7 @@
         <v>100</v>
       </c>
       <c r="H156" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I156" s="1">
         <v>3056</v>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -4,13 +4,16 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$J$6:$L$6</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -83,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="458">
   <si>
     <t>string</t>
   </si>
@@ -8332,10 +8335,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:B395"/>
+  <dimension ref="A2:Q395"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8343,7 +8346,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>87</v>
       </c>
@@ -8351,7 +8354,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -8359,7 +8362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -8367,239 +8370,690 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>91</v>
       </c>
       <c r="B6">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J6">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>92</v>
       </c>
       <c r="B7">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J7" s="2">
+        <v>1101</v>
+      </c>
+      <c r="K7" s="2" t="str">
+        <f>VLOOKUP(J7,$P$7:$Q$34,2,FALSE)</f>
+        <v>芜菁种子</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1101</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>93</v>
       </c>
       <c r="B8">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J8" s="2">
+        <v>1102</v>
+      </c>
+      <c r="K8" s="2" t="str">
+        <f>VLOOKUP(J8,$P$7:$Q$34,2,FALSE)</f>
+        <v>卷心菜种子</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1102</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>94</v>
       </c>
       <c r="B9">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J9" s="2">
+        <v>1103</v>
+      </c>
+      <c r="K9" s="2" t="str">
+        <f>VLOOKUP(J9,$P$7:$Q$34,2,FALSE)</f>
+        <v>葱种子</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1103</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>95</v>
       </c>
       <c r="B10">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J10" s="2">
+        <v>1104</v>
+      </c>
+      <c r="K10" s="2" t="str">
+        <f>VLOOKUP(J10,$P$7:$Q$34,2,FALSE)</f>
+        <v>萝卜种子</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2</v>
+      </c>
+      <c r="P10">
+        <v>1104</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>96</v>
       </c>
       <c r="B11">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J11" s="2">
+        <v>1105</v>
+      </c>
+      <c r="K11" s="2" t="str">
+        <f>VLOOKUP(J11,$P$7:$Q$34,2,FALSE)</f>
+        <v>紫甘蓝种子</v>
+      </c>
+      <c r="L11" s="1">
+        <v>2</v>
+      </c>
+      <c r="P11">
+        <v>1105</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>97</v>
       </c>
       <c r="B12">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J12" s="2">
+        <v>1106</v>
+      </c>
+      <c r="K12" s="2" t="str">
+        <f>VLOOKUP(J12,$P$7:$Q$34,2,FALSE)</f>
+        <v>黄瓜种子</v>
+      </c>
+      <c r="L12" s="1">
+        <v>2</v>
+      </c>
+      <c r="P12">
+        <v>1106</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>98</v>
       </c>
       <c r="B13">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J13" s="2">
+        <v>1107</v>
+      </c>
+      <c r="K13" s="2" t="str">
+        <f>VLOOKUP(J13,$P$7:$Q$34,2,FALSE)</f>
+        <v>西兰花种子</v>
+      </c>
+      <c r="L13" s="1">
+        <v>3</v>
+      </c>
+      <c r="P13">
+        <v>1107</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>99</v>
       </c>
       <c r="B14">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J14" s="2">
+        <v>1108</v>
+      </c>
+      <c r="K14" s="2" t="str">
+        <f>VLOOKUP(J14,$P$7:$Q$34,2,FALSE)</f>
+        <v>番茄种子</v>
+      </c>
+      <c r="L14" s="1">
+        <v>3</v>
+      </c>
+      <c r="P14">
+        <v>1108</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>100</v>
       </c>
       <c r="B15">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J15" s="2">
+        <v>1109</v>
+      </c>
+      <c r="K15" s="2" t="str">
+        <f>VLOOKUP(J15,$P$7:$Q$34,2,FALSE)</f>
+        <v>胡萝卜种子</v>
+      </c>
+      <c r="L15" s="1">
+        <v>3</v>
+      </c>
+      <c r="P15">
+        <v>1109</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>101</v>
       </c>
       <c r="B16">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J16" s="2">
+        <v>1110</v>
+      </c>
+      <c r="K16" s="2" t="str">
+        <f>VLOOKUP(J16,$P$7:$Q$34,2,FALSE)</f>
+        <v>西瓜种子</v>
+      </c>
+      <c r="L16" s="1">
+        <v>4</v>
+      </c>
+      <c r="P16">
+        <v>1110</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>72</v>
       </c>
       <c r="B17">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J17" s="2">
+        <v>1111</v>
+      </c>
+      <c r="K17" s="2" t="str">
+        <f>VLOOKUP(J17,$P$7:$Q$34,2,FALSE)</f>
+        <v>辣椒种子</v>
+      </c>
+      <c r="L17" s="1">
+        <v>4</v>
+      </c>
+      <c r="P17">
+        <v>1111</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>82</v>
       </c>
       <c r="B18">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J18" s="2">
+        <v>1112</v>
+      </c>
+      <c r="K18" s="2" t="str">
+        <f>VLOOKUP(J18,$P$7:$Q$34,2,FALSE)</f>
+        <v>奇异果种子</v>
+      </c>
+      <c r="L18" s="1">
+        <v>4</v>
+      </c>
+      <c r="P18">
+        <v>1112</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>102</v>
       </c>
       <c r="B19">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J19" s="2">
+        <v>1113</v>
+      </c>
+      <c r="K19" s="2" t="str">
+        <f>VLOOKUP(J19,$P$7:$Q$34,2,FALSE)</f>
+        <v>茄子种子</v>
+      </c>
+      <c r="L19" s="1">
+        <v>5</v>
+      </c>
+      <c r="P19">
+        <v>1113</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>103</v>
       </c>
       <c r="B20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J20" s="2">
+        <v>1114</v>
+      </c>
+      <c r="K20" s="2" t="str">
+        <f>VLOOKUP(J20,$P$7:$Q$34,2,FALSE)</f>
+        <v>豌豆种子</v>
+      </c>
+      <c r="L20" s="1">
+        <v>5</v>
+      </c>
+      <c r="P20">
+        <v>1114</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>104</v>
       </c>
       <c r="B21">
         <v>101</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J21" s="2">
+        <v>1115</v>
+      </c>
+      <c r="K21" s="2" t="str">
+        <f>VLOOKUP(J21,$P$7:$Q$34,2,FALSE)</f>
+        <v>土豆种子</v>
+      </c>
+      <c r="L21" s="1">
+        <v>5</v>
+      </c>
+      <c r="P21">
+        <v>1115</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>105</v>
       </c>
       <c r="B22">
         <v>102</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J22" s="2">
+        <v>1116</v>
+      </c>
+      <c r="K22" s="2" t="str">
+        <f>VLOOKUP(J22,$P$7:$Q$34,2,FALSE)</f>
+        <v>大蒜种子</v>
+      </c>
+      <c r="L22" s="1">
+        <v>6</v>
+      </c>
+      <c r="P22">
+        <v>1116</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>106</v>
       </c>
       <c r="B23">
         <v>103</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J23" s="2">
+        <v>1117</v>
+      </c>
+      <c r="K23" s="2" t="str">
+        <f>VLOOKUP(J23,$P$7:$Q$34,2,FALSE)</f>
+        <v>芦笋种子</v>
+      </c>
+      <c r="L23" s="1">
+        <v>6</v>
+      </c>
+      <c r="P23">
+        <v>1117</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>107</v>
       </c>
       <c r="B24">
         <v>104</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J24" s="2">
+        <v>1118</v>
+      </c>
+      <c r="K24" s="2" t="str">
+        <f>VLOOKUP(J24,$P$7:$Q$34,2,FALSE)</f>
+        <v>南瓜种子</v>
+      </c>
+      <c r="L24" s="1">
+        <v>6</v>
+      </c>
+      <c r="P24">
+        <v>1118</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>108</v>
       </c>
       <c r="B25">
         <v>105</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J25" s="2">
+        <v>1119</v>
+      </c>
+      <c r="K25" s="2" t="str">
+        <f>VLOOKUP(J25,$P$7:$Q$34,2,FALSE)</f>
+        <v>玉米种子</v>
+      </c>
+      <c r="L25" s="1">
+        <v>7</v>
+      </c>
+      <c r="P25">
+        <v>1119</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>109</v>
       </c>
       <c r="B26">
         <v>200</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J26" s="2">
+        <v>1120</v>
+      </c>
+      <c r="K26" s="2" t="str">
+        <f>VLOOKUP(J26,$P$7:$Q$34,2,FALSE)</f>
+        <v>大麦种子</v>
+      </c>
+      <c r="L26" s="1">
+        <v>7</v>
+      </c>
+      <c r="P26">
+        <v>1120</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>110</v>
       </c>
       <c r="B27">
         <v>201</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J27" s="2">
+        <v>1121</v>
+      </c>
+      <c r="K27" s="2" t="str">
+        <f>VLOOKUP(J27,$P$7:$Q$34,2,FALSE)</f>
+        <v>啤酒花种子</v>
+      </c>
+      <c r="L27" s="1">
+        <v>7</v>
+      </c>
+      <c r="P27">
+        <v>1121</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>111</v>
       </c>
       <c r="B28">
         <v>202</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J28" s="2">
+        <v>1122</v>
+      </c>
+      <c r="K28" s="2" t="str">
+        <f>VLOOKUP(J28,$P$7:$Q$34,2,FALSE)</f>
+        <v>葡萄种子</v>
+      </c>
+      <c r="L28" s="1">
+        <v>8</v>
+      </c>
+      <c r="P28">
+        <v>1122</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>112</v>
       </c>
       <c r="B29">
         <v>203</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J29" s="2">
+        <v>1123</v>
+      </c>
+      <c r="K29" s="2" t="str">
+        <f>VLOOKUP(J29,$P$7:$Q$34,2,FALSE)</f>
+        <v>菠萝种子</v>
+      </c>
+      <c r="L29" s="1">
+        <v>8</v>
+      </c>
+      <c r="P29">
+        <v>1123</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>85</v>
       </c>
       <c r="B30">
         <v>204</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J30" s="2">
+        <v>1124</v>
+      </c>
+      <c r="K30" s="2" t="str">
+        <f>VLOOKUP(J30,$P$7:$Q$34,2,FALSE)</f>
+        <v>咖啡种子</v>
+      </c>
+      <c r="L30" s="1">
+        <v>8</v>
+      </c>
+      <c r="P30">
+        <v>1124</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>113</v>
       </c>
       <c r="B31">
         <v>205</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J31" s="2">
+        <v>1125</v>
+      </c>
+      <c r="K31" s="2" t="str">
+        <f>VLOOKUP(J31,$P$7:$Q$34,2,FALSE)</f>
+        <v>草莓种子</v>
+      </c>
+      <c r="L31" s="1">
+        <v>9</v>
+      </c>
+      <c r="P31">
+        <v>1125</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>114</v>
       </c>
       <c r="B32">
         <v>207</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J32" s="2">
+        <v>1126</v>
+      </c>
+      <c r="K32" s="2" t="str">
+        <f>VLOOKUP(J32,$P$7:$Q$34,2,FALSE)</f>
+        <v>蓝莓种子</v>
+      </c>
+      <c r="L32" s="1">
+        <v>9</v>
+      </c>
+      <c r="P32">
+        <v>1126</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>115</v>
       </c>
       <c r="B33">
         <v>208</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J33" s="2">
+        <v>1127</v>
+      </c>
+      <c r="K33" s="2" t="str">
+        <f>VLOOKUP(J33,$P$7:$Q$34,2,FALSE)</f>
+        <v>红薯种子</v>
+      </c>
+      <c r="L33" s="1">
+        <v>9</v>
+      </c>
+      <c r="P33">
+        <v>1127</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>116</v>
       </c>
       <c r="B34">
         <v>210</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="J34" s="2">
+        <v>1128</v>
+      </c>
+      <c r="K34" s="2" t="str">
+        <f>VLOOKUP(J34,$P$7:$Q$34,2,FALSE)</f>
+        <v>甜菜种子</v>
+      </c>
+      <c r="L34" s="1">
+        <v>9</v>
+      </c>
+      <c r="P34">
+        <v>1128</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>117</v>
       </c>
@@ -8607,7 +9061,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>118</v>
       </c>
@@ -8615,7 +9069,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>119</v>
       </c>
@@ -8623,7 +9077,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>120</v>
       </c>
@@ -8631,7 +9085,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>121</v>
       </c>
@@ -8639,7 +9093,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>122</v>
       </c>
@@ -8647,7 +9101,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>123</v>
       </c>
@@ -8655,7 +9109,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>124</v>
       </c>
@@ -8663,7 +9117,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>125</v>
       </c>
@@ -8671,7 +9125,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>126</v>
       </c>
@@ -8679,7 +9133,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>127</v>
       </c>
@@ -8687,7 +9141,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>128</v>
       </c>
@@ -8695,7 +9149,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>129</v>
       </c>
@@ -8703,7 +9157,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>130</v>
       </c>
@@ -11488,8 +11942,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="J6:L6">
+    <sortState ref="J7:L34">
+      <sortCondition ref="J6"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="ShopItemData" sheetId="1" r:id="rId1"/>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="458">
   <si>
     <t>string</t>
   </si>
@@ -1870,7 +1870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M158"/>
+  <dimension ref="A1:M164"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -5314,7 +5314,7 @@
         <v>100</v>
       </c>
       <c r="H85" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I85" s="1">
         <v>900</v>
@@ -5384,7 +5384,7 @@
         <v>21</v>
       </c>
       <c r="D87" s="1">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -5396,7 +5396,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I87" s="1">
         <v>900</v>
@@ -5425,7 +5425,7 @@
         <v>21</v>
       </c>
       <c r="D88" s="1">
-        <v>3504</v>
+        <v>3505</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -5437,7 +5437,7 @@
         <v>100</v>
       </c>
       <c r="H88" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I88" s="1">
         <v>900</v>
@@ -5478,7 +5478,7 @@
         <v>100</v>
       </c>
       <c r="H89" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I89" s="1">
         <v>900</v>
@@ -5498,19 +5498,19 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>455</v>
+        <v>22</v>
       </c>
       <c r="B90" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D90" s="1">
-        <v>301</v>
+        <v>3507</v>
       </c>
       <c r="E90" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -5519,7 +5519,7 @@
         <v>100</v>
       </c>
       <c r="H90" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I90" s="1">
         <v>900</v>
@@ -5531,7 +5531,7 @@
         <v>33</v>
       </c>
       <c r="L90" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="1">
         <v>0</v>
@@ -5539,19 +5539,19 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B91" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D91" s="5">
-        <v>3007</v>
+      <c r="D91" s="1">
+        <v>3508</v>
       </c>
       <c r="E91" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>100</v>
       </c>
       <c r="H91" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I91" s="1">
         <v>900</v>
@@ -5572,7 +5572,7 @@
         <v>33</v>
       </c>
       <c r="L91" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="1">
         <v>0</v>
@@ -5580,19 +5580,19 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B92" s="1">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D92" s="1">
-        <v>302</v>
+        <v>3509</v>
       </c>
       <c r="E92" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
@@ -5601,7 +5601,7 @@
         <v>100</v>
       </c>
       <c r="H92" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I92" s="1">
         <v>900</v>
@@ -5613,7 +5613,7 @@
         <v>33</v>
       </c>
       <c r="L92" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="1">
         <v>0</v>
@@ -5621,7 +5621,7 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>39</v>
+        <v>455</v>
       </c>
       <c r="B93" s="1">
         <v>1005</v>
@@ -5630,7 +5630,7 @@
         <v>21</v>
       </c>
       <c r="D93" s="1">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E93" s="1">
         <v>0</v>
@@ -5642,7 +5642,7 @@
         <v>100</v>
       </c>
       <c r="H93" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I93" s="1">
         <v>900</v>
@@ -5670,8 +5670,8 @@
       <c r="C94" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D94" s="1">
-        <v>3008</v>
+      <c r="D94" s="5">
+        <v>3007</v>
       </c>
       <c r="E94" s="1">
         <v>0</v>
@@ -5683,7 +5683,7 @@
         <v>100</v>
       </c>
       <c r="H94" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I94" s="1">
         <v>900</v>
@@ -5711,8 +5711,8 @@
       <c r="C95" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D95" s="5">
-        <v>3006</v>
+      <c r="D95" s="1">
+        <v>302</v>
       </c>
       <c r="E95" s="1">
         <v>0</v>
@@ -5724,7 +5724,7 @@
         <v>100</v>
       </c>
       <c r="H95" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I95" s="1">
         <v>900</v>
@@ -5753,7 +5753,7 @@
         <v>21</v>
       </c>
       <c r="D96" s="1">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E96" s="1">
         <v>0</v>
@@ -5765,7 +5765,7 @@
         <v>100</v>
       </c>
       <c r="H96" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I96" s="1">
         <v>900</v>
@@ -5785,16 +5785,16 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B97" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D97" s="1">
-        <v>3002</v>
+        <v>3008</v>
       </c>
       <c r="E97" s="1">
         <v>0</v>
@@ -5806,16 +5806,16 @@
         <v>100</v>
       </c>
       <c r="H97" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I97" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J97" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>35</v>
+        <v>1079546</v>
+      </c>
+      <c r="K97" t="s">
+        <v>33</v>
       </c>
       <c r="L97" s="1" t="b">
         <v>0</v>
@@ -5826,16 +5826,16 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B98" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D98" s="1">
-        <v>3011</v>
+        <v>21</v>
+      </c>
+      <c r="D98" s="5">
+        <v>3006</v>
       </c>
       <c r="E98" s="1">
         <v>0</v>
@@ -5847,16 +5847,16 @@
         <v>100</v>
       </c>
       <c r="H98" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I98" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J98" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>35</v>
+        <v>1079546</v>
+      </c>
+      <c r="K98" t="s">
+        <v>33</v>
       </c>
       <c r="L98" s="1" t="b">
         <v>0</v>
@@ -5867,16 +5867,16 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B99" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D99" s="1">
-        <v>3009</v>
+        <v>276</v>
       </c>
       <c r="E99" s="1">
         <v>0</v>
@@ -5888,16 +5888,16 @@
         <v>100</v>
       </c>
       <c r="H99" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I99" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J99" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>35</v>
+        <v>1079546</v>
+      </c>
+      <c r="K99" t="s">
+        <v>33</v>
       </c>
       <c r="L99" s="1" t="b">
         <v>0</v>
@@ -5908,16 +5908,16 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B100" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D100" s="1">
-        <v>3000</v>
+        <v>241</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
@@ -5929,16 +5929,16 @@
         <v>100</v>
       </c>
       <c r="H100" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I100" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J100" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>35</v>
+        <v>1079546</v>
+      </c>
+      <c r="K100" t="s">
+        <v>33</v>
       </c>
       <c r="L100" s="1" t="b">
         <v>0</v>
@@ -5949,16 +5949,16 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B101" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D101" s="1">
-        <v>3001</v>
+        <v>229</v>
       </c>
       <c r="E101" s="1">
         <v>0</v>
@@ -5970,16 +5970,16 @@
         <v>100</v>
       </c>
       <c r="H101" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I101" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J101" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>35</v>
+        <v>1079546</v>
+      </c>
+      <c r="K101" t="s">
+        <v>33</v>
       </c>
       <c r="L101" s="1" t="b">
         <v>0</v>
@@ -5990,16 +5990,16 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B102" s="1">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D102" s="1">
-        <v>3003</v>
+        <v>203</v>
       </c>
       <c r="E102" s="1">
         <v>0</v>
@@ -6011,16 +6011,16 @@
         <v>100</v>
       </c>
       <c r="H102" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I102" s="1">
-        <v>2180</v>
+        <v>900</v>
       </c>
       <c r="J102" s="1">
-        <v>1165443</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>35</v>
+        <v>1079546</v>
+      </c>
+      <c r="K102" t="s">
+        <v>33</v>
       </c>
       <c r="L102" s="1" t="b">
         <v>0</v>
@@ -6037,10 +6037,10 @@
         <v>1006</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="D103" s="1">
-        <v>3005</v>
+        <v>3002</v>
       </c>
       <c r="E103" s="1">
         <v>0</v>
@@ -6081,7 +6081,7 @@
         <v>40</v>
       </c>
       <c r="D104" s="1">
-        <v>200</v>
+        <v>3011</v>
       </c>
       <c r="E104" s="1">
         <v>0</v>
@@ -6122,7 +6122,7 @@
         <v>40</v>
       </c>
       <c r="D105" s="1">
-        <v>20</v>
+        <v>3009</v>
       </c>
       <c r="E105" s="1">
         <v>0</v>
@@ -6163,7 +6163,7 @@
         <v>40</v>
       </c>
       <c r="D106" s="1">
-        <v>21</v>
+        <v>3000</v>
       </c>
       <c r="E106" s="1">
         <v>0</v>
@@ -6195,16 +6195,16 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B107" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D107" s="1">
-        <v>3142</v>
+        <v>3001</v>
       </c>
       <c r="E107" s="1">
         <v>0</v>
@@ -6236,16 +6236,16 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B108" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D108" s="1">
-        <v>3143</v>
+        <v>3003</v>
       </c>
       <c r="E108" s="1">
         <v>0</v>
@@ -6277,16 +6277,16 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B109" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D109" s="1">
-        <v>3144</v>
+        <v>3005</v>
       </c>
       <c r="E109" s="1">
         <v>0</v>
@@ -6318,16 +6318,16 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B110" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D110" s="1">
-        <v>3108</v>
+        <v>200</v>
       </c>
       <c r="E110" s="1">
         <v>0</v>
@@ -6359,16 +6359,16 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B111" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D111" s="1">
-        <v>3109</v>
+        <v>20</v>
       </c>
       <c r="E111" s="1">
         <v>0</v>
@@ -6400,16 +6400,16 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B112" s="1">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D112" s="1">
-        <v>3120</v>
+        <v>21</v>
       </c>
       <c r="E112" s="1">
         <v>0</v>
@@ -6450,7 +6450,7 @@
         <v>40</v>
       </c>
       <c r="D113" s="1">
-        <v>3100</v>
+        <v>3142</v>
       </c>
       <c r="E113" s="1">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         <v>40</v>
       </c>
       <c r="D114" s="1">
-        <v>3156</v>
+        <v>3143</v>
       </c>
       <c r="E114" s="1">
         <v>0</v>
@@ -6523,16 +6523,16 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B115" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D115" s="1">
-        <v>1600</v>
+        <v>3144</v>
       </c>
       <c r="E115" s="1">
         <v>0</v>
@@ -6547,13 +6547,13 @@
         <v>1</v>
       </c>
       <c r="I115" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J115" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L115" s="1" t="b">
         <v>0</v>
@@ -6564,16 +6564,16 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B116" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D116" s="1">
-        <v>1605</v>
+        <v>3108</v>
       </c>
       <c r="E116" s="1">
         <v>0</v>
@@ -6588,13 +6588,13 @@
         <v>1</v>
       </c>
       <c r="I116" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J116" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L116" s="1" t="b">
         <v>0</v>
@@ -6605,16 +6605,16 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B117" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D117" s="1">
-        <v>1609</v>
+        <v>3109</v>
       </c>
       <c r="E117" s="1">
         <v>0</v>
@@ -6629,13 +6629,13 @@
         <v>1</v>
       </c>
       <c r="I117" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J117" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L117" s="1" t="b">
         <v>0</v>
@@ -6646,16 +6646,16 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B118" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D118" s="1">
-        <v>1612</v>
+        <v>3120</v>
       </c>
       <c r="E118" s="1">
         <v>0</v>
@@ -6670,13 +6670,13 @@
         <v>1</v>
       </c>
       <c r="I118" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J118" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L118" s="1" t="b">
         <v>0</v>
@@ -6687,16 +6687,16 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B119" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D119" s="1">
-        <v>1613</v>
+        <v>3100</v>
       </c>
       <c r="E119" s="1">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>1</v>
       </c>
       <c r="I119" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J119" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L119" s="1" t="b">
         <v>0</v>
@@ -6728,16 +6728,16 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="B120" s="1">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D120" s="1">
-        <v>1652</v>
+        <v>3156</v>
       </c>
       <c r="E120" s="1">
         <v>0</v>
@@ -6752,13 +6752,13 @@
         <v>1</v>
       </c>
       <c r="I120" s="1">
-        <v>1756</v>
+        <v>2180</v>
       </c>
       <c r="J120" s="1">
-        <v>1019120</v>
+        <v>1165443</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L120" s="1" t="b">
         <v>0</v>
@@ -6769,16 +6769,16 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B121" s="1">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D121" s="1">
-        <v>1654</v>
+        <v>1600</v>
       </c>
       <c r="E121" s="1">
         <v>0</v>
@@ -6810,16 +6810,16 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B122" s="1">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D122" s="1">
-        <v>1702</v>
+        <v>1605</v>
       </c>
       <c r="E122" s="1">
         <v>0</v>
@@ -6851,16 +6851,16 @@
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B123" s="1">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D123" s="1">
-        <v>1803</v>
+        <v>1609</v>
       </c>
       <c r="E123" s="1">
         <v>0</v>
@@ -6892,16 +6892,16 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B124" s="1">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D124" s="1">
-        <v>22</v>
+        <v>1612</v>
       </c>
       <c r="E124" s="1">
         <v>0</v>
@@ -6933,16 +6933,16 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B125" s="1">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D125" s="1">
-        <v>2000</v>
+        <v>1613</v>
       </c>
       <c r="E125" s="1">
         <v>0</v>
@@ -6974,16 +6974,16 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B126" s="1">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D126" s="1">
-        <v>2001</v>
+        <v>1652</v>
       </c>
       <c r="E126" s="1">
         <v>0</v>
@@ -7015,16 +7015,16 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B127" s="1">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D127" s="5">
-        <v>2115</v>
+      <c r="D127" s="1">
+        <v>1654</v>
       </c>
       <c r="E127" s="1">
         <v>0</v>
@@ -7056,16 +7056,16 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B128" s="1">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D128" s="5">
-        <v>2116</v>
+      <c r="D128" s="1">
+        <v>1702</v>
       </c>
       <c r="E128" s="1">
         <v>0</v>
@@ -7097,16 +7097,16 @@
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B129" s="1">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D129" s="1">
-        <v>2002</v>
+        <v>1803</v>
       </c>
       <c r="E129" s="1">
         <v>0</v>
@@ -7147,7 +7147,7 @@
         <v>44</v>
       </c>
       <c r="D130" s="1">
-        <v>2003</v>
+        <v>22</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
@@ -7188,7 +7188,7 @@
         <v>44</v>
       </c>
       <c r="D131" s="1">
-        <v>298</v>
+        <v>2000</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
@@ -7220,16 +7220,16 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B132" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D132" s="1">
-        <v>1650</v>
+        <v>2001</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
@@ -7244,13 +7244,13 @@
         <v>1</v>
       </c>
       <c r="I132" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J132" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K132" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="L132" s="1" t="b">
         <v>0</v>
@@ -7261,16 +7261,16 @@
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B133" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D133" s="1">
-        <v>1651</v>
+        <v>44</v>
+      </c>
+      <c r="D133" s="5">
+        <v>2115</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
@@ -7285,13 +7285,13 @@
         <v>1</v>
       </c>
       <c r="I133" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J133" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K133" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="L133" s="1" t="b">
         <v>0</v>
@@ -7302,16 +7302,16 @@
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B134" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D134" s="1">
-        <v>1700</v>
+        <v>44</v>
+      </c>
+      <c r="D134" s="5">
+        <v>2116</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
@@ -7326,13 +7326,13 @@
         <v>1</v>
       </c>
       <c r="I134" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J134" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K134" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="L134" s="1" t="b">
         <v>0</v>
@@ -7343,16 +7343,16 @@
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B135" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D135" s="1">
-        <v>1701</v>
+        <v>2002</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
@@ -7367,13 +7367,13 @@
         <v>1</v>
       </c>
       <c r="I135" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J135" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K135" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="L135" s="1" t="b">
         <v>0</v>
@@ -7384,16 +7384,16 @@
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B136" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D136" s="1">
-        <v>1800</v>
+        <v>2003</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
@@ -7408,13 +7408,13 @@
         <v>1</v>
       </c>
       <c r="I136" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J136" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K136" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="L136" s="1" t="b">
         <v>0</v>
@@ -7425,16 +7425,16 @@
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B137" s="1">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D137" s="1">
-        <v>1802</v>
+        <v>298</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
@@ -7449,13 +7449,13 @@
         <v>1</v>
       </c>
       <c r="I137" s="1">
-        <v>5309</v>
+        <v>1756</v>
       </c>
       <c r="J137" s="1">
-        <v>1159783</v>
-      </c>
-      <c r="K137" s="1">
-        <v>41</v>
+        <v>1019120</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="L137" s="1" t="b">
         <v>0</v>
@@ -7466,16 +7466,16 @@
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="B138" s="1">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D138" s="1">
-        <v>23</v>
+        <v>1650</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -7507,16 +7507,16 @@
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="B139" s="1">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D139" s="1">
-        <v>271</v>
+        <v>1651</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
@@ -7548,16 +7548,16 @@
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="B140" s="1">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D140" s="1">
-        <v>277</v>
+        <v>1700</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
@@ -7589,16 +7589,16 @@
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="B141" s="1">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D141" s="1">
-        <v>204</v>
+        <v>1701</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
@@ -7630,16 +7630,16 @@
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>457</v>
+        <v>45</v>
       </c>
       <c r="B142" s="1">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D142" s="1">
-        <v>11</v>
+        <v>1800</v>
       </c>
       <c r="E142" s="1">
         <v>0</v>
@@ -7654,13 +7654,13 @@
         <v>1</v>
       </c>
       <c r="I142" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J142" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K142" s="1" t="s">
-        <v>36</v>
+        <v>1159783</v>
+      </c>
+      <c r="K142" s="1">
+        <v>41</v>
       </c>
       <c r="L142" s="1" t="b">
         <v>0</v>
@@ -7671,16 +7671,16 @@
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>457</v>
+        <v>45</v>
       </c>
       <c r="B143" s="1">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D143" s="1">
-        <v>201</v>
+        <v>1802</v>
       </c>
       <c r="E143" s="1">
         <v>0</v>
@@ -7695,13 +7695,13 @@
         <v>1</v>
       </c>
       <c r="I143" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J143" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K143" s="1" t="s">
-        <v>36</v>
+        <v>1159783</v>
+      </c>
+      <c r="K143" s="1">
+        <v>41</v>
       </c>
       <c r="L143" s="1" t="b">
         <v>0</v>
@@ -7712,16 +7712,16 @@
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="B144" s="1">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D144" s="1">
-        <v>295</v>
+        <v>23</v>
       </c>
       <c r="E144" s="1">
         <v>0</v>
@@ -7733,16 +7733,16 @@
         <v>100</v>
       </c>
       <c r="H144" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I144" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J144" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K144" s="1" t="s">
-        <v>36</v>
+        <v>1159783</v>
+      </c>
+      <c r="K144" s="1">
+        <v>41</v>
       </c>
       <c r="L144" s="1" t="b">
         <v>0</v>
@@ -7753,16 +7753,16 @@
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="B145" s="1">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D145" s="1">
-        <v>24</v>
+        <v>271</v>
       </c>
       <c r="E145" s="1">
         <v>0</v>
@@ -7774,16 +7774,16 @@
         <v>100</v>
       </c>
       <c r="H145" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I145" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J145" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K145" s="1" t="s">
-        <v>36</v>
+        <v>1159783</v>
+      </c>
+      <c r="K145" s="1">
+        <v>41</v>
       </c>
       <c r="L145" s="1" t="b">
         <v>0</v>
@@ -7794,16 +7794,16 @@
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="B146" s="1">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D146" s="1">
-        <v>4000</v>
+        <v>277</v>
       </c>
       <c r="E146" s="1">
         <v>0</v>
@@ -7815,16 +7815,16 @@
         <v>100</v>
       </c>
       <c r="H146" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I146" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J146" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K146" s="1" t="s">
-        <v>36</v>
+        <v>1159783</v>
+      </c>
+      <c r="K146" s="1">
+        <v>41</v>
       </c>
       <c r="L146" s="1" t="b">
         <v>0</v>
@@ -7835,16 +7835,16 @@
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="B147" s="1">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D147" s="1">
-        <v>4001</v>
+        <v>204</v>
       </c>
       <c r="E147" s="1">
         <v>0</v>
@@ -7856,16 +7856,16 @@
         <v>100</v>
       </c>
       <c r="H147" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I147" s="1">
-        <v>3056</v>
+        <v>5309</v>
       </c>
       <c r="J147" s="1">
-        <v>1019972</v>
-      </c>
-      <c r="K147" s="1" t="s">
-        <v>36</v>
+        <v>1159783</v>
+      </c>
+      <c r="K147" s="1">
+        <v>41</v>
       </c>
       <c r="L147" s="1" t="b">
         <v>0</v>
@@ -7876,7 +7876,7 @@
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>49</v>
+        <v>457</v>
       </c>
       <c r="B148" s="1">
         <v>1013</v>
@@ -7885,7 +7885,7 @@
         <v>47</v>
       </c>
       <c r="D148" s="1">
-        <v>4002</v>
+        <v>11</v>
       </c>
       <c r="E148" s="1">
         <v>0</v>
@@ -7897,7 +7897,7 @@
         <v>100</v>
       </c>
       <c r="H148" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I148" s="1">
         <v>3056</v>
@@ -7917,7 +7917,7 @@
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>49</v>
+        <v>457</v>
       </c>
       <c r="B149" s="1">
         <v>1013</v>
@@ -7926,7 +7926,7 @@
         <v>47</v>
       </c>
       <c r="D149" s="1">
-        <v>4003</v>
+        <v>201</v>
       </c>
       <c r="E149" s="1">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>100</v>
       </c>
       <c r="H149" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I149" s="1">
         <v>3056</v>
@@ -7967,7 +7967,7 @@
         <v>47</v>
       </c>
       <c r="D150" s="1">
-        <v>4004</v>
+        <v>295</v>
       </c>
       <c r="E150" s="1">
         <v>0</v>
@@ -8008,7 +8008,7 @@
         <v>47</v>
       </c>
       <c r="D151" s="1">
-        <v>4005</v>
+        <v>24</v>
       </c>
       <c r="E151" s="1">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>47</v>
       </c>
       <c r="D152" s="1">
-        <v>4006</v>
+        <v>4000</v>
       </c>
       <c r="E152" s="1">
         <v>0</v>
@@ -8090,7 +8090,7 @@
         <v>47</v>
       </c>
       <c r="D153" s="1">
-        <v>4007</v>
+        <v>4001</v>
       </c>
       <c r="E153" s="1">
         <v>0</v>
@@ -8131,7 +8131,7 @@
         <v>47</v>
       </c>
       <c r="D154" s="1">
-        <v>4008</v>
+        <v>4002</v>
       </c>
       <c r="E154" s="1">
         <v>0</v>
@@ -8172,7 +8172,7 @@
         <v>47</v>
       </c>
       <c r="D155" s="1">
-        <v>4009</v>
+        <v>4003</v>
       </c>
       <c r="E155" s="1">
         <v>0</v>
@@ -8213,7 +8213,7 @@
         <v>47</v>
       </c>
       <c r="D156" s="1">
-        <v>4010</v>
+        <v>4004</v>
       </c>
       <c r="E156" s="1">
         <v>0</v>
@@ -8245,16 +8245,16 @@
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B157" s="1">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D157" s="1">
-        <v>12</v>
+        <v>4005</v>
       </c>
       <c r="E157" s="1">
         <v>0</v>
@@ -8266,16 +8266,16 @@
         <v>100</v>
       </c>
       <c r="H157" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I157" s="1">
-        <v>2497</v>
+        <v>3056</v>
       </c>
       <c r="J157" s="1">
-        <v>1116139</v>
-      </c>
-      <c r="K157" s="1">
-        <v>26</v>
+        <v>1019972</v>
+      </c>
+      <c r="K157" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="L157" s="1" t="b">
         <v>0</v>
@@ -8286,16 +8286,16 @@
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B158" s="1">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D158" s="1">
-        <v>2004</v>
+        <v>4006</v>
       </c>
       <c r="E158" s="1">
         <v>0</v>
@@ -8307,21 +8307,267 @@
         <v>100</v>
       </c>
       <c r="H158" s="1">
+        <v>100</v>
+      </c>
+      <c r="I158" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J158" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K158" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L158" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M158" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A159" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B159" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D159" s="1">
+        <v>4007</v>
+      </c>
+      <c r="E159" s="1">
+        <v>0</v>
+      </c>
+      <c r="F159" s="1">
+        <v>0</v>
+      </c>
+      <c r="G159" s="1">
+        <v>100</v>
+      </c>
+      <c r="H159" s="1">
+        <v>100</v>
+      </c>
+      <c r="I159" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J159" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K159" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L159" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M159" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A160" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B160" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D160" s="1">
+        <v>4008</v>
+      </c>
+      <c r="E160" s="1">
+        <v>0</v>
+      </c>
+      <c r="F160" s="1">
+        <v>0</v>
+      </c>
+      <c r="G160" s="1">
+        <v>100</v>
+      </c>
+      <c r="H160" s="1">
+        <v>100</v>
+      </c>
+      <c r="I160" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J160" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K160" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L160" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A161" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B161" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D161" s="1">
+        <v>4009</v>
+      </c>
+      <c r="E161" s="1">
+        <v>0</v>
+      </c>
+      <c r="F161" s="1">
+        <v>0</v>
+      </c>
+      <c r="G161" s="1">
+        <v>100</v>
+      </c>
+      <c r="H161" s="1">
+        <v>100</v>
+      </c>
+      <c r="I161" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J161" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K161" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L161" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M161" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A162" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B162" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D162" s="1">
+        <v>4010</v>
+      </c>
+      <c r="E162" s="1">
+        <v>0</v>
+      </c>
+      <c r="F162" s="1">
+        <v>0</v>
+      </c>
+      <c r="G162" s="1">
+        <v>100</v>
+      </c>
+      <c r="H162" s="1">
+        <v>100</v>
+      </c>
+      <c r="I162" s="1">
+        <v>3056</v>
+      </c>
+      <c r="J162" s="1">
+        <v>1019972</v>
+      </c>
+      <c r="K162" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L162" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M162" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B163" s="1">
+        <v>1014</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D163" s="1">
+        <v>12</v>
+      </c>
+      <c r="E163" s="1">
+        <v>0</v>
+      </c>
+      <c r="F163" s="1">
+        <v>0</v>
+      </c>
+      <c r="G163" s="1">
+        <v>100</v>
+      </c>
+      <c r="H163" s="1">
         <v>1</v>
       </c>
-      <c r="I158" s="1">
+      <c r="I163" s="1">
         <v>2497</v>
       </c>
-      <c r="J158" s="1">
+      <c r="J163" s="1">
         <v>1116139</v>
       </c>
-      <c r="K158" s="1">
+      <c r="K163" s="1">
         <v>26</v>
       </c>
-      <c r="L158" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M158" s="1">
+      <c r="L163" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M163" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A164" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B164" s="1">
+        <v>1014</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D164" s="1">
+        <v>2004</v>
+      </c>
+      <c r="E164" s="1">
+        <v>0</v>
+      </c>
+      <c r="F164" s="1">
+        <v>0</v>
+      </c>
+      <c r="G164" s="1">
+        <v>100</v>
+      </c>
+      <c r="H164" s="1">
+        <v>1</v>
+      </c>
+      <c r="I164" s="1">
+        <v>2497</v>
+      </c>
+      <c r="J164" s="1">
+        <v>1116139</v>
+      </c>
+      <c r="K164" s="1">
+        <v>26</v>
+      </c>
+      <c r="L164" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M164" s="1">
         <v>0</v>
       </c>
     </row>
@@ -8392,7 +8638,7 @@
         <v>1101</v>
       </c>
       <c r="K7" s="2" t="str">
-        <f>VLOOKUP(J7,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" ref="K7:K34" si="0">VLOOKUP(J7,$P$7:$Q$34,2,FALSE)</f>
         <v>芜菁种子</v>
       </c>
       <c r="L7" s="1">
@@ -8416,7 +8662,7 @@
         <v>1102</v>
       </c>
       <c r="K8" s="2" t="str">
-        <f>VLOOKUP(J8,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>卷心菜种子</v>
       </c>
       <c r="L8" s="1">
@@ -8440,7 +8686,7 @@
         <v>1103</v>
       </c>
       <c r="K9" s="2" t="str">
-        <f>VLOOKUP(J9,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>葱种子</v>
       </c>
       <c r="L9" s="1">
@@ -8464,7 +8710,7 @@
         <v>1104</v>
       </c>
       <c r="K10" s="2" t="str">
-        <f>VLOOKUP(J10,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>萝卜种子</v>
       </c>
       <c r="L10" s="1">
@@ -8488,7 +8734,7 @@
         <v>1105</v>
       </c>
       <c r="K11" s="2" t="str">
-        <f>VLOOKUP(J11,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>紫甘蓝种子</v>
       </c>
       <c r="L11" s="1">
@@ -8512,7 +8758,7 @@
         <v>1106</v>
       </c>
       <c r="K12" s="2" t="str">
-        <f>VLOOKUP(J12,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>黄瓜种子</v>
       </c>
       <c r="L12" s="1">
@@ -8536,7 +8782,7 @@
         <v>1107</v>
       </c>
       <c r="K13" s="2" t="str">
-        <f>VLOOKUP(J13,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>西兰花种子</v>
       </c>
       <c r="L13" s="1">
@@ -8560,7 +8806,7 @@
         <v>1108</v>
       </c>
       <c r="K14" s="2" t="str">
-        <f>VLOOKUP(J14,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>番茄种子</v>
       </c>
       <c r="L14" s="1">
@@ -8584,7 +8830,7 @@
         <v>1109</v>
       </c>
       <c r="K15" s="2" t="str">
-        <f>VLOOKUP(J15,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>胡萝卜种子</v>
       </c>
       <c r="L15" s="1">
@@ -8608,7 +8854,7 @@
         <v>1110</v>
       </c>
       <c r="K16" s="2" t="str">
-        <f>VLOOKUP(J16,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>西瓜种子</v>
       </c>
       <c r="L16" s="1">
@@ -8632,7 +8878,7 @@
         <v>1111</v>
       </c>
       <c r="K17" s="2" t="str">
-        <f>VLOOKUP(J17,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>辣椒种子</v>
       </c>
       <c r="L17" s="1">
@@ -8656,7 +8902,7 @@
         <v>1112</v>
       </c>
       <c r="K18" s="2" t="str">
-        <f>VLOOKUP(J18,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>奇异果种子</v>
       </c>
       <c r="L18" s="1">
@@ -8680,7 +8926,7 @@
         <v>1113</v>
       </c>
       <c r="K19" s="2" t="str">
-        <f>VLOOKUP(J19,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>茄子种子</v>
       </c>
       <c r="L19" s="1">
@@ -8704,7 +8950,7 @@
         <v>1114</v>
       </c>
       <c r="K20" s="2" t="str">
-        <f>VLOOKUP(J20,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>豌豆种子</v>
       </c>
       <c r="L20" s="1">
@@ -8728,7 +8974,7 @@
         <v>1115</v>
       </c>
       <c r="K21" s="2" t="str">
-        <f>VLOOKUP(J21,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>土豆种子</v>
       </c>
       <c r="L21" s="1">
@@ -8752,7 +8998,7 @@
         <v>1116</v>
       </c>
       <c r="K22" s="2" t="str">
-        <f>VLOOKUP(J22,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>大蒜种子</v>
       </c>
       <c r="L22" s="1">
@@ -8776,7 +9022,7 @@
         <v>1117</v>
       </c>
       <c r="K23" s="2" t="str">
-        <f>VLOOKUP(J23,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>芦笋种子</v>
       </c>
       <c r="L23" s="1">
@@ -8800,7 +9046,7 @@
         <v>1118</v>
       </c>
       <c r="K24" s="2" t="str">
-        <f>VLOOKUP(J24,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>南瓜种子</v>
       </c>
       <c r="L24" s="1">
@@ -8824,7 +9070,7 @@
         <v>1119</v>
       </c>
       <c r="K25" s="2" t="str">
-        <f>VLOOKUP(J25,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>玉米种子</v>
       </c>
       <c r="L25" s="1">
@@ -8848,7 +9094,7 @@
         <v>1120</v>
       </c>
       <c r="K26" s="2" t="str">
-        <f>VLOOKUP(J26,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>大麦种子</v>
       </c>
       <c r="L26" s="1">
@@ -8872,7 +9118,7 @@
         <v>1121</v>
       </c>
       <c r="K27" s="2" t="str">
-        <f>VLOOKUP(J27,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>啤酒花种子</v>
       </c>
       <c r="L27" s="1">
@@ -8896,7 +9142,7 @@
         <v>1122</v>
       </c>
       <c r="K28" s="2" t="str">
-        <f>VLOOKUP(J28,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>葡萄种子</v>
       </c>
       <c r="L28" s="1">
@@ -8920,7 +9166,7 @@
         <v>1123</v>
       </c>
       <c r="K29" s="2" t="str">
-        <f>VLOOKUP(J29,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>菠萝种子</v>
       </c>
       <c r="L29" s="1">
@@ -8944,7 +9190,7 @@
         <v>1124</v>
       </c>
       <c r="K30" s="2" t="str">
-        <f>VLOOKUP(J30,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>咖啡种子</v>
       </c>
       <c r="L30" s="1">
@@ -8968,7 +9214,7 @@
         <v>1125</v>
       </c>
       <c r="K31" s="2" t="str">
-        <f>VLOOKUP(J31,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>草莓种子</v>
       </c>
       <c r="L31" s="1">
@@ -8992,7 +9238,7 @@
         <v>1126</v>
       </c>
       <c r="K32" s="2" t="str">
-        <f>VLOOKUP(J32,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>蓝莓种子</v>
       </c>
       <c r="L32" s="1">
@@ -9016,7 +9262,7 @@
         <v>1127</v>
       </c>
       <c r="K33" s="2" t="str">
-        <f>VLOOKUP(J33,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>红薯种子</v>
       </c>
       <c r="L33" s="1">
@@ -9040,7 +9286,7 @@
         <v>1128</v>
       </c>
       <c r="K34" s="2" t="str">
-        <f>VLOOKUP(J34,$P$7:$Q$34,2,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>甜菜种子</v>
       </c>
       <c r="L34" s="1">

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -7903,7 +7903,7 @@
         <v>3056</v>
       </c>
       <c r="J148" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K148" s="1" t="s">
         <v>36</v>
@@ -7944,7 +7944,7 @@
         <v>3056</v>
       </c>
       <c r="J149" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K149" s="1" t="s">
         <v>36</v>
@@ -7985,7 +7985,7 @@
         <v>3056</v>
       </c>
       <c r="J150" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K150" s="1" t="s">
         <v>36</v>
@@ -8026,7 +8026,7 @@
         <v>3056</v>
       </c>
       <c r="J151" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K151" s="1" t="s">
         <v>36</v>
@@ -8067,7 +8067,7 @@
         <v>3056</v>
       </c>
       <c r="J152" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K152" s="1" t="s">
         <v>36</v>
@@ -8108,7 +8108,7 @@
         <v>3056</v>
       </c>
       <c r="J153" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K153" s="1" t="s">
         <v>36</v>
@@ -8149,7 +8149,7 @@
         <v>3056</v>
       </c>
       <c r="J154" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K154" s="1" t="s">
         <v>36</v>
@@ -8190,7 +8190,7 @@
         <v>3056</v>
       </c>
       <c r="J155" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K155" s="1" t="s">
         <v>36</v>
@@ -8231,7 +8231,7 @@
         <v>3056</v>
       </c>
       <c r="J156" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K156" s="1" t="s">
         <v>36</v>
@@ -8272,7 +8272,7 @@
         <v>3056</v>
       </c>
       <c r="J157" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K157" s="1" t="s">
         <v>36</v>
@@ -8313,7 +8313,7 @@
         <v>3056</v>
       </c>
       <c r="J158" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K158" s="1" t="s">
         <v>36</v>
@@ -8354,7 +8354,7 @@
         <v>3056</v>
       </c>
       <c r="J159" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>36</v>
@@ -8395,7 +8395,7 @@
         <v>3056</v>
       </c>
       <c r="J160" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K160" s="1" t="s">
         <v>36</v>
@@ -8436,7 +8436,7 @@
         <v>3056</v>
       </c>
       <c r="J161" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K161" s="1" t="s">
         <v>36</v>
@@ -8477,7 +8477,7 @@
         <v>3056</v>
       </c>
       <c r="J162" s="1">
-        <v>1019972</v>
+        <v>1182578</v>
       </c>
       <c r="K162" s="1" t="s">
         <v>36</v>

--- a/Datas/ShopDataList.xlsx
+++ b/Datas/ShopDataList.xlsx
@@ -1549,12 +1549,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1572,7 +1578,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1588,6 +1594,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6767,208 +6776,208 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A121" s="1" t="s">
+    <row r="121" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B121" s="1">
+      <c r="B121" s="6">
         <v>1008</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D121" s="1">
+      <c r="D121" s="6">
         <v>1600</v>
       </c>
-      <c r="E121" s="1">
-        <v>0</v>
-      </c>
-      <c r="F121" s="1">
-        <v>0</v>
-      </c>
-      <c r="G121" s="1">
+      <c r="E121" s="6">
+        <v>0</v>
+      </c>
+      <c r="F121" s="6">
+        <v>0</v>
+      </c>
+      <c r="G121" s="6">
         <v>100</v>
       </c>
-      <c r="H121" s="1">
+      <c r="H121" s="6">
         <v>1</v>
       </c>
-      <c r="I121" s="1">
+      <c r="I121" s="6">
         <v>1756</v>
       </c>
-      <c r="J121" s="1">
+      <c r="J121" s="6">
         <v>1019120</v>
       </c>
-      <c r="K121" s="1" t="s">
+      <c r="K121" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L121" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M121" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A122" s="1" t="s">
+      <c r="L121" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M121" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B122" s="1">
+      <c r="B122" s="6">
         <v>1008</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D122" s="1">
+      <c r="D122" s="6">
         <v>1605</v>
       </c>
-      <c r="E122" s="1">
-        <v>0</v>
-      </c>
-      <c r="F122" s="1">
-        <v>0</v>
-      </c>
-      <c r="G122" s="1">
+      <c r="E122" s="6">
+        <v>0</v>
+      </c>
+      <c r="F122" s="6">
+        <v>0</v>
+      </c>
+      <c r="G122" s="6">
         <v>100</v>
       </c>
-      <c r="H122" s="1">
+      <c r="H122" s="6">
         <v>1</v>
       </c>
-      <c r="I122" s="1">
+      <c r="I122" s="6">
         <v>1756</v>
       </c>
-      <c r="J122" s="1">
+      <c r="J122" s="6">
         <v>1019120</v>
       </c>
-      <c r="K122" s="1" t="s">
+      <c r="K122" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L122" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M122" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A123" s="1" t="s">
+      <c r="L122" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M122" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B123" s="1">
+      <c r="B123" s="6">
         <v>1008</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C123" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D123" s="1">
+      <c r="D123" s="6">
         <v>1609</v>
       </c>
-      <c r="E123" s="1">
-        <v>0</v>
-      </c>
-      <c r="F123" s="1">
-        <v>0</v>
-      </c>
-      <c r="G123" s="1">
+      <c r="E123" s="6">
+        <v>0</v>
+      </c>
+      <c r="F123" s="6">
+        <v>0</v>
+      </c>
+      <c r="G123" s="6">
         <v>100</v>
       </c>
-      <c r="H123" s="1">
+      <c r="H123" s="6">
         <v>1</v>
       </c>
-      <c r="I123" s="1">
+      <c r="I123" s="6">
         <v>1756</v>
       </c>
-      <c r="J123" s="1">
+      <c r="J123" s="6">
         <v>1019120</v>
       </c>
-      <c r="K123" s="1" t="s">
+      <c r="K123" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L123" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M123" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A124" s="1" t="s">
+      <c r="L123" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M123" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B124" s="1">
+      <c r="B124" s="6">
         <v>1008</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D124" s="1">
+      <c r="D124" s="6">
         <v>1612</v>
       </c>
-      <c r="E124" s="1">
-        <v>0</v>
-      </c>
-      <c r="F124" s="1">
-        <v>0</v>
-      </c>
-      <c r="G124" s="1">
+      <c r="E124" s="6">
+        <v>0</v>
+      </c>
+      <c r="F124" s="6">
+        <v>0</v>
+      </c>
+      <c r="G124" s="6">
         <v>100</v>
       </c>
-      <c r="H124" s="1">
+      <c r="H124" s="6">
         <v>1</v>
       </c>
-      <c r="I124" s="1">
+      <c r="I124" s="6">
         <v>1756</v>
       </c>
-      <c r="J124" s="1">
+      <c r="J124" s="6">
         <v>1019120</v>
       </c>
-      <c r="K124" s="1" t="s">
+      <c r="K124" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L124" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M124" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A125" s="1" t="s">
+      <c r="L124" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M124" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B125" s="1">
+      <c r="B125" s="6">
         <v>1008</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D125" s="1">
+      <c r="D125" s="6">
         <v>1613</v>
       </c>
-      <c r="E125" s="1">
-        <v>0</v>
-      </c>
-      <c r="F125" s="1">
-        <v>0</v>
-      </c>
-      <c r="G125" s="1">
+      <c r="E125" s="6">
+        <v>0</v>
+      </c>
+      <c r="F125" s="6">
+        <v>0</v>
+      </c>
+      <c r="G125" s="6">
         <v>100</v>
       </c>
-      <c r="H125" s="1">
+      <c r="H125" s="6">
         <v>1</v>
       </c>
-      <c r="I125" s="1">
+      <c r="I125" s="6">
         <v>1756</v>
       </c>
-      <c r="J125" s="1">
+      <c r="J125" s="6">
         <v>1019120</v>
       </c>
-      <c r="K125" s="1" t="s">
+      <c r="K125" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L125" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M125" s="1">
+      <c r="L125" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M125" s="6">
         <v>0</v>
       </c>
     </row>
